--- a/data/leagues/BP- Loudoun 2025 2026.xlsx
+++ b/data/leagues/BP- Loudoun 2025 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="115">
   <si>
     <t>Bears, Jags, Foxes, Oh My!</t>
   </si>
@@ -67,10 +67,13 @@
     <t>Dave's Dynamos</t>
   </si>
   <si>
-    <t>0-1-0</t>
-  </si>
-  <si>
-    <t>1-0-0</t>
+    <t>0-2-0</t>
+  </si>
+  <si>
+    <t>2-0-0</t>
+  </si>
+  <si>
+    <t>1-1-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -142,6 +145,9 @@
     <t>Week_2</t>
   </si>
   <si>
+    <t>Week_3</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -163,45 +169,45 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Ishan Goel</t>
+  </si>
+  <si>
+    <t>Roy Armbruster</t>
+  </si>
+  <si>
+    <t>Chungfu Yang</t>
+  </si>
+  <si>
+    <t>MARVIN AYALA</t>
+  </si>
+  <si>
+    <t>Matthew Graesser</t>
+  </si>
+  <si>
+    <t>Dale Goodwin</t>
+  </si>
+  <si>
+    <t>Daniel Tracey</t>
+  </si>
+  <si>
+    <t>Jeffrey Laidacker</t>
+  </si>
+  <si>
+    <t>Hannah Davis</t>
+  </si>
+  <si>
+    <t>Dave Linton</t>
+  </si>
+  <si>
+    <t>Justin Fox</t>
+  </si>
+  <si>
+    <t>Jessica Stratton</t>
+  </si>
+  <si>
     <t>Robert Schottler</t>
   </si>
   <si>
-    <t>Daniel Tracey</t>
-  </si>
-  <si>
-    <t>Dale Goodwin</t>
-  </si>
-  <si>
-    <t>Roy Armbruster</t>
-  </si>
-  <si>
-    <t>MARVIN AYALA</t>
-  </si>
-  <si>
-    <t>Jeffrey Laidacker</t>
-  </si>
-  <si>
-    <t>Chungfu Yang</t>
-  </si>
-  <si>
-    <t>Dave Linton</t>
-  </si>
-  <si>
-    <t>Justin Fox</t>
-  </si>
-  <si>
-    <t>Hannah Davis</t>
-  </si>
-  <si>
-    <t>Ishan Goel</t>
-  </si>
-  <si>
-    <t>Jessica Stratton</t>
-  </si>
-  <si>
-    <t>Matthew Graesser</t>
-  </si>
-  <si>
     <t>Yahya Ayaz</t>
   </si>
   <si>
@@ -229,72 +235,78 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>1-0</t>
-  </si>
-  <si>
-    <t>0-1</t>
-  </si>
-  <si>
-    <t>11.9-2.0-0.1</t>
-  </si>
-  <si>
-    <t>9.7-4.2-0.1</t>
-  </si>
-  <si>
-    <t>8.8-5.0-0.1</t>
-  </si>
-  <si>
-    <t>8.8-5.1-0.1</t>
-  </si>
-  <si>
-    <t>8.0-5.9-0.1</t>
-  </si>
-  <si>
-    <t>7.3-6.6-0.1</t>
+    <t>2-0</t>
+  </si>
+  <si>
+    <t>1-1</t>
+  </si>
+  <si>
+    <t>0-2</t>
+  </si>
+  <si>
+    <t>11.2-2.7-0.1</t>
+  </si>
+  <si>
+    <t>10.5-3.3-0.1</t>
+  </si>
+  <si>
+    <t>9.3-4.7</t>
+  </si>
+  <si>
+    <t>9.3-4.6-0.1</t>
+  </si>
+  <si>
+    <t>8.7-5.1-0.2</t>
+  </si>
+  <si>
+    <t>7.7-6.2-0.1</t>
+  </si>
+  <si>
+    <t>7.1-6.7-0.1</t>
   </si>
   <si>
     <t>6.8-7.1-0.1</t>
   </si>
   <si>
-    <t>6.1-7.8-0.1</t>
-  </si>
-  <si>
-    <t>6.0-7.9-0.1</t>
-  </si>
-  <si>
-    <t>5.2-8.7-0.1</t>
-  </si>
-  <si>
-    <t>4.8-9.1-0.1</t>
-  </si>
-  <si>
-    <t>4.6-9.3-0.1</t>
+    <t>5.7-8.2-0.1</t>
+  </si>
+  <si>
+    <t>5.1-8.8-0.1</t>
+  </si>
+  <si>
+    <t>4.9-9.0-0.1</t>
+  </si>
+  <si>
+    <t>3.9-9.9-0.1</t>
+  </si>
+  <si>
+    <t>3.6-10.3-0.1</t>
   </si>
   <si>
     <t>3.3-10.6-0.1</t>
   </si>
   <si>
-    <t>12-2</t>
+    <t>11-3</t>
+  </si>
+  <si>
+    <t>9-5</t>
   </si>
   <si>
     <t>10-4</t>
   </si>
   <si>
-    <t>9-5</t>
-  </si>
-  <si>
     <t>8-6</t>
   </si>
   <si>
     <t>7-7</t>
   </si>
   <si>
-    <t>6-8</t>
-  </si>
-  <si>
     <t>5-9</t>
   </si>
   <si>
+    <t>4-10</t>
+  </si>
+  <si>
     <t>3-11</t>
   </si>
   <si>
@@ -307,7 +319,34 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↑4</t>
+  </si>
+  <si>
+    <t>↑1</t>
+  </si>
+  <si>
+    <t>↓1</t>
+  </si>
+  <si>
+    <t>↑6</t>
+  </si>
+  <si>
+    <t>↓2</t>
+  </si>
+  <si>
+    <t>↑8</t>
+  </si>
+  <si>
+    <t>↓9</t>
+  </si>
+  <si>
+    <t>↓11</t>
+  </si>
+  <si>
     <t>Week 1</t>
+  </si>
+  <si>
+    <t>Week 2</t>
   </si>
   <si>
     <t>Week</t>
@@ -741,25 +780,25 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s">
         <v>14</v>
       </c>
       <c r="I2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J2" t="s">
         <v>14</v>
@@ -771,10 +810,10 @@
         <v>15</v>
       </c>
       <c r="M2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O2" t="s">
         <v>15</v>
@@ -794,25 +833,25 @@
         <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I3" t="s">
         <v>15</v>
       </c>
       <c r="J3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L3" t="s">
         <v>15</v>
@@ -821,7 +860,7 @@
         <v>15</v>
       </c>
       <c r="N3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O3" t="s">
         <v>15</v>
@@ -832,7 +871,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
@@ -844,7 +883,7 @@
         <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
@@ -853,13 +892,13 @@
         <v>15</v>
       </c>
       <c r="I4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L4" t="s">
         <v>15</v>
@@ -868,7 +907,7 @@
         <v>15</v>
       </c>
       <c r="N4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O4" t="s">
         <v>15</v>
@@ -879,40 +918,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
         <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G5" t="s">
         <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J5" t="s">
         <v>14</v>
       </c>
       <c r="K5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N5" t="s">
         <v>15</v>
@@ -929,28 +968,28 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6" t="s">
         <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K6" t="s">
         <v>14</v>
@@ -959,13 +998,13 @@
         <v>15</v>
       </c>
       <c r="M6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -973,46 +1012,46 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -1029,7 +1068,7 @@
         <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F8" t="s">
         <v>14</v>
@@ -1041,7 +1080,7 @@
         <v>14</v>
       </c>
       <c r="I8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J8" t="s">
         <v>14</v>
@@ -1050,7 +1089,7 @@
         <v>14</v>
       </c>
       <c r="L8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M8" t="s">
         <v>14</v>
@@ -1076,19 +1115,19 @@
         <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s">
         <v>14</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H9" t="s">
         <v>14</v>
       </c>
       <c r="I9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J9" t="s">
         <v>14</v>
@@ -1100,13 +1139,13 @@
         <v>15</v>
       </c>
       <c r="M9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -1114,7 +1153,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>
@@ -1123,22 +1162,22 @@
         <v>15</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K10" t="s">
         <v>14</v>
@@ -1150,7 +1189,7 @@
         <v>15</v>
       </c>
       <c r="N10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O10" t="s">
         <v>15</v>
@@ -1164,13 +1203,13 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F11" t="s">
         <v>14</v>
@@ -1182,7 +1221,7 @@
         <v>14</v>
       </c>
       <c r="I11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J11" t="s">
         <v>14</v>
@@ -1191,7 +1230,7 @@
         <v>14</v>
       </c>
       <c r="L11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M11" t="s">
         <v>14</v>
@@ -1200,7 +1239,7 @@
         <v>14</v>
       </c>
       <c r="O11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -1217,13 +1256,13 @@
         <v>14</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F12" t="s">
         <v>14</v>
       </c>
       <c r="G12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H12" t="s">
         <v>14</v>
@@ -1244,10 +1283,10 @@
         <v>14</v>
       </c>
       <c r="N12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -1255,16 +1294,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F13" t="s">
         <v>14</v>
@@ -1276,13 +1315,13 @@
         <v>14</v>
       </c>
       <c r="I13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J13" t="s">
         <v>14</v>
       </c>
       <c r="K13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L13" t="s">
         <v>15</v>
@@ -1291,7 +1330,7 @@
         <v>15</v>
       </c>
       <c r="N13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O13" t="s">
         <v>15</v>
@@ -1302,16 +1341,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F14" t="s">
         <v>14</v>
@@ -1320,16 +1359,16 @@
         <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L14" t="s">
         <v>15</v>
@@ -1338,7 +1377,7 @@
         <v>15</v>
       </c>
       <c r="N14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O14" t="s">
         <v>15</v>
@@ -1370,10 +1409,10 @@
         <v>15</v>
       </c>
       <c r="I15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K15" t="s">
         <v>15</v>
@@ -1385,7 +1424,7 @@
         <v>15</v>
       </c>
       <c r="N15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O15" t="s">
         <v>15</v>
@@ -1398,30 +1437,108 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:H1"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:8">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>101</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2">
+        <v>-3</v>
+      </c>
+      <c r="F2">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1436,13 +1553,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1450,10 +1567,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>0.07142857142857142</v>
+        <v>0.5</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -1464,13 +1581,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>0.1428571428571428</v>
+        <v>0.5</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1478,10 +1595,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>0.2142857142857143</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -1492,13 +1609,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>0.2857142857142857</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1506,10 +1623,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>0.2857142857142857</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
@@ -1520,13 +1637,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C7">
-        <v>0.4285714285714285</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1534,10 +1651,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>0.4285714285714285</v>
+        <v>1</v>
       </c>
       <c r="D8" t="s">
         <v>15</v>
@@ -1548,13 +1665,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9">
         <v>1</v>
       </c>
-      <c r="C9">
-        <v>0.5</v>
-      </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1562,13 +1679,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>0.6428571428571429</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1576,10 +1693,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>0.6428571428571429</v>
+        <v>1.214285714285714</v>
       </c>
       <c r="D11" t="s">
         <v>15</v>
@@ -1590,13 +1707,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C12">
-        <v>0.7857142857142857</v>
+        <v>1.214285714285714</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1604,13 +1721,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>0.7857142857142857</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1618,13 +1735,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C14">
-        <v>0.8571428571428571</v>
+        <v>1.571428571428571</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1632,10 +1749,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C15">
-        <v>0.9285714285714286</v>
+        <v>1.642857142857143</v>
       </c>
       <c r="D15" t="s">
         <v>15</v>
@@ -1653,16 +1770,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1670,13 +1787,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>1.785714285714286</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>-0.2142857142857142</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
@@ -1687,13 +1804,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>0.9285714285714286</v>
+        <v>1.571428571428571</v>
       </c>
       <c r="D3">
-        <v>-0.0714285714285714</v>
+        <v>-0.4285714285714286</v>
       </c>
       <c r="E3" t="s">
         <v>15</v>
@@ -1704,13 +1821,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>0.8571428571428571</v>
+        <v>1.571428571428571</v>
       </c>
       <c r="D4">
-        <v>-0.1428571428571429</v>
+        <v>-0.4285714285714286</v>
       </c>
       <c r="E4" t="s">
         <v>15</v>
@@ -1721,16 +1838,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>0.7857142857142857</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="D5">
-        <v>-0.2142857142857143</v>
+        <v>0.2857142857142858</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1741,13 +1858,13 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>0.6428571428571429</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="D6">
-        <v>-0.3571428571428571</v>
+        <v>0.2857142857142858</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1755,16 +1872,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>0.6428571428571429</v>
+        <v>1.214285714285714</v>
       </c>
       <c r="D7">
-        <v>0.6428571428571429</v>
+        <v>-0.7857142857142858</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1772,16 +1889,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>1.071428571428571</v>
       </c>
       <c r="D8">
-        <v>0.5</v>
+        <v>-0.9285714285714286</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1789,16 +1906,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C9">
-        <v>0.4285714285714285</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>-0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1806,13 +1923,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>0.4285714285714285</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="D10">
-        <v>0.4285714285714285</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="E10" t="s">
         <v>14</v>
@@ -1823,16 +1940,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11">
-        <v>0.2857142857142857</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="D11">
-        <v>-0.7142857142857143</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1840,16 +1957,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>0.2857142857142857</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D12">
-        <v>0.2857142857142857</v>
+        <v>-0.4285714285714286</v>
       </c>
       <c r="E12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1857,13 +1974,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C13">
-        <v>0.1428571428571428</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D13">
-        <v>0.1428571428571428</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="E13" t="s">
         <v>14</v>
@@ -1874,13 +1991,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C14">
-        <v>0.07142857142857142</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="D14">
-        <v>0.07142857142857142</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="E14" t="s">
         <v>14</v>
@@ -1891,13 +2008,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="E15" t="s">
         <v>14</v>
@@ -1915,78 +2032,78 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B2">
-        <v>80.5</v>
+        <v>52.5</v>
       </c>
       <c r="C2">
-        <v>14.3</v>
+        <v>24.8</v>
       </c>
       <c r="D2">
-        <v>3.8</v>
+        <v>11.7</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="F2">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="H2">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -2010,157 +2127,157 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>9.5</v>
+        <v>22.3</v>
       </c>
       <c r="C3">
-        <v>34.8</v>
+        <v>33.5</v>
       </c>
       <c r="D3">
-        <v>22.2</v>
+        <v>21.6</v>
       </c>
       <c r="E3">
-        <v>15.8</v>
+        <v>10.9</v>
       </c>
       <c r="F3">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="G3">
-        <v>5.4</v>
+        <v>2.8</v>
       </c>
       <c r="H3">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="I3">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J3">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="K3">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M3">
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>94.90000000000001</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>11.5</v>
       </c>
       <c r="C4">
-        <v>18.6</v>
+        <v>15.6</v>
       </c>
       <c r="D4">
-        <v>20.8</v>
+        <v>19.4</v>
       </c>
       <c r="E4">
-        <v>18</v>
+        <v>16.4</v>
       </c>
       <c r="F4">
-        <v>13.4</v>
+        <v>13.8</v>
       </c>
       <c r="G4">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="H4">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="I4">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="J4">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="K4">
         <v>1.6</v>
       </c>
       <c r="L4">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="M4">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="N4">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>84.5</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>9.4</v>
+      </c>
+      <c r="C5">
+        <v>13.3</v>
+      </c>
+      <c r="D5">
+        <v>19.2</v>
+      </c>
+      <c r="E5">
+        <v>20.2</v>
+      </c>
+      <c r="F5">
+        <v>13.6</v>
+      </c>
+      <c r="G5">
+        <v>10</v>
+      </c>
+      <c r="H5">
         <v>8</v>
       </c>
-      <c r="B5">
-        <v>2.9</v>
-      </c>
-      <c r="C5">
-        <v>17.2</v>
-      </c>
-      <c r="D5">
-        <v>21.7</v>
-      </c>
-      <c r="E5">
-        <v>17.8</v>
-      </c>
-      <c r="F5">
-        <v>14.6</v>
-      </c>
-      <c r="G5">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H5">
-        <v>7</v>
-      </c>
       <c r="I5">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="J5">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="K5">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="L5">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="M5">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>83.40000000000001</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2168,349 +2285,349 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="C6">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="D6">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="E6">
-        <v>15.3</v>
+        <v>21.3</v>
       </c>
       <c r="F6">
-        <v>16.5</v>
+        <v>21.7</v>
       </c>
       <c r="G6">
-        <v>14.5</v>
+        <v>17.7</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="I6">
-        <v>7.5</v>
+        <v>4.2</v>
       </c>
       <c r="J6">
-        <v>5.7</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>4.7</v>
+        <v>0.7</v>
       </c>
       <c r="L6">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="M6">
-        <v>2.3</v>
+        <v>0.1</v>
       </c>
       <c r="N6">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>66.7</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="C7">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="D7">
-        <v>9.1</v>
+        <v>7.2</v>
       </c>
       <c r="E7">
-        <v>12.3</v>
+        <v>10.6</v>
       </c>
       <c r="F7">
-        <v>12.5</v>
+        <v>15.4</v>
       </c>
       <c r="G7">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="H7">
-        <v>12.3</v>
+        <v>15.5</v>
       </c>
       <c r="I7">
-        <v>10.5</v>
+        <v>10.8</v>
       </c>
       <c r="J7">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="K7">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="L7">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="M7">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="N7">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="O7">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="P7">
-        <v>54.3</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>0.4</v>
+      </c>
+      <c r="C8">
+        <v>2.1</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8">
+        <v>7.1</v>
+      </c>
+      <c r="F8">
         <v>11</v>
       </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>1.7</v>
-      </c>
-      <c r="D8">
-        <v>3.7</v>
-      </c>
-      <c r="E8">
-        <v>6.3</v>
-      </c>
-      <c r="F8">
-        <v>10.3</v>
-      </c>
       <c r="G8">
-        <v>12.2</v>
+        <v>14.1</v>
       </c>
       <c r="H8">
-        <v>14.1</v>
+        <v>18.5</v>
       </c>
       <c r="I8">
-        <v>13.7</v>
+        <v>15.4</v>
       </c>
       <c r="J8">
-        <v>10.7</v>
+        <v>11.6</v>
       </c>
       <c r="K8">
-        <v>10.8</v>
+        <v>6.6</v>
       </c>
       <c r="L8">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="M8">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="N8">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="O8">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="P8">
-        <v>34.2</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B9">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="D9">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="E9">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="F9">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="G9">
-        <v>9.199999999999999</v>
+        <v>12.9</v>
       </c>
       <c r="H9">
-        <v>12.6</v>
+        <v>15.1</v>
       </c>
       <c r="I9">
-        <v>11.6</v>
+        <v>22.5</v>
       </c>
       <c r="J9">
-        <v>12.3</v>
+        <v>16.5</v>
       </c>
       <c r="K9">
-        <v>10.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L9">
-        <v>10.1</v>
+        <v>5.3</v>
       </c>
       <c r="M9">
-        <v>10.4</v>
+        <v>2.9</v>
       </c>
       <c r="N9">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="O9">
-        <v>3.2</v>
+        <v>0.1</v>
       </c>
       <c r="P9">
-        <v>23.5</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B10">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D10">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="F10">
+        <v>3.7</v>
+      </c>
+      <c r="G10">
         <v>6.8</v>
       </c>
-      <c r="G10">
-        <v>8.699999999999999</v>
-      </c>
       <c r="H10">
-        <v>12.4</v>
+        <v>12.7</v>
       </c>
       <c r="I10">
-        <v>14.2</v>
+        <v>13.7</v>
       </c>
       <c r="J10">
-        <v>13.4</v>
+        <v>14.8</v>
       </c>
       <c r="K10">
-        <v>10.4</v>
+        <v>15.2</v>
       </c>
       <c r="L10">
-        <v>10.5</v>
+        <v>12.6</v>
       </c>
       <c r="M10">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="N10">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O10">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="P10">
-        <v>22.2</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="D11">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="F11">
-        <v>4.9</v>
+        <v>1.5</v>
       </c>
       <c r="G11">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="H11">
-        <v>9.1</v>
+        <v>5.3</v>
       </c>
       <c r="I11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J11">
         <v>13.6</v>
       </c>
-      <c r="J11">
-        <v>12.2</v>
-      </c>
       <c r="K11">
-        <v>14.8</v>
+        <v>15.6</v>
       </c>
       <c r="L11">
-        <v>12.7</v>
+        <v>16.2</v>
       </c>
       <c r="M11">
-        <v>11</v>
+        <v>15.1</v>
       </c>
       <c r="N11">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="O11">
-        <v>3.3</v>
+        <v>7.8</v>
       </c>
       <c r="P11">
-        <v>15.9</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B12">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="E12">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="F12">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="G12">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="H12">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="I12">
-        <v>7.1</v>
+        <v>10.1</v>
       </c>
       <c r="J12">
-        <v>13.7</v>
+        <v>16.7</v>
       </c>
       <c r="K12">
-        <v>12.9</v>
+        <v>17.9</v>
       </c>
       <c r="L12">
-        <v>14.8</v>
+        <v>15.1</v>
       </c>
       <c r="M12">
-        <v>14.3</v>
+        <v>13.5</v>
       </c>
       <c r="N12">
-        <v>14.2</v>
+        <v>10.2</v>
       </c>
       <c r="O12">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="P12">
-        <v>8.6</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2524,43 +2641,43 @@
         <v>0</v>
       </c>
       <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0.1</v>
+      </c>
+      <c r="F13">
+        <v>0.2</v>
+      </c>
+      <c r="G13">
         <v>0.6</v>
       </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13">
-        <v>1.9</v>
-      </c>
-      <c r="G13">
-        <v>3.4</v>
-      </c>
       <c r="H13">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="I13">
-        <v>6.6</v>
+        <v>2.9</v>
       </c>
       <c r="J13">
-        <v>7.9</v>
+        <v>5.2</v>
       </c>
       <c r="K13">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="L13">
-        <v>17.2</v>
+        <v>17.6</v>
       </c>
       <c r="M13">
-        <v>15.8</v>
+        <v>19.4</v>
       </c>
       <c r="N13">
-        <v>19.7</v>
+        <v>21.4</v>
       </c>
       <c r="O13">
-        <v>12.3</v>
+        <v>18.5</v>
       </c>
       <c r="P13">
-        <v>6.9</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2574,48 +2691,48 @@
         <v>0</v>
       </c>
       <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0.2</v>
+      </c>
+      <c r="G14">
         <v>0.3</v>
       </c>
-      <c r="E14">
-        <v>0.6</v>
-      </c>
-      <c r="F14">
-        <v>1.6</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
       <c r="H14">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="I14">
-        <v>5.7</v>
+        <v>1.7</v>
       </c>
       <c r="J14">
-        <v>7.9</v>
+        <v>4.8</v>
       </c>
       <c r="K14">
-        <v>11.6</v>
+        <v>10.1</v>
       </c>
       <c r="L14">
-        <v>12.8</v>
+        <v>15</v>
       </c>
       <c r="M14">
-        <v>17.4</v>
+        <v>22.1</v>
       </c>
       <c r="N14">
-        <v>22.5</v>
+        <v>25.4</v>
       </c>
       <c r="O14">
-        <v>13.8</v>
+        <v>19.5</v>
       </c>
       <c r="P14">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2627,40 +2744,40 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F15">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="I15">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J15">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="K15">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="L15">
-        <v>7</v>
+        <v>9.9</v>
       </c>
       <c r="M15">
-        <v>11.6</v>
+        <v>13.9</v>
       </c>
       <c r="N15">
-        <v>18.3</v>
+        <v>22.6</v>
       </c>
       <c r="O15">
-        <v>54.2</v>
+        <v>42.5</v>
       </c>
       <c r="P15">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -2670,169 +2787,214 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>39</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
+        <v>95.5</v>
+      </c>
+      <c r="C2">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="D2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>84.89999999999999</v>
+      </c>
+      <c r="C3">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="D3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>18.8</v>
+      </c>
+      <c r="C4">
+        <v>82.39999999999999</v>
+      </c>
+      <c r="D4">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>99.7</v>
-      </c>
-      <c r="C2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3">
-        <v>96.39999999999999</v>
-      </c>
-      <c r="C3">
-        <v>94.19999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="C4">
-        <v>85.59999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="B5">
-        <v>82.5</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="C5">
-        <v>84.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="D5">
+        <v>86.90000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B6">
-        <v>68.60000000000001</v>
+        <v>70.89999999999999</v>
       </c>
       <c r="C6">
-        <v>65.8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>79.7</v>
+      </c>
+      <c r="D6">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="C7">
+        <v>54.90000000000001</v>
+      </c>
+      <c r="D7">
+        <v>54.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>83.89999999999999</v>
+      </c>
+      <c r="C8">
+        <v>38</v>
+      </c>
+      <c r="D8">
+        <v>39.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>35.09999999999999</v>
+      </c>
+      <c r="C9">
+        <v>34.2</v>
+      </c>
+      <c r="D9">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B7">
-        <v>53.40000000000001</v>
-      </c>
-      <c r="C7">
-        <v>52.8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8">
-        <v>38.1</v>
-      </c>
-      <c r="C8">
-        <v>35.6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9">
-        <v>23.5</v>
-      </c>
-      <c r="C9">
-        <v>23.1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
+      <c r="B10">
+        <v>53</v>
+      </c>
+      <c r="C10">
+        <v>13.7</v>
+      </c>
+      <c r="D10">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B10">
-        <v>16.9</v>
-      </c>
-      <c r="C10">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="B11">
-        <v>17.5</v>
+        <v>19.8</v>
       </c>
       <c r="C11">
-        <v>15.4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="D11">
+        <v>6.600000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12">
+        <v>21.2</v>
+      </c>
+      <c r="C12">
+        <v>4.5</v>
+      </c>
+      <c r="D12">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="C13">
+        <v>0.2</v>
+      </c>
+      <c r="D13">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B12">
-        <v>7.9</v>
-      </c>
-      <c r="C12">
-        <v>7.399999999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="1" t="s">
+      <c r="B14">
+        <v>7.3</v>
+      </c>
+      <c r="C14">
+        <v>0.5</v>
+      </c>
+      <c r="D14">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B13">
-        <v>2.9</v>
-      </c>
-      <c r="C13">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14">
-        <v>6.5</v>
-      </c>
-      <c r="C14">
-        <v>5.800000000000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="B15">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="C15">
-        <v>0.8</v>
+        <v>0.3</v>
+      </c>
+      <c r="D15">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -2847,28 +3009,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2876,28 +3038,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D2">
-        <v>81.59999999999999</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>110.22</v>
+        <v>104.49</v>
       </c>
       <c r="G2">
-        <v>0.538</v>
+        <v>0.542</v>
       </c>
       <c r="H2">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="I2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2905,28 +3067,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3">
-        <v>95.42</v>
+        <v>78.27</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>109.15</v>
+        <v>104.49</v>
       </c>
       <c r="G3">
-        <v>0.462</v>
+        <v>0.542</v>
       </c>
       <c r="H3">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2934,28 +3096,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D4">
-        <v>94.31999999999999</v>
+        <v>87.98</v>
       </c>
       <c r="E4" t="s">
         <v>14</v>
       </c>
       <c r="F4">
-        <v>109.24</v>
+        <v>102.56</v>
       </c>
       <c r="G4">
-        <v>0.538</v>
+        <v>0.5</v>
       </c>
       <c r="H4">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="I4">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2963,28 +3125,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D5">
-        <v>96.66</v>
+        <v>97.83</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5">
-        <v>109.06</v>
+        <v>102.56</v>
       </c>
       <c r="G5">
-        <v>0.538</v>
+        <v>0.5</v>
       </c>
       <c r="H5">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="I5">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2992,28 +3154,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D6">
-        <v>102.8</v>
+        <v>116.34</v>
       </c>
       <c r="E6" t="s">
         <v>15</v>
       </c>
       <c r="F6">
-        <v>108.58</v>
+        <v>101.02</v>
       </c>
       <c r="G6">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="H6">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3021,28 +3183,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7">
+        <v>87.92</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7">
+        <v>101.02</v>
+      </c>
+      <c r="G7">
+        <v>0.5</v>
+      </c>
+      <c r="H7">
+        <v>-0.2</v>
+      </c>
+      <c r="I7">
         <v>12</v>
-      </c>
-      <c r="C7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7">
-        <v>112.16</v>
-      </c>
-      <c r="E7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7">
-        <v>107.86</v>
-      </c>
-      <c r="G7">
-        <v>0.462</v>
-      </c>
-      <c r="H7">
-        <v>0.1</v>
-      </c>
-      <c r="I7">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3050,28 +3212,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D8">
-        <v>92.95999999999999</v>
+        <v>110.79</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F8">
-        <v>109.34</v>
+        <v>99.62</v>
       </c>
       <c r="G8">
-        <v>0.538</v>
+        <v>0.458</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="I8">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3079,28 +3241,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D9">
-        <v>126.66</v>
+        <v>110.22</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F9">
-        <v>106.75</v>
+        <v>99.62</v>
       </c>
       <c r="G9">
-        <v>0.462</v>
+        <v>0.458</v>
       </c>
       <c r="H9">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="I9">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3108,28 +3270,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D10">
-        <v>104.94</v>
+        <v>97.39</v>
       </c>
       <c r="E10" t="s">
         <v>14</v>
       </c>
       <c r="F10">
-        <v>108.42</v>
+        <v>99.87</v>
       </c>
       <c r="G10">
-        <v>0.538</v>
+        <v>0.5</v>
       </c>
       <c r="H10">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="I10">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3137,28 +3299,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D11">
-        <v>114.96</v>
+        <v>120.7</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F11">
-        <v>107.65</v>
+        <v>99.87</v>
       </c>
       <c r="G11">
-        <v>0.538</v>
+        <v>0.5</v>
       </c>
       <c r="H11">
         <v>-0.4</v>
       </c>
       <c r="I11">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3166,28 +3328,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D12">
-        <v>104.9</v>
+        <v>93.48</v>
       </c>
       <c r="E12" t="s">
         <v>14</v>
       </c>
       <c r="F12">
-        <v>108.42</v>
+        <v>100.33</v>
       </c>
       <c r="G12">
-        <v>0.538</v>
+        <v>0.5</v>
       </c>
       <c r="H12">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="I12">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3198,25 +3360,25 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D13">
-        <v>148.96</v>
+        <v>119.09</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
       </c>
       <c r="F13">
-        <v>105.03</v>
+        <v>100.33</v>
       </c>
       <c r="G13">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="H13">
         <v>-0.5</v>
       </c>
       <c r="I13">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -3224,28 +3386,28 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D14">
-        <v>118.9</v>
+        <v>109.68</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F14">
-        <v>107.35</v>
+        <v>100.36</v>
       </c>
       <c r="G14">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="H14">
         <v>-0.5</v>
       </c>
       <c r="I14">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -3256,25 +3418,25 @@
         <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D15">
-        <v>119.16</v>
+        <v>102.47</v>
       </c>
       <c r="E15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F15">
-        <v>107.33</v>
+        <v>100.36</v>
       </c>
       <c r="G15">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="H15">
         <v>-0.5</v>
       </c>
       <c r="I15">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -3289,147 +3451,147 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>148.96</v>
+        <v>120.7</v>
       </c>
       <c r="E2">
-        <v>148.96</v>
+        <v>241.4</v>
       </c>
       <c r="F2">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>126.66</v>
+        <v>116.34</v>
       </c>
       <c r="E3">
-        <v>126.66</v>
+        <v>232.68</v>
       </c>
       <c r="F3">
-        <v>94.89999999999999</v>
+        <v>98</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>118.9</v>
+        <v>119.09</v>
       </c>
       <c r="E4">
-        <v>118.9</v>
+        <v>238.18</v>
       </c>
       <c r="F4">
-        <v>84.5</v>
+        <v>86.7</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>119.16</v>
+        <v>110.79</v>
       </c>
       <c r="E5">
-        <v>119.16</v>
+        <v>221.58</v>
       </c>
       <c r="F5">
-        <v>83.39999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3437,202 +3599,202 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D6">
-        <v>112.16</v>
+        <v>110.22</v>
       </c>
       <c r="E6">
-        <v>112.16</v>
+        <v>220.44</v>
       </c>
       <c r="F6">
-        <v>66.7</v>
+        <v>82.69999999999999</v>
       </c>
       <c r="G6">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
-        <v>114.96</v>
+        <v>109.68</v>
       </c>
       <c r="E7">
-        <v>114.96</v>
+        <v>219.36</v>
       </c>
       <c r="F7">
-        <v>54.3</v>
+        <v>56.59999999999999</v>
       </c>
       <c r="G7">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="H7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I7" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D8">
-        <v>102.8</v>
+        <v>102.47</v>
       </c>
       <c r="E8">
-        <v>102.8</v>
+        <v>204.94</v>
       </c>
       <c r="F8">
-        <v>34.2</v>
+        <v>38.7</v>
       </c>
       <c r="G8">
-        <v>0.8</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H8" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I8" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>104.9</v>
+        <v>97.83</v>
       </c>
       <c r="E9">
-        <v>104.9</v>
+        <v>195.66</v>
       </c>
       <c r="F9">
-        <v>23.5</v>
+        <v>26.9</v>
       </c>
       <c r="G9">
-        <v>3.2</v>
+        <v>0.1</v>
       </c>
       <c r="H9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I9" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>104.94</v>
+        <v>97.38999999999999</v>
       </c>
       <c r="E10">
-        <v>104.94</v>
+        <v>194.78</v>
       </c>
       <c r="F10">
-        <v>22.2</v>
+        <v>13.3</v>
       </c>
       <c r="G10">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="H10" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I10" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D11">
-        <v>95.42</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="E11">
-        <v>95.42</v>
+        <v>168.7</v>
       </c>
       <c r="F11">
-        <v>15.9</v>
+        <v>5.2</v>
       </c>
       <c r="G11">
-        <v>3.3</v>
+        <v>7.8</v>
       </c>
       <c r="H11" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I11" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>96.66</v>
+        <v>93.47999999999999</v>
       </c>
       <c r="E12">
-        <v>96.66</v>
+        <v>186.96</v>
       </c>
       <c r="F12">
-        <v>8.6</v>
+        <v>4.9</v>
       </c>
       <c r="G12">
-        <v>8.799999999999999</v>
+        <v>6.800000000000001</v>
       </c>
       <c r="H12" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3640,28 +3802,28 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>94.31999999999999</v>
+        <v>87.91999999999999</v>
       </c>
       <c r="E13">
-        <v>94.31999999999999</v>
+        <v>175.84</v>
       </c>
       <c r="F13">
-        <v>6.9</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="G13">
-        <v>12.3</v>
+        <v>18.5</v>
       </c>
       <c r="H13" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -3669,57 +3831,57 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>92.95999999999999</v>
+        <v>87.97999999999999</v>
       </c>
       <c r="E14">
-        <v>92.95999999999999</v>
+        <v>175.96</v>
       </c>
       <c r="F14">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="G14">
-        <v>13.8</v>
+        <v>19.5</v>
       </c>
       <c r="H14" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I14" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>81.59999999999999</v>
+        <v>78.27</v>
       </c>
       <c r="E15">
-        <v>81.59999999999999</v>
+        <v>156.54</v>
       </c>
       <c r="F15">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G15">
-        <v>54.2</v>
+        <v>42.5</v>
       </c>
       <c r="H15" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I15" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -3734,19 +3896,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3754,19 +3916,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3777,16 +3939,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="s">
         <v>15</v>
       </c>
-      <c r="F3">
-        <v>0</v>
+      <c r="F3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3794,7 +3956,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
         <v>59</v>
@@ -3805,8 +3967,8 @@
       <c r="E4" t="s">
         <v>15</v>
       </c>
-      <c r="F4">
-        <v>0</v>
+      <c r="F4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3814,7 +3976,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
         <v>55</v>
@@ -3823,10 +3985,10 @@
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="F5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3834,19 +3996,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
         <v>56</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" t="s">
         <v>14</v>
       </c>
-      <c r="F6">
-        <v>0</v>
+      <c r="F6" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3854,19 +4016,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="F7" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3874,19 +4036,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="F8" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3894,19 +4056,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="F9" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3914,19 +4076,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D10">
         <v>-2</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="F10" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3934,19 +4096,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D11">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="F11" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3954,19 +4116,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D12">
         <v>-3</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="F12" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3974,10 +4136,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D13">
         <v>-4</v>
@@ -3985,8 +4147,8 @@
       <c r="E13" t="s">
         <v>14</v>
       </c>
-      <c r="F13">
-        <v>0</v>
+      <c r="F13" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -3994,19 +4156,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D14">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="F14" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4014,19 +4176,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D15">
-        <v>-9</v>
+        <v>-15</v>
       </c>
       <c r="E15" t="s">
         <v>14</v>
       </c>
-      <c r="F15">
-        <v>0</v>
+      <c r="F15" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -4036,29 +4198,35 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>107</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -4066,139 +4234,178 @@
         <v>6</v>
       </c>
       <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="C4">
         <v>5</v>
       </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5">
+        <v>-2</v>
+      </c>
+      <c r="C5">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="D5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="B6">
         <v>4</v>
       </c>
       <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8">
         <v>3</v>
       </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8">
+      <c r="C8">
         <v>1</v>
       </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>-8</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B9">
+      <c r="B10">
         <v>-1</v>
       </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10">
+      <c r="C10">
         <v>-2</v>
       </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="D10" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B11">
         <v>-3</v>
       </c>
       <c r="C11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>-2</v>
+      </c>
+      <c r="D11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B12">
+        <v>-9</v>
+      </c>
+      <c r="C12">
         <v>-3</v>
       </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="D12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13">
+        <v>-3</v>
+      </c>
+      <c r="C13">
+        <v>-4</v>
+      </c>
+      <c r="D13" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14">
+        <v>4</v>
+      </c>
+      <c r="C14">
+        <v>-5</v>
+      </c>
+      <c r="D14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B13">
+      <c r="B15">
         <v>-4</v>
       </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14">
-        <v>-8</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15">
-        <v>-9</v>
-      </c>
       <c r="C15">
-        <v>0</v>
+        <v>-15</v>
+      </c>
+      <c r="D15" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/BP- Loudoun 2025 2026.xlsx
+++ b/data/leagues/BP- Loudoun 2025 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="116">
   <si>
     <t>Bears, Jags, Foxes, Oh My!</t>
   </si>
@@ -250,13 +250,13 @@
     <t>10.5-3.3-0.1</t>
   </si>
   <si>
-    <t>9.3-4.7</t>
-  </si>
-  <si>
-    <t>9.3-4.6-0.1</t>
-  </si>
-  <si>
-    <t>8.7-5.1-0.2</t>
+    <t>9.4-4.5-0.1</t>
+  </si>
+  <si>
+    <t>9.2-4.7-0.1</t>
+  </si>
+  <si>
+    <t>8.7-5.2-0.2</t>
   </si>
   <si>
     <t>7.7-6.2-0.1</t>
@@ -265,25 +265,28 @@
     <t>7.1-6.7-0.1</t>
   </si>
   <si>
-    <t>6.8-7.1-0.1</t>
-  </si>
-  <si>
-    <t>5.7-8.2-0.1</t>
-  </si>
-  <si>
-    <t>5.1-8.8-0.1</t>
-  </si>
-  <si>
-    <t>4.9-9.0-0.1</t>
+    <t>6.8-7.0-0.1</t>
+  </si>
+  <si>
+    <t>5.8-8.1-0.1</t>
+  </si>
+  <si>
+    <t>5.0-8.9-0.1</t>
+  </si>
+  <si>
+    <t>4.8-9.1-0.1</t>
   </si>
   <si>
     <t>3.9-9.9-0.1</t>
   </si>
   <si>
+    <t>3.4-10.5-0.1</t>
+  </si>
+  <si>
     <t>3.6-10.3-0.1</t>
   </si>
   <si>
-    <t>3.3-10.6-0.1</t>
+    <t>12-2</t>
   </si>
   <si>
     <t>11-3</t>
@@ -292,13 +295,13 @@
     <t>9-5</t>
   </si>
   <si>
-    <t>10-4</t>
-  </si>
-  <si>
     <t>8-6</t>
   </si>
   <si>
     <t>7-7</t>
+  </si>
+  <si>
+    <t>6-8</t>
   </si>
   <si>
     <t>5-9</t>
@@ -1442,25 +1445,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -2085,28 +2088,28 @@
         <v>13</v>
       </c>
       <c r="B2">
-        <v>52.5</v>
+        <v>51.7</v>
       </c>
       <c r="C2">
-        <v>24.8</v>
+        <v>23</v>
       </c>
       <c r="D2">
-        <v>11.7</v>
+        <v>13.9</v>
       </c>
       <c r="E2">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="F2">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="G2">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="H2">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2127,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>99.8</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2138,28 +2141,28 @@
         <v>22.3</v>
       </c>
       <c r="C3">
-        <v>33.5</v>
+        <v>33.3</v>
       </c>
       <c r="D3">
-        <v>21.6</v>
+        <v>20.8</v>
       </c>
       <c r="E3">
-        <v>10.9</v>
+        <v>11.7</v>
       </c>
       <c r="F3">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="G3">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="H3">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="I3">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J3">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -2177,7 +2180,7 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>98</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2185,43 +2188,43 @@
         <v>1</v>
       </c>
       <c r="B4">
-        <v>11.5</v>
+        <v>12.9</v>
       </c>
       <c r="C4">
-        <v>15.6</v>
+        <v>17.7</v>
       </c>
       <c r="D4">
-        <v>19.4</v>
+        <v>18.3</v>
       </c>
       <c r="E4">
-        <v>16.4</v>
+        <v>15.9</v>
       </c>
       <c r="F4">
-        <v>13.8</v>
+        <v>12.6</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H4">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="I4">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="K4">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="L4">
         <v>0.5</v>
       </c>
       <c r="M4">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -2235,49 +2238,49 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>9.4</v>
+        <v>7.7</v>
       </c>
       <c r="C5">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="D5">
-        <v>19.2</v>
+        <v>18.3</v>
       </c>
       <c r="E5">
-        <v>20.2</v>
+        <v>18.9</v>
       </c>
       <c r="F5">
-        <v>13.6</v>
+        <v>14.5</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>10.7</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I5">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="J5">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="K5">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="L5">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>85.7</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2288,46 +2291,46 @@
         <v>1.7</v>
       </c>
       <c r="C6">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="E6">
-        <v>21.3</v>
+        <v>22.5</v>
       </c>
       <c r="F6">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="G6">
-        <v>17.7</v>
+        <v>16</v>
       </c>
       <c r="H6">
-        <v>10.1</v>
+        <v>8.4</v>
       </c>
       <c r="I6">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="L6">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
         <v>0.1</v>
       </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>82.7</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2335,49 +2338,49 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="C7">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="D7">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="E7">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="F7">
-        <v>15.4</v>
+        <v>16.5</v>
       </c>
       <c r="G7">
-        <v>18.1</v>
+        <v>18.5</v>
       </c>
       <c r="H7">
-        <v>15.5</v>
+        <v>13.6</v>
       </c>
       <c r="I7">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J7">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="K7">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="L7">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="M7">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="N7">
         <v>0.7</v>
       </c>
       <c r="O7">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P7">
-        <v>56.6</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2385,40 +2388,40 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="C8">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="E8">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="F8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="G8">
-        <v>14.1</v>
+        <v>16.3</v>
       </c>
       <c r="H8">
-        <v>18.5</v>
+        <v>17.1</v>
       </c>
       <c r="I8">
-        <v>15.4</v>
+        <v>17.2</v>
       </c>
       <c r="J8">
-        <v>11.6</v>
+        <v>10.8</v>
       </c>
       <c r="K8">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L8">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="M8">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="N8">
         <v>1</v>
@@ -2427,7 +2430,7 @@
         <v>0.7</v>
       </c>
       <c r="P8">
-        <v>38.7</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2438,46 +2441,46 @@
         <v>0.1</v>
       </c>
       <c r="C9">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D9">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="F9">
         <v>7.7</v>
       </c>
       <c r="G9">
-        <v>12.9</v>
+        <v>12.4</v>
       </c>
       <c r="H9">
-        <v>15.1</v>
+        <v>18.4</v>
       </c>
       <c r="I9">
-        <v>22.5</v>
+        <v>21.1</v>
       </c>
       <c r="J9">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="K9">
-        <v>9.800000000000001</v>
+        <v>10.6</v>
       </c>
       <c r="L9">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="M9">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="N9">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="O9">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>26.9</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2485,49 +2488,49 @@
         <v>4</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="C10">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="E10">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="F10">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="G10">
-        <v>6.8</v>
+        <v>7.9</v>
       </c>
       <c r="H10">
-        <v>12.7</v>
+        <v>11</v>
       </c>
       <c r="I10">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="J10">
-        <v>14.8</v>
+        <v>17</v>
       </c>
       <c r="K10">
-        <v>15.2</v>
+        <v>14.6</v>
       </c>
       <c r="L10">
-        <v>12.6</v>
+        <v>11.1</v>
       </c>
       <c r="M10">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
       <c r="N10">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="O10">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="P10">
-        <v>13.3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2544,40 +2547,40 @@
         <v>0.3</v>
       </c>
       <c r="E11">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F11">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G11">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="H11">
-        <v>5.3</v>
+        <v>6.3</v>
       </c>
       <c r="I11">
-        <v>9.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J11">
-        <v>13.6</v>
+        <v>11.8</v>
       </c>
       <c r="K11">
-        <v>15.6</v>
+        <v>14.3</v>
       </c>
       <c r="L11">
-        <v>16.2</v>
+        <v>17.1</v>
       </c>
       <c r="M11">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="N11">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="O11">
-        <v>7.8</v>
+        <v>10.2</v>
       </c>
       <c r="P11">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2591,43 +2594,43 @@
         <v>0</v>
       </c>
       <c r="D12">
+        <v>0.1</v>
+      </c>
+      <c r="E12">
         <v>0.2</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>0.5</v>
       </c>
-      <c r="F12">
-        <v>1.2</v>
-      </c>
       <c r="G12">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="H12">
-        <v>4.8</v>
+        <v>7.1</v>
       </c>
       <c r="I12">
-        <v>10.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J12">
-        <v>16.7</v>
+        <v>13.9</v>
       </c>
       <c r="K12">
-        <v>17.9</v>
+        <v>17.7</v>
       </c>
       <c r="L12">
-        <v>15.1</v>
+        <v>17.1</v>
       </c>
       <c r="M12">
-        <v>13.5</v>
+        <v>14.1</v>
       </c>
       <c r="N12">
-        <v>10.2</v>
+        <v>11.6</v>
       </c>
       <c r="O12">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="P12">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2644,45 +2647,45 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G13">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="H13">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="I13">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="J13">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="K13">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="L13">
-        <v>17.6</v>
+        <v>18.4</v>
       </c>
       <c r="M13">
-        <v>19.4</v>
+        <v>18</v>
       </c>
       <c r="N13">
-        <v>21.4</v>
+        <v>19.5</v>
       </c>
       <c r="O13">
-        <v>18.5</v>
+        <v>18.9</v>
       </c>
       <c r="P13">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2697,42 +2700,42 @@
         <v>0</v>
       </c>
       <c r="F14">
+        <v>0.1</v>
+      </c>
+      <c r="G14">
+        <v>0.1</v>
+      </c>
+      <c r="H14">
+        <v>0.7</v>
+      </c>
+      <c r="I14">
+        <v>1.8</v>
+      </c>
+      <c r="J14">
+        <v>2.9</v>
+      </c>
+      <c r="K14">
+        <v>7.2</v>
+      </c>
+      <c r="L14">
+        <v>7.4</v>
+      </c>
+      <c r="M14">
+        <v>19.3</v>
+      </c>
+      <c r="N14">
+        <v>22.6</v>
+      </c>
+      <c r="O14">
+        <v>37.9</v>
+      </c>
+      <c r="P14">
         <v>0.2</v>
-      </c>
-      <c r="G14">
-        <v>0.3</v>
-      </c>
-      <c r="H14">
-        <v>0.9</v>
-      </c>
-      <c r="I14">
-        <v>1.7</v>
-      </c>
-      <c r="J14">
-        <v>4.8</v>
-      </c>
-      <c r="K14">
-        <v>10.1</v>
-      </c>
-      <c r="L14">
-        <v>15</v>
-      </c>
-      <c r="M14">
-        <v>22.1</v>
-      </c>
-      <c r="N14">
-        <v>25.4</v>
-      </c>
-      <c r="O14">
-        <v>19.5</v>
-      </c>
-      <c r="P14">
-        <v>0.5</v>
       </c>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2744,37 +2747,37 @@
         <v>0</v>
       </c>
       <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
         <v>0.1</v>
       </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
       <c r="H15">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="I15">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J15">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="K15">
-        <v>5.2</v>
+        <v>10.1</v>
       </c>
       <c r="L15">
-        <v>9.9</v>
+        <v>15.4</v>
       </c>
       <c r="M15">
-        <v>13.9</v>
+        <v>21.1</v>
       </c>
       <c r="N15">
-        <v>22.6</v>
+        <v>24.3</v>
       </c>
       <c r="O15">
-        <v>42.5</v>
+        <v>22</v>
       </c>
       <c r="P15">
         <v>0.1</v>
@@ -2806,13 +2809,13 @@
         <v>13</v>
       </c>
       <c r="B2">
-        <v>95.5</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="C2">
-        <v>99.59999999999999</v>
+        <v>99.5</v>
       </c>
       <c r="D2">
-        <v>100</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2820,13 +2823,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>84.89999999999999</v>
+        <v>82.69999999999999</v>
       </c>
       <c r="C3">
-        <v>99.09999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="D3">
-        <v>98</v>
+        <v>98.59999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2834,13 +2837,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>18.8</v>
+        <v>19.8</v>
       </c>
       <c r="C4">
-        <v>82.39999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D4">
-        <v>87</v>
+        <v>85.39999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2851,10 +2854,10 @@
         <v>99.90000000000001</v>
       </c>
       <c r="C5">
-        <v>87.09999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="D5">
-        <v>86.90000000000001</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2862,13 +2865,13 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>70.89999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="C6">
-        <v>79.7</v>
+        <v>79.60000000000001</v>
       </c>
       <c r="D6">
-        <v>81</v>
+        <v>81.89999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2879,10 +2882,10 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="C7">
-        <v>54.90000000000001</v>
+        <v>56.39999999999999</v>
       </c>
       <c r="D7">
-        <v>54.8</v>
+        <v>55.7</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2890,13 +2893,13 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>83.89999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="C8">
-        <v>38</v>
+        <v>40.6</v>
       </c>
       <c r="D8">
-        <v>39.3</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2904,13 +2907,13 @@
         <v>11</v>
       </c>
       <c r="B9">
-        <v>35.09999999999999</v>
+        <v>35.5</v>
       </c>
       <c r="C9">
-        <v>34.2</v>
+        <v>32.8</v>
       </c>
       <c r="D9">
-        <v>28.9</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2918,13 +2921,13 @@
         <v>4</v>
       </c>
       <c r="B10">
-        <v>53</v>
+        <v>53.2</v>
       </c>
       <c r="C10">
-        <v>13.7</v>
+        <v>11.6</v>
       </c>
       <c r="D10">
-        <v>12.8</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2932,13 +2935,13 @@
         <v>7</v>
       </c>
       <c r="B11">
-        <v>19.8</v>
+        <v>20.5</v>
       </c>
       <c r="C11">
-        <v>5.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="D11">
-        <v>6.600000000000001</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2946,13 +2949,13 @@
         <v>0</v>
       </c>
       <c r="B12">
-        <v>21.2</v>
+        <v>19.7</v>
       </c>
       <c r="C12">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D12">
-        <v>3.9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2960,41 +2963,41 @@
         <v>6</v>
       </c>
       <c r="B13">
-        <v>5.800000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="C13">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="D13">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B14">
-        <v>7.3</v>
+        <v>3.3</v>
       </c>
       <c r="C14">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="D14">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B15">
-        <v>3.2</v>
+        <v>7.8</v>
       </c>
       <c r="C15">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="D15">
         <v>0.3</v>
-      </c>
-      <c r="D15">
-        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -3495,7 +3498,7 @@
         <v>241.4</v>
       </c>
       <c r="F2">
-        <v>99.8</v>
+        <v>99.5</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -3524,7 +3527,7 @@
         <v>232.68</v>
       </c>
       <c r="F3">
-        <v>98</v>
+        <v>98.2</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -3533,7 +3536,7 @@
         <v>74</v>
       </c>
       <c r="I3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3562,7 +3565,7 @@
         <v>75</v>
       </c>
       <c r="I4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3582,7 +3585,7 @@
         <v>221.58</v>
       </c>
       <c r="F5">
-        <v>85.7</v>
+        <v>83.3</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -3611,7 +3614,7 @@
         <v>220.44</v>
       </c>
       <c r="F6">
-        <v>82.69999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -3620,7 +3623,7 @@
         <v>77</v>
       </c>
       <c r="I6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3640,10 +3643,10 @@
         <v>219.36</v>
       </c>
       <c r="F7">
-        <v>56.59999999999999</v>
+        <v>60</v>
       </c>
       <c r="G7">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H7" t="s">
         <v>78</v>
@@ -3669,7 +3672,7 @@
         <v>204.94</v>
       </c>
       <c r="F8">
-        <v>38.7</v>
+        <v>39.90000000000001</v>
       </c>
       <c r="G8">
         <v>0.7000000000000001</v>
@@ -3698,10 +3701,10 @@
         <v>195.66</v>
       </c>
       <c r="F9">
-        <v>26.9</v>
+        <v>26.4</v>
       </c>
       <c r="G9">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="s">
         <v>80</v>
@@ -3727,10 +3730,10 @@
         <v>194.78</v>
       </c>
       <c r="F10">
-        <v>13.3</v>
+        <v>15</v>
       </c>
       <c r="G10">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="H10" t="s">
         <v>81</v>
@@ -3756,16 +3759,16 @@
         <v>168.7</v>
       </c>
       <c r="F11">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="G11">
-        <v>7.8</v>
+        <v>10.2</v>
       </c>
       <c r="H11" t="s">
         <v>82</v>
       </c>
       <c r="I11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3785,16 +3788,16 @@
         <v>186.96</v>
       </c>
       <c r="F12">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="G12">
-        <v>6.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="H12" t="s">
         <v>83</v>
       </c>
       <c r="I12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3814,21 +3817,21 @@
         <v>175.84</v>
       </c>
       <c r="F13">
-        <v>0.8999999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="G13">
-        <v>18.5</v>
+        <v>18.9</v>
       </c>
       <c r="H13" t="s">
         <v>84</v>
       </c>
       <c r="I13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B14" t="s">
         <v>72</v>
@@ -3837,27 +3840,27 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>87.97999999999999</v>
+        <v>78.27</v>
       </c>
       <c r="E14">
-        <v>175.96</v>
+        <v>156.54</v>
       </c>
       <c r="F14">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="G14">
-        <v>19.5</v>
+        <v>37.9</v>
       </c>
       <c r="H14" t="s">
         <v>85</v>
       </c>
       <c r="I14" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B15" t="s">
         <v>72</v>
@@ -3866,22 +3869,22 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>78.27</v>
+        <v>87.97999999999999</v>
       </c>
       <c r="E15">
-        <v>156.54</v>
+        <v>175.96</v>
       </c>
       <c r="F15">
         <v>0.1</v>
       </c>
       <c r="G15">
-        <v>42.5</v>
+        <v>22</v>
       </c>
       <c r="H15" t="s">
         <v>86</v>
       </c>
       <c r="I15" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -3899,16 +3902,16 @@
         <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3928,7 +3931,7 @@
         <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3948,7 +3951,7 @@
         <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3968,7 +3971,7 @@
         <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3988,7 +3991,7 @@
         <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4008,7 +4011,7 @@
         <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4028,7 +4031,7 @@
         <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4048,7 +4051,7 @@
         <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4068,7 +4071,7 @@
         <v>15</v>
       </c>
       <c r="F9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4088,7 +4091,7 @@
         <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4108,7 +4111,7 @@
         <v>15</v>
       </c>
       <c r="F11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4128,7 +4131,7 @@
         <v>16</v>
       </c>
       <c r="F12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4148,7 +4151,7 @@
         <v>14</v>
       </c>
       <c r="F13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4168,7 +4171,7 @@
         <v>16</v>
       </c>
       <c r="F14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4188,7 +4191,7 @@
         <v>14</v>
       </c>
       <c r="F15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -4203,13 +4206,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -4223,7 +4226,7 @@
         <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -4237,7 +4240,7 @@
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -4251,7 +4254,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -4265,7 +4268,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -4279,7 +4282,7 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -4293,7 +4296,7 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -4307,7 +4310,7 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4321,7 +4324,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -4335,7 +4338,7 @@
         <v>-2</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -4349,7 +4352,7 @@
         <v>-2</v>
       </c>
       <c r="D11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -4363,7 +4366,7 @@
         <v>-3</v>
       </c>
       <c r="D12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -4377,7 +4380,7 @@
         <v>-4</v>
       </c>
       <c r="D13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -4391,7 +4394,7 @@
         <v>-5</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -4405,7 +4408,7 @@
         <v>-15</v>
       </c>
       <c r="D15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/BP- Loudoun 2025 2026.xlsx
+++ b/data/leagues/BP- Loudoun 2025 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="121">
   <si>
     <t>Bears, Jags, Foxes, Oh My!</t>
   </si>
@@ -67,13 +67,16 @@
     <t>Dave's Dynamos</t>
   </si>
   <si>
-    <t>0-2-0</t>
-  </si>
-  <si>
-    <t>2-0-0</t>
-  </si>
-  <si>
-    <t>1-1-0</t>
+    <t>0-3-0</t>
+  </si>
+  <si>
+    <t>2-1-0</t>
+  </si>
+  <si>
+    <t>1-2-0</t>
+  </si>
+  <si>
+    <t>3-0-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -148,6 +151,9 @@
     <t>Week_3</t>
   </si>
   <si>
+    <t>Week_4</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -178,39 +184,39 @@
     <t>Chungfu Yang</t>
   </si>
   <si>
+    <t>Justin Fox</t>
+  </si>
+  <si>
+    <t>Dale Goodwin</t>
+  </si>
+  <si>
+    <t>Dave Linton</t>
+  </si>
+  <si>
+    <t>Matthew Graesser</t>
+  </si>
+  <si>
     <t>MARVIN AYALA</t>
   </si>
   <si>
-    <t>Matthew Graesser</t>
-  </si>
-  <si>
-    <t>Dale Goodwin</t>
+    <t>Hannah Davis</t>
+  </si>
+  <si>
+    <t>Jeffrey Laidacker</t>
+  </si>
+  <si>
+    <t>Jessica Stratton</t>
   </si>
   <si>
     <t>Daniel Tracey</t>
   </si>
   <si>
-    <t>Jeffrey Laidacker</t>
-  </si>
-  <si>
-    <t>Hannah Davis</t>
-  </si>
-  <si>
-    <t>Dave Linton</t>
-  </si>
-  <si>
-    <t>Justin Fox</t>
-  </si>
-  <si>
-    <t>Jessica Stratton</t>
+    <t>Yahya Ayaz</t>
   </si>
   <si>
     <t>Robert Schottler</t>
   </si>
   <si>
-    <t>Yahya Ayaz</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -235,75 +241,72 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>2-0</t>
-  </si>
-  <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>0-2</t>
-  </si>
-  <si>
-    <t>11.2-2.7-0.1</t>
-  </si>
-  <si>
-    <t>10.5-3.3-0.1</t>
-  </si>
-  <si>
-    <t>9.4-4.5-0.1</t>
-  </si>
-  <si>
-    <t>9.2-4.7-0.1</t>
-  </si>
-  <si>
-    <t>8.7-5.2-0.2</t>
-  </si>
-  <si>
-    <t>7.7-6.2-0.1</t>
-  </si>
-  <si>
-    <t>7.1-6.7-0.1</t>
-  </si>
-  <si>
-    <t>6.8-7.0-0.1</t>
-  </si>
-  <si>
-    <t>5.8-8.1-0.1</t>
-  </si>
-  <si>
-    <t>5.0-8.9-0.1</t>
-  </si>
-  <si>
-    <t>4.8-9.1-0.1</t>
+    <t>3-0</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>0-3</t>
+  </si>
+  <si>
+    <t>10.7-3.2-0.2</t>
+  </si>
+  <si>
+    <t>9.9-3.9-0.1</t>
+  </si>
+  <si>
+    <t>9.7-4.1-0.2</t>
+  </si>
+  <si>
+    <t>9.1-4.8-0.2</t>
+  </si>
+  <si>
+    <t>9.2-4.6-0.2</t>
+  </si>
+  <si>
+    <t>8.7-5.2-0.1</t>
+  </si>
+  <si>
+    <t>8.5-5.3-0.2</t>
+  </si>
+  <si>
+    <t>8.1-5.8-0.1</t>
+  </si>
+  <si>
+    <t>4.7-9.2-0.1</t>
+  </si>
+  <si>
+    <t>4.8-9.1-0.2</t>
+  </si>
+  <si>
+    <t>4.1-9.8-0.1</t>
+  </si>
+  <si>
+    <t>3.4-10.5-0.1</t>
   </si>
   <si>
     <t>3.9-9.9-0.1</t>
   </si>
   <si>
-    <t>3.4-10.5-0.1</t>
-  </si>
-  <si>
-    <t>3.6-10.3-0.1</t>
-  </si>
-  <si>
-    <t>12-2</t>
+    <t>2.2-11.7-0.1</t>
   </si>
   <si>
     <t>11-3</t>
   </si>
   <si>
+    <t>10-4</t>
+  </si>
+  <si>
     <t>9-5</t>
   </si>
   <si>
     <t>8-6</t>
   </si>
   <si>
-    <t>7-7</t>
-  </si>
-  <si>
-    <t>6-8</t>
-  </si>
-  <si>
     <t>5-9</t>
   </si>
   <si>
@@ -313,6 +316,9 @@
     <t>3-11</t>
   </si>
   <si>
+    <t>2-12</t>
+  </si>
+  <si>
     <t>Owners</t>
   </si>
   <si>
@@ -322,34 +328,43 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↑2</t>
+  </si>
+  <si>
+    <t>↑7</t>
+  </si>
+  <si>
+    <t>↓1</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>↑4</t>
   </si>
   <si>
+    <t>↑5</t>
+  </si>
+  <si>
     <t>↑1</t>
   </si>
   <si>
-    <t>↓1</t>
-  </si>
-  <si>
-    <t>↑6</t>
-  </si>
-  <si>
-    <t>↓2</t>
-  </si>
-  <si>
-    <t>↑8</t>
-  </si>
-  <si>
-    <t>↓9</t>
-  </si>
-  <si>
-    <t>↓11</t>
+    <t>↓4</t>
+  </si>
+  <si>
+    <t>↓5</t>
+  </si>
+  <si>
+    <t>↓7</t>
   </si>
   <si>
     <t>Week 1</t>
   </si>
   <si>
     <t>Week 2</t>
+  </si>
+  <si>
+    <t>Week 3</t>
   </si>
   <si>
     <t>Week</t>
@@ -804,22 +819,22 @@
         <v>16</v>
       </c>
       <c r="J2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L2" t="s">
         <v>15</v>
       </c>
       <c r="M2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N2" t="s">
         <v>16</v>
       </c>
       <c r="O2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -854,7 +869,7 @@
         <v>16</v>
       </c>
       <c r="K3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L3" t="s">
         <v>15</v>
@@ -866,7 +881,7 @@
         <v>16</v>
       </c>
       <c r="O3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -895,25 +910,25 @@
         <v>15</v>
       </c>
       <c r="I4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N4" t="s">
         <v>16</v>
       </c>
       <c r="O4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -927,10 +942,10 @@
         <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
@@ -942,25 +957,25 @@
         <v>16</v>
       </c>
       <c r="I5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N5" t="s">
         <v>15</v>
       </c>
       <c r="O5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -992,10 +1007,10 @@
         <v>16</v>
       </c>
       <c r="J6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L6" t="s">
         <v>15</v>
@@ -1007,7 +1022,7 @@
         <v>16</v>
       </c>
       <c r="O6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -1021,10 +1036,10 @@
         <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
@@ -1033,28 +1048,28 @@
         <v>16</v>
       </c>
       <c r="H7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N7" t="s">
         <v>16</v>
       </c>
       <c r="O7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -1148,7 +1163,7 @@
         <v>16</v>
       </c>
       <c r="O9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -1156,46 +1171,46 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F10" t="s">
         <v>16</v>
       </c>
       <c r="G10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1224,25 +1239,25 @@
         <v>14</v>
       </c>
       <c r="I11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N11" t="s">
         <v>14</v>
       </c>
       <c r="O11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -1250,16 +1265,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F12" t="s">
         <v>14</v>
@@ -1268,28 +1283,28 @@
         <v>16</v>
       </c>
       <c r="H12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -1297,46 +1312,46 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -1344,46 +1359,46 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F14" t="s">
         <v>14</v>
       </c>
       <c r="G14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:15">
@@ -1397,10 +1412,10 @@
         <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F15" t="s">
         <v>15</v>
@@ -1409,28 +1424,28 @@
         <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N15" t="s">
         <v>16</v>
       </c>
       <c r="O15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1440,30 +1455,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1471,25 +1486,25 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E2">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>-14</v>
       </c>
       <c r="G2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1500,22 +1515,22 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>-3</v>
+      </c>
+      <c r="F3">
+        <v>9</v>
+      </c>
+      <c r="G3">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
       <c r="H3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1523,24 +1538,102 @@
         <v>2</v>
       </c>
       <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
         <v>2</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>6</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+      <c r="H4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
         <v>13</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D7" t="s">
         <v>4</v>
       </c>
-      <c r="E4">
+      <c r="E7">
         <v>2</v>
       </c>
-      <c r="F4">
+      <c r="F7">
         <v>3</v>
       </c>
-      <c r="G4">
+      <c r="G7">
         <v>1</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H7" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1556,13 +1649,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1573,7 +1666,7 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -1584,13 +1677,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1598,10 +1691,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>0.5714285714285714</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -1612,13 +1705,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>0.7142857142857143</v>
+        <v>1.214285714285714</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1626,13 +1719,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>0.7142857142857143</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1640,13 +1733,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C7">
-        <v>0.9285714285714286</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1654,13 +1747,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1668,13 +1761,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1682,13 +1775,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C10">
-        <v>1.142857142857143</v>
+        <v>1.5</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1696,13 +1789,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C11">
-        <v>1.214285714285714</v>
+        <v>1.642857142857143</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1710,13 +1803,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C12">
-        <v>1.214285714285714</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1724,13 +1817,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C13">
-        <v>1.285714285714286</v>
+        <v>1.928571428571429</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1741,10 +1834,10 @@
         <v>10</v>
       </c>
       <c r="C14">
-        <v>1.571428571428571</v>
+        <v>2.214285714285714</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1755,10 +1848,10 @@
         <v>13</v>
       </c>
       <c r="C15">
-        <v>1.642857142857143</v>
+        <v>2.571428571428572</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1773,16 +1866,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1793,13 +1886,13 @@
         <v>13</v>
       </c>
       <c r="C2">
-        <v>1.785714285714286</v>
+        <v>2.428571428571428</v>
       </c>
       <c r="D2">
-        <v>-0.2142857142857142</v>
+        <v>-0.5714285714285716</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1807,13 +1900,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>1.571428571428571</v>
+        <v>2.214285714285714</v>
       </c>
       <c r="D3">
-        <v>-0.4285714285714286</v>
+        <v>0.2142857142857144</v>
       </c>
       <c r="E3" t="s">
         <v>15</v>
@@ -1824,13 +1917,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C4">
-        <v>1.571428571428571</v>
+        <v>2.142857142857143</v>
       </c>
       <c r="D4">
-        <v>-0.4285714285714286</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="E4" t="s">
         <v>15</v>
@@ -1841,16 +1934,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>1.285714285714286</v>
+        <v>2.071428571428572</v>
       </c>
       <c r="D5">
-        <v>0.2857142857142858</v>
+        <v>-0.9285714285714284</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1858,16 +1951,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>1.285714285714286</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>0.2857142857142858</v>
+        <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1878,13 +1971,13 @@
         <v>3</v>
       </c>
       <c r="C7">
-        <v>1.214285714285714</v>
+        <v>1.785714285714286</v>
       </c>
       <c r="D7">
-        <v>-0.7857142857142858</v>
+        <v>-1.214285714285714</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1892,13 +1985,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>1.071428571428571</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="D8">
-        <v>-0.9285714285714286</v>
+        <v>-0.2857142857142858</v>
       </c>
       <c r="E8" t="s">
         <v>15</v>
@@ -1912,10 +2005,10 @@
         <v>5</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>1.642857142857143</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>0.6428571428571428</v>
       </c>
       <c r="E9" t="s">
         <v>16</v>
@@ -1926,16 +2019,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C10">
-        <v>0.7857142857142857</v>
+        <v>1.071428571428571</v>
       </c>
       <c r="D10">
-        <v>0.7857142857142857</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1943,13 +2036,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>0.7857142857142857</v>
+        <v>1.071428571428571</v>
       </c>
       <c r="D11">
-        <v>0.7857142857142857</v>
+        <v>1.071428571428571</v>
       </c>
       <c r="E11" t="s">
         <v>14</v>
@@ -1960,16 +2053,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C12">
-        <v>0.5714285714285714</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>-0.4285714285714286</v>
+        <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1980,13 +2073,13 @@
         <v>9</v>
       </c>
       <c r="C13">
-        <v>0.4285714285714285</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D13">
-        <v>0.4285714285714285</v>
+        <v>-0.1428571428571429</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1994,16 +2087,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14">
-        <v>0.3571428571428572</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="D14">
-        <v>0.3571428571428572</v>
+        <v>-0.3571428571428571</v>
       </c>
       <c r="E14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2011,13 +2104,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C15">
-        <v>0.2857142857142857</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="D15">
-        <v>0.2857142857142857</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="E15" t="s">
         <v>14</v>
@@ -2035,52 +2128,52 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -2088,31 +2181,31 @@
         <v>13</v>
       </c>
       <c r="B2">
-        <v>51.7</v>
+        <v>43.1</v>
       </c>
       <c r="C2">
-        <v>23</v>
+        <v>19.8</v>
       </c>
       <c r="D2">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="E2">
-        <v>6.8</v>
+        <v>10.8</v>
       </c>
       <c r="F2">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="G2">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="I2">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -2130,42 +2223,42 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>99.5</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B3">
-        <v>22.3</v>
+        <v>18.2</v>
       </c>
       <c r="C3">
-        <v>33.3</v>
+        <v>22.6</v>
       </c>
       <c r="D3">
-        <v>20.8</v>
+        <v>17.7</v>
       </c>
       <c r="E3">
-        <v>11.7</v>
+        <v>15.6</v>
       </c>
       <c r="F3">
-        <v>6.7</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>3.4</v>
+        <v>8.5</v>
       </c>
       <c r="H3">
-        <v>0.9</v>
+        <v>5.5</v>
       </c>
       <c r="I3">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J3">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -2180,98 +2273,98 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>98.2</v>
+        <v>92.59999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <v>12.9</v>
       </c>
       <c r="C4">
-        <v>17.7</v>
+        <v>14.9</v>
       </c>
       <c r="D4">
-        <v>18.3</v>
+        <v>14.7</v>
       </c>
       <c r="E4">
-        <v>15.9</v>
+        <v>15.1</v>
       </c>
       <c r="F4">
-        <v>12.6</v>
+        <v>13.1</v>
       </c>
       <c r="G4">
-        <v>9.300000000000001</v>
+        <v>11.7</v>
       </c>
       <c r="H4">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>7.6</v>
       </c>
       <c r="J4">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="K4">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="L4">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>86.7</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>13.2</v>
+        <v>10.8</v>
       </c>
       <c r="D5">
-        <v>18.3</v>
+        <v>14.7</v>
       </c>
       <c r="E5">
-        <v>18.9</v>
+        <v>11.6</v>
       </c>
       <c r="F5">
-        <v>14.5</v>
+        <v>16.2</v>
       </c>
       <c r="G5">
-        <v>10.7</v>
+        <v>15.2</v>
       </c>
       <c r="H5">
-        <v>8.800000000000001</v>
+        <v>11.9</v>
       </c>
       <c r="I5">
-        <v>4.3</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="K5">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="L5">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -2280,42 +2373,42 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>83.3</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6">
-        <v>1.7</v>
+        <v>7.5</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>13.1</v>
       </c>
       <c r="D6">
-        <v>14.5</v>
+        <v>11.1</v>
       </c>
       <c r="E6">
-        <v>22.5</v>
+        <v>12.1</v>
       </c>
       <c r="F6">
-        <v>21.6</v>
+        <v>16.8</v>
       </c>
       <c r="G6">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>14.3</v>
       </c>
       <c r="I6">
-        <v>5.3</v>
+        <v>9.6</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="K6">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -2324,268 +2417,268 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>82.3</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B7">
-        <v>2.8</v>
+        <v>5.2</v>
       </c>
       <c r="C7">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="D7">
-        <v>7.1</v>
+        <v>10.3</v>
       </c>
       <c r="E7">
-        <v>10.2</v>
+        <v>13.5</v>
       </c>
       <c r="F7">
-        <v>16.5</v>
+        <v>12.2</v>
       </c>
       <c r="G7">
-        <v>18.5</v>
+        <v>14.9</v>
       </c>
       <c r="H7">
-        <v>13.6</v>
+        <v>17</v>
       </c>
       <c r="I7">
-        <v>9.300000000000001</v>
+        <v>13.7</v>
       </c>
       <c r="J7">
-        <v>7.7</v>
+        <v>3.3</v>
       </c>
       <c r="K7">
-        <v>4.9</v>
+        <v>1.3</v>
       </c>
       <c r="L7">
-        <v>2.8</v>
+        <v>0.2</v>
       </c>
       <c r="M7">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>60</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B8">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>5.4</v>
       </c>
       <c r="D8">
-        <v>4.5</v>
+        <v>10.8</v>
       </c>
       <c r="E8">
-        <v>7</v>
+        <v>12.1</v>
       </c>
       <c r="F8">
-        <v>10.5</v>
+        <v>13.6</v>
       </c>
       <c r="G8">
-        <v>16.3</v>
+        <v>15.7</v>
       </c>
       <c r="H8">
-        <v>17.1</v>
+        <v>15.5</v>
       </c>
       <c r="I8">
-        <v>17.2</v>
+        <v>17.5</v>
       </c>
       <c r="J8">
-        <v>10.8</v>
+        <v>4.2</v>
       </c>
       <c r="K8">
-        <v>6.4</v>
+        <v>1.1</v>
       </c>
       <c r="L8">
-        <v>5.3</v>
+        <v>0.3</v>
       </c>
       <c r="M8">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="N8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>39.9</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B9">
-        <v>0.1</v>
+        <v>2.4</v>
       </c>
       <c r="C9">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="D9">
-        <v>1.6</v>
+        <v>6.8</v>
       </c>
       <c r="E9">
-        <v>4.2</v>
+        <v>9.1</v>
       </c>
       <c r="F9">
-        <v>7.7</v>
+        <v>12.3</v>
       </c>
       <c r="G9">
-        <v>12.4</v>
+        <v>14.9</v>
       </c>
       <c r="H9">
-        <v>18.4</v>
+        <v>20.6</v>
       </c>
       <c r="I9">
-        <v>21.1</v>
+        <v>20.5</v>
       </c>
       <c r="J9">
-        <v>16</v>
+        <v>5.5</v>
       </c>
       <c r="K9">
-        <v>10.6</v>
+        <v>1.8</v>
       </c>
       <c r="L9">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="M9">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="N9">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>26.4</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
         <v>0.2</v>
       </c>
-      <c r="C10">
-        <v>0.4</v>
-      </c>
-      <c r="D10">
-        <v>0.6</v>
-      </c>
       <c r="E10">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>0.2</v>
       </c>
       <c r="G10">
-        <v>7.9</v>
+        <v>0.9</v>
       </c>
       <c r="H10">
-        <v>11</v>
+        <v>1.7</v>
       </c>
       <c r="I10">
-        <v>13.8</v>
+        <v>5.5</v>
       </c>
       <c r="J10">
-        <v>17</v>
+        <v>22.5</v>
       </c>
       <c r="K10">
+        <v>23.1</v>
+      </c>
+      <c r="L10">
+        <v>18.6</v>
+      </c>
+      <c r="M10">
         <v>14.6</v>
       </c>
-      <c r="L10">
-        <v>11.1</v>
-      </c>
-      <c r="M10">
-        <v>7.4</v>
-      </c>
       <c r="N10">
-        <v>7.2</v>
+        <v>9.5</v>
       </c>
       <c r="O10">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P10">
-        <v>15</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
         <v>0.1</v>
       </c>
-      <c r="D11">
-        <v>0.3</v>
-      </c>
-      <c r="E11">
-        <v>0.7</v>
-      </c>
-      <c r="F11">
-        <v>1.4</v>
-      </c>
       <c r="G11">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="H11">
-        <v>6.3</v>
+        <v>1.6</v>
       </c>
       <c r="I11">
-        <v>8.300000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="J11">
-        <v>11.8</v>
+        <v>29.1</v>
       </c>
       <c r="K11">
-        <v>14.3</v>
+        <v>24.5</v>
       </c>
       <c r="L11">
-        <v>17.1</v>
+        <v>16</v>
       </c>
       <c r="M11">
-        <v>15</v>
+        <v>11.7</v>
       </c>
       <c r="N11">
-        <v>12.1</v>
+        <v>7.6</v>
       </c>
       <c r="O11">
-        <v>10.2</v>
+        <v>2</v>
       </c>
       <c r="P11">
-        <v>4.9</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2594,48 +2687,48 @@
         <v>0</v>
       </c>
       <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
         <v>0.1</v>
       </c>
-      <c r="E12">
+      <c r="G12">
+        <v>0.1</v>
+      </c>
+      <c r="H12">
+        <v>0.8</v>
+      </c>
+      <c r="I12">
+        <v>3.4</v>
+      </c>
+      <c r="J12">
+        <v>11.1</v>
+      </c>
+      <c r="K12">
+        <v>17.5</v>
+      </c>
+      <c r="L12">
+        <v>23.4</v>
+      </c>
+      <c r="M12">
+        <v>23</v>
+      </c>
+      <c r="N12">
+        <v>14.2</v>
+      </c>
+      <c r="O12">
+        <v>6.4</v>
+      </c>
+      <c r="P12">
         <v>0.2</v>
-      </c>
-      <c r="F12">
-        <v>0.5</v>
-      </c>
-      <c r="G12">
-        <v>1.6</v>
-      </c>
-      <c r="H12">
-        <v>7.1</v>
-      </c>
-      <c r="I12">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="J12">
-        <v>13.9</v>
-      </c>
-      <c r="K12">
-        <v>17.7</v>
-      </c>
-      <c r="L12">
-        <v>17.1</v>
-      </c>
-      <c r="M12">
-        <v>14.1</v>
-      </c>
-      <c r="N12">
-        <v>11.6</v>
-      </c>
-      <c r="O12">
-        <v>7.3</v>
-      </c>
-      <c r="P12">
-        <v>2.4</v>
       </c>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2650,42 +2743,42 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="H13">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="I13">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J13">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="K13">
-        <v>11.8</v>
+        <v>8.6</v>
       </c>
       <c r="L13">
-        <v>18.4</v>
+        <v>12.9</v>
       </c>
       <c r="M13">
-        <v>18</v>
+        <v>22.9</v>
       </c>
       <c r="N13">
-        <v>19.5</v>
+        <v>32.6</v>
       </c>
       <c r="O13">
-        <v>18.9</v>
+        <v>17.5</v>
       </c>
       <c r="P13">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2700,42 +2793,42 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="I14">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J14">
-        <v>2.9</v>
+        <v>13.3</v>
       </c>
       <c r="K14">
-        <v>7.2</v>
+        <v>19.2</v>
       </c>
       <c r="L14">
-        <v>7.4</v>
+        <v>23.4</v>
       </c>
       <c r="M14">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="N14">
-        <v>22.6</v>
+        <v>15</v>
       </c>
       <c r="O14">
-        <v>37.9</v>
+        <v>7.1</v>
       </c>
       <c r="P14">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2753,34 +2846,34 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="K15">
-        <v>10.1</v>
+        <v>1.7</v>
       </c>
       <c r="L15">
-        <v>15.4</v>
+        <v>4.3</v>
       </c>
       <c r="M15">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="N15">
         <v>21.1</v>
       </c>
-      <c r="N15">
-        <v>24.3</v>
-      </c>
       <c r="O15">
-        <v>22</v>
+        <v>63.9</v>
       </c>
       <c r="P15">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2790,214 +2883,259 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>41</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B2">
-        <v>94.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="C2">
-        <v>99.5</v>
+        <v>99.3</v>
       </c>
       <c r="D2">
-        <v>99.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>97.5</v>
+      </c>
+      <c r="E2">
+        <v>95.89999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B3">
-        <v>82.69999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="C3">
-        <v>98.90000000000001</v>
+        <v>79.80000000000001</v>
       </c>
       <c r="D3">
-        <v>98.59999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>91.60000000000001</v>
+      </c>
+      <c r="E3">
+        <v>92.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>19.8</v>
+        <v>6.800000000000001</v>
       </c>
       <c r="C4">
-        <v>83.59999999999999</v>
+        <v>90</v>
       </c>
       <c r="D4">
-        <v>85.39999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>82.39999999999999</v>
+      </c>
+      <c r="E4">
+        <v>78.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>27.4</v>
+      </c>
+      <c r="C5">
+        <v>28.6</v>
+      </c>
+      <c r="D5">
+        <v>77.10000000000001</v>
+      </c>
+      <c r="E5">
+        <v>77.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>95.5</v>
+      </c>
+      <c r="C6">
+        <v>34</v>
+      </c>
+      <c r="D6">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="E6">
+        <v>76.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B5">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="C5">
-        <v>86.3</v>
-      </c>
-      <c r="D5">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="C6">
-        <v>79.60000000000001</v>
-      </c>
-      <c r="D6">
-        <v>81.89999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+      <c r="B7">
+        <v>100</v>
+      </c>
+      <c r="C7">
+        <v>96.8</v>
+      </c>
+      <c r="D7">
+        <v>61.4</v>
+      </c>
+      <c r="E7">
+        <v>64.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="C8">
+        <v>97.39999999999999</v>
+      </c>
+      <c r="D8">
+        <v>62</v>
+      </c>
+      <c r="E8">
+        <v>58.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7">
-        <v>0.7000000000000001</v>
-      </c>
-      <c r="C7">
-        <v>56.39999999999999</v>
-      </c>
-      <c r="D7">
-        <v>55.7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>85.90000000000001</v>
-      </c>
-      <c r="C8">
-        <v>40.6</v>
-      </c>
-      <c r="D8">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="B9">
-        <v>35.5</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>32.8</v>
+        <v>67.80000000000001</v>
       </c>
       <c r="D9">
-        <v>30.3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>48.9</v>
+      </c>
+      <c r="E9">
+        <v>53.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>1.4</v>
+      </c>
+      <c r="E10">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10">
-        <v>53.2</v>
-      </c>
-      <c r="C10">
-        <v>11.6</v>
-      </c>
-      <c r="D10">
-        <v>14.2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
+      <c r="B11">
+        <v>68.60000000000001</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11">
+        <v>1.6</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12">
+        <v>14.7</v>
+      </c>
+      <c r="C12">
+        <v>1.5</v>
+      </c>
+      <c r="D12">
+        <v>0.6</v>
+      </c>
+      <c r="E12">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13">
+        <v>0.2</v>
+      </c>
+      <c r="C13">
+        <v>0.2</v>
+      </c>
+      <c r="D13">
+        <v>0.5</v>
+      </c>
+      <c r="E13">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B11">
-        <v>20.5</v>
-      </c>
-      <c r="C11">
-        <v>5.5</v>
-      </c>
-      <c r="D11">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12">
-        <v>19.7</v>
-      </c>
-      <c r="C12">
-        <v>3.5</v>
-      </c>
-      <c r="D12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
+      <c r="B14">
+        <v>10.1</v>
+      </c>
+      <c r="C14">
+        <v>0.6</v>
+      </c>
+      <c r="D14">
+        <v>0.1</v>
+      </c>
+      <c r="E14">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B13">
-        <v>5.3</v>
-      </c>
-      <c r="C13">
-        <v>0.6</v>
-      </c>
-      <c r="D13">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14">
-        <v>3.3</v>
-      </c>
-      <c r="C14">
-        <v>0.2</v>
-      </c>
-      <c r="D14">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="B15">
-        <v>7.8</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="C15">
-        <v>0.8999999999999999</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>0.3</v>
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3012,28 +3150,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3044,25 +3182,25 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D2">
-        <v>84.34999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="E2" t="s">
         <v>16</v>
       </c>
       <c r="F2">
-        <v>104.49</v>
+        <v>103.24</v>
       </c>
       <c r="G2">
-        <v>0.542</v>
+        <v>0.545</v>
       </c>
       <c r="H2">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3073,25 +3211,25 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D3">
-        <v>78.27</v>
+        <v>91.23</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F3">
-        <v>104.49</v>
+        <v>102.91</v>
       </c>
       <c r="G3">
-        <v>0.542</v>
+        <v>0.576</v>
       </c>
       <c r="H3">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="I3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3102,25 +3240,25 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D4">
-        <v>87.98</v>
+        <v>88.13</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F4">
-        <v>102.56</v>
+        <v>101.82</v>
       </c>
       <c r="G4">
-        <v>0.5</v>
+        <v>0.485</v>
       </c>
       <c r="H4">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="I4">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3128,28 +3266,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5">
+        <v>91.73</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5">
+        <v>100.54</v>
+      </c>
+      <c r="G5">
+        <v>0.545</v>
+      </c>
+      <c r="H5">
+        <v>0.7</v>
+      </c>
+      <c r="I5">
         <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5">
-        <v>97.83</v>
-      </c>
-      <c r="E5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5">
-        <v>102.56</v>
-      </c>
-      <c r="G5">
-        <v>0.5</v>
-      </c>
-      <c r="H5">
-        <v>0.3</v>
-      </c>
-      <c r="I5">
-        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3157,28 +3295,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D6">
-        <v>116.34</v>
+        <v>76.37</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>101.02</v>
+        <v>99.8</v>
       </c>
       <c r="G6">
+        <v>0.485</v>
+      </c>
+      <c r="H6">
         <v>0.5</v>
       </c>
-      <c r="H6">
-        <v>-0.2</v>
-      </c>
       <c r="I6">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3186,28 +3324,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D7">
-        <v>87.92</v>
+        <v>115.29</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F7">
-        <v>101.02</v>
+        <v>101</v>
       </c>
       <c r="G7">
+        <v>0.545</v>
+      </c>
+      <c r="H7">
         <v>0.5</v>
       </c>
-      <c r="H7">
-        <v>-0.2</v>
-      </c>
       <c r="I7">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3215,28 +3353,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D8">
-        <v>110.79</v>
+        <v>107.44</v>
       </c>
       <c r="E8" t="s">
         <v>15</v>
       </c>
       <c r="F8">
-        <v>99.62</v>
+        <v>100.72</v>
       </c>
       <c r="G8">
-        <v>0.458</v>
+        <v>0.485</v>
       </c>
       <c r="H8">
-        <v>-0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I8">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3244,28 +3382,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D9">
-        <v>110.22</v>
+        <v>106.83</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F9">
-        <v>99.62</v>
+        <v>100.7</v>
       </c>
       <c r="G9">
-        <v>0.458</v>
+        <v>0.515</v>
       </c>
       <c r="H9">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3276,25 +3414,25 @@
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D10">
-        <v>97.39</v>
+        <v>94.27</v>
       </c>
       <c r="E10" t="s">
         <v>14</v>
       </c>
       <c r="F10">
-        <v>99.87</v>
+        <v>98.23</v>
       </c>
       <c r="G10">
-        <v>0.5</v>
+        <v>0.455</v>
       </c>
       <c r="H10">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="I10">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3302,28 +3440,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D11">
-        <v>120.7</v>
+        <v>112.94</v>
       </c>
       <c r="E11" t="s">
         <v>15</v>
       </c>
       <c r="F11">
-        <v>99.87</v>
+        <v>97.29000000000001</v>
       </c>
       <c r="G11">
-        <v>0.5</v>
+        <v>0.455</v>
       </c>
       <c r="H11">
-        <v>-0.4</v>
+        <v>-1.3</v>
       </c>
       <c r="I11">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3331,28 +3469,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D12">
-        <v>93.48</v>
+        <v>108.05</v>
       </c>
       <c r="E12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F12">
-        <v>100.33</v>
+        <v>98.92</v>
       </c>
       <c r="G12">
-        <v>0.5</v>
+        <v>0.515</v>
       </c>
       <c r="H12">
-        <v>-0.5</v>
+        <v>-1.5</v>
       </c>
       <c r="I12">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3360,28 +3498,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D13">
-        <v>119.09</v>
+        <v>105.23</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F13">
-        <v>100.33</v>
+        <v>97.39</v>
       </c>
       <c r="G13">
-        <v>0.5</v>
+        <v>0.424</v>
       </c>
       <c r="H13">
-        <v>-0.5</v>
+        <v>-1.6</v>
       </c>
       <c r="I13">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -3389,28 +3527,28 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D14">
-        <v>109.68</v>
+        <v>108.96</v>
       </c>
       <c r="E14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F14">
-        <v>100.36</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="G14">
-        <v>0.5</v>
+        <v>0.485</v>
       </c>
       <c r="H14">
-        <v>-0.5</v>
+        <v>-1.6</v>
       </c>
       <c r="I14">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -3418,28 +3556,28 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D15">
-        <v>102.47</v>
+        <v>108.53</v>
       </c>
       <c r="E15" t="s">
         <v>16</v>
       </c>
       <c r="F15">
-        <v>100.36</v>
+        <v>96.95</v>
       </c>
       <c r="G15">
-        <v>0.5</v>
+        <v>0.485</v>
       </c>
       <c r="H15">
-        <v>-0.5</v>
+        <v>-2.2</v>
       </c>
       <c r="I15">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -3454,31 +3592,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3486,373 +3624,373 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>120.7</v>
+        <v>115.2933333333333</v>
       </c>
       <c r="E2">
-        <v>241.4</v>
+        <v>345.88</v>
       </c>
       <c r="F2">
-        <v>99.5</v>
+        <v>96.8</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D3">
-        <v>116.34</v>
+        <v>112.94</v>
       </c>
       <c r="E3">
-        <v>232.68</v>
+        <v>338.82</v>
       </c>
       <c r="F3">
-        <v>98.2</v>
+        <v>92.60000000000001</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>119.09</v>
+        <v>105.2333333333333</v>
       </c>
       <c r="E4">
-        <v>238.18</v>
+        <v>315.7</v>
       </c>
       <c r="F4">
-        <v>86.7</v>
+        <v>82.39999999999999</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D5">
-        <v>110.79</v>
+        <v>108.96</v>
       </c>
       <c r="E5">
-        <v>221.58</v>
+        <v>326.88</v>
       </c>
       <c r="F5">
-        <v>83.3</v>
+        <v>75.5</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>110.22</v>
+        <v>106.8333333333333</v>
       </c>
       <c r="E6">
-        <v>220.44</v>
+        <v>320.5</v>
       </c>
       <c r="F6">
-        <v>82.3</v>
+        <v>73.8</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I6" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D7">
-        <v>109.68</v>
+        <v>108.0466666666667</v>
       </c>
       <c r="E7">
-        <v>219.36</v>
+        <v>324.14</v>
       </c>
       <c r="F7">
-        <v>60</v>
+        <v>64.5</v>
       </c>
       <c r="G7">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D8">
-        <v>102.47</v>
+        <v>107.44</v>
       </c>
       <c r="E8">
-        <v>204.94</v>
+        <v>322.32</v>
       </c>
       <c r="F8">
-        <v>39.90000000000001</v>
+        <v>61.3</v>
       </c>
       <c r="G8">
-        <v>0.7000000000000001</v>
+        <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D9">
-        <v>97.83</v>
+        <v>108.5333333333333</v>
       </c>
       <c r="E9">
-        <v>195.66</v>
+        <v>325.6</v>
       </c>
       <c r="F9">
-        <v>26.4</v>
+        <v>50.5</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D10">
-        <v>97.38999999999999</v>
+        <v>91.23333333333333</v>
       </c>
       <c r="E10">
-        <v>194.78</v>
+        <v>273.7</v>
       </c>
       <c r="F10">
-        <v>15</v>
+        <v>1.4</v>
       </c>
       <c r="G10">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="H10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C11">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>84.34999999999999</v>
+        <v>94.26666666666665</v>
       </c>
       <c r="E11">
-        <v>168.7</v>
+        <v>282.8</v>
       </c>
       <c r="F11">
-        <v>4.9</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="G11">
-        <v>10.2</v>
+        <v>2</v>
       </c>
       <c r="H11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D12">
-        <v>93.47999999999999</v>
+        <v>88.13333333333333</v>
       </c>
       <c r="E12">
-        <v>186.96</v>
+        <v>264.4</v>
       </c>
       <c r="F12">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="G12">
-        <v>7.3</v>
+        <v>6.4</v>
       </c>
       <c r="H12" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D13">
-        <v>87.91999999999999</v>
+        <v>81.89999999999999</v>
       </c>
       <c r="E13">
-        <v>175.84</v>
+        <v>245.7</v>
       </c>
       <c r="F13">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="G13">
-        <v>18.9</v>
+        <v>17.5</v>
       </c>
       <c r="H13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>78.27</v>
+        <v>91.73333333333333</v>
       </c>
       <c r="E14">
-        <v>156.54</v>
+        <v>275.2</v>
       </c>
       <c r="F14">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>37.9</v>
+        <v>7.1</v>
       </c>
       <c r="H14" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I14" t="s">
         <v>95</v>
@@ -3860,31 +3998,31 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>87.97999999999999</v>
+        <v>76.36666666666666</v>
       </c>
       <c r="E15">
-        <v>175.96</v>
+        <v>229.1</v>
       </c>
       <c r="F15">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>22</v>
+        <v>63.9</v>
       </c>
       <c r="H15" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -3899,19 +4037,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3922,16 +4060,16 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3939,19 +4077,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
         <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3959,19 +4097,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
         <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3979,19 +4117,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4002,10 +4140,10 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E6" t="s">
         <v>14</v>
@@ -4019,7 +4157,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
         <v>57</v>
@@ -4028,10 +4166,10 @@
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4039,19 +4177,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4059,16 +4197,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F9" t="s">
         <v>104</v>
@@ -4079,19 +4217,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D10">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4099,19 +4237,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D11">
         <v>-2</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4119,19 +4257,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D12">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="E12" t="s">
         <v>16</v>
       </c>
       <c r="F12" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4142,16 +4280,16 @@
         <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D13">
-        <v>-4</v>
+        <v>-9</v>
       </c>
       <c r="E13" t="s">
         <v>14</v>
       </c>
       <c r="F13" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4162,16 +4300,16 @@
         <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D14">
-        <v>-5</v>
+        <v>-12</v>
       </c>
       <c r="E14" t="s">
         <v>16</v>
       </c>
       <c r="F14" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4182,16 +4320,16 @@
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D15">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="E15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -4201,21 +4339,24 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>113</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -4225,53 +4366,65 @@
       <c r="C2">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="D2">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3">
+        <v>-2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="B3">
-        <v>6</v>
-      </c>
-      <c r="C3">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
       </c>
       <c r="B4">
         <v>6</v>
       </c>
       <c r="C4">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5">
         <v>5</v>
       </c>
-      <c r="D4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5">
-        <v>-2</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -4281,95 +4434,116 @@
       <c r="C6">
         <v>3</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>-3</v>
+      </c>
+      <c r="C7">
+        <v>-2</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>-9</v>
+      </c>
+      <c r="C8">
+        <v>-3</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>-8</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B7">
+      <c r="B11">
         <v>1</v>
       </c>
-      <c r="C7">
+      <c r="C11">
         <v>2</v>
       </c>
-      <c r="D7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8">
-        <v>3</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9">
-        <v>-8</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
+      <c r="D11">
+        <v>-2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B10">
+      <c r="B12">
         <v>-1</v>
       </c>
-      <c r="C10">
+      <c r="C12">
         <v>-2</v>
       </c>
-      <c r="D10" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11">
-        <v>-3</v>
-      </c>
-      <c r="C11">
-        <v>-2</v>
-      </c>
-      <c r="D11" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12">
-        <v>-9</v>
-      </c>
-      <c r="C12">
-        <v>-3</v>
-      </c>
-      <c r="D12" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="D12">
+        <v>-7</v>
+      </c>
+      <c r="E12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
         <v>6</v>
       </c>
@@ -4379,11 +4553,14 @@
       <c r="C13">
         <v>-4</v>
       </c>
-      <c r="D13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="D13">
+        <v>-9</v>
+      </c>
+      <c r="E13" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" s="1" t="s">
         <v>7</v>
       </c>
@@ -4393,11 +4570,14 @@
       <c r="C14">
         <v>-5</v>
       </c>
-      <c r="D14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="D14">
+        <v>-12</v>
+      </c>
+      <c r="E14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
@@ -4407,8 +4587,11 @@
       <c r="C15">
         <v>-15</v>
       </c>
-      <c r="D15" t="s">
-        <v>106</v>
+      <c r="D15">
+        <v>-14</v>
+      </c>
+      <c r="E15" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/BP- Loudoun 2025 2026.xlsx
+++ b/data/leagues/BP- Loudoun 2025 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="124">
   <si>
     <t>Bears, Jags, Foxes, Oh My!</t>
   </si>
@@ -67,16 +67,19 @@
     <t>Dave's Dynamos</t>
   </si>
   <si>
-    <t>0-3-0</t>
-  </si>
-  <si>
-    <t>2-1-0</t>
-  </si>
-  <si>
-    <t>1-2-0</t>
-  </si>
-  <si>
-    <t>3-0-0</t>
+    <t>0-4-0</t>
+  </si>
+  <si>
+    <t>2-2-0</t>
+  </si>
+  <si>
+    <t>1-3-0</t>
+  </si>
+  <si>
+    <t>3-1-0</t>
+  </si>
+  <si>
+    <t>4-0-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -154,6 +157,9 @@
     <t>Week_4</t>
   </si>
   <si>
+    <t>Week_5</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -178,42 +184,42 @@
     <t>Ishan Goel</t>
   </si>
   <si>
+    <t>Chungfu Yang</t>
+  </si>
+  <si>
+    <t>Justin Fox</t>
+  </si>
+  <si>
     <t>Roy Armbruster</t>
   </si>
   <si>
-    <t>Chungfu Yang</t>
-  </si>
-  <si>
-    <t>Justin Fox</t>
+    <t>Hannah Davis</t>
+  </si>
+  <si>
+    <t>Dave Linton</t>
+  </si>
+  <si>
+    <t>MARVIN AYALA</t>
   </si>
   <si>
     <t>Dale Goodwin</t>
   </si>
   <si>
-    <t>Dave Linton</t>
+    <t>Daniel Tracey</t>
+  </si>
+  <si>
+    <t>Yahya Ayaz</t>
   </si>
   <si>
     <t>Matthew Graesser</t>
   </si>
   <si>
-    <t>MARVIN AYALA</t>
-  </si>
-  <si>
-    <t>Hannah Davis</t>
+    <t>Jessica Stratton</t>
   </si>
   <si>
     <t>Jeffrey Laidacker</t>
   </si>
   <si>
-    <t>Jessica Stratton</t>
-  </si>
-  <si>
-    <t>Daniel Tracey</t>
-  </si>
-  <si>
-    <t>Yahya Ayaz</t>
-  </si>
-  <si>
     <t>Robert Schottler</t>
   </si>
   <si>
@@ -241,58 +247,61 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>3-0</t>
-  </si>
-  <si>
-    <t>2-1</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>0-3</t>
-  </si>
-  <si>
-    <t>10.7-3.2-0.2</t>
-  </si>
-  <si>
-    <t>9.9-3.9-0.1</t>
-  </si>
-  <si>
-    <t>9.7-4.1-0.2</t>
-  </si>
-  <si>
-    <t>9.1-4.8-0.2</t>
-  </si>
-  <si>
-    <t>9.2-4.6-0.2</t>
-  </si>
-  <si>
-    <t>8.7-5.2-0.1</t>
-  </si>
-  <si>
-    <t>8.5-5.3-0.2</t>
-  </si>
-  <si>
-    <t>8.1-5.8-0.1</t>
+    <t>4-0</t>
+  </si>
+  <si>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>0-4</t>
+  </si>
+  <si>
+    <t>10.4-3.5-0.1</t>
+  </si>
+  <si>
+    <t>10.2-3.7-0.1</t>
+  </si>
+  <si>
+    <t>9.6-4.3-0.1</t>
+  </si>
+  <si>
+    <t>9.3-4.5-0.1</t>
+  </si>
+  <si>
+    <t>8.6-5.3-0.1</t>
+  </si>
+  <si>
+    <t>8.5-5.3-0.1</t>
+  </si>
+  <si>
+    <t>8.4-5.5-0.2</t>
+  </si>
+  <si>
+    <t>7.4-6.5-0.1</t>
+  </si>
+  <si>
+    <t>5.9-8.0-0.1</t>
+  </si>
+  <si>
+    <t>4.8-9.1-0.1</t>
   </si>
   <si>
     <t>4.7-9.2-0.1</t>
   </si>
   <si>
-    <t>4.8-9.1-0.2</t>
-  </si>
-  <si>
-    <t>4.1-9.8-0.1</t>
-  </si>
-  <si>
-    <t>3.4-10.5-0.1</t>
-  </si>
-  <si>
-    <t>3.9-9.9-0.1</t>
-  </si>
-  <si>
-    <t>2.2-11.7-0.1</t>
+    <t>4.0-9.9-0.1</t>
+  </si>
+  <si>
+    <t>2.8-11.1-0.1</t>
+  </si>
+  <si>
+    <t>2.7-11.2-0.1</t>
   </si>
   <si>
     <t>11-3</t>
@@ -307,6 +316,12 @@
     <t>8-6</t>
   </si>
   <si>
+    <t>7-7</t>
+  </si>
+  <si>
+    <t>6-8</t>
+  </si>
+  <si>
     <t>5-9</t>
   </si>
   <si>
@@ -316,9 +331,6 @@
     <t>3-11</t>
   </si>
   <si>
-    <t>2-12</t>
-  </si>
-  <si>
     <t>Owners</t>
   </si>
   <si>
@@ -331,31 +343,25 @@
     <t>↑2</t>
   </si>
   <si>
-    <t>↑7</t>
-  </si>
-  <si>
-    <t>↓1</t>
-  </si>
-  <si>
     <t>0</t>
   </si>
   <si>
+    <t>↑3</t>
+  </si>
+  <si>
     <t>↑4</t>
   </si>
   <si>
+    <t>↓2</t>
+  </si>
+  <si>
+    <t>↓5</t>
+  </si>
+  <si>
     <t>↑5</t>
   </si>
   <si>
-    <t>↑1</t>
-  </si>
-  <si>
-    <t>↓4</t>
-  </si>
-  <si>
-    <t>↓5</t>
-  </si>
-  <si>
-    <t>↓7</t>
+    <t>↓3</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -365,6 +371,9 @@
   </si>
   <si>
     <t>Week 3</t>
+  </si>
+  <si>
+    <t>Week 4</t>
   </si>
   <si>
     <t>Week</t>
@@ -804,10 +813,10 @@
         <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
         <v>16</v>
@@ -819,7 +828,7 @@
         <v>16</v>
       </c>
       <c r="J2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K2" t="s">
         <v>16</v>
@@ -851,10 +860,10 @@
         <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
@@ -866,10 +875,10 @@
         <v>15</v>
       </c>
       <c r="J3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L3" t="s">
         <v>15</v>
@@ -889,34 +898,34 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I4" t="s">
         <v>15</v>
       </c>
       <c r="J4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L4" t="s">
         <v>17</v>
@@ -925,7 +934,7 @@
         <v>17</v>
       </c>
       <c r="N4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O4" t="s">
         <v>17</v>
@@ -936,34 +945,34 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
         <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I5" t="s">
         <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L5" t="s">
         <v>15</v>
@@ -972,10 +981,10 @@
         <v>15</v>
       </c>
       <c r="N5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -983,34 +992,34 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
         <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L6" t="s">
         <v>15</v>
@@ -1019,10 +1028,10 @@
         <v>16</v>
       </c>
       <c r="N6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -1030,46 +1039,46 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -1077,46 +1086,46 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L8" t="s">
         <v>16</v>
       </c>
       <c r="M8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -1171,46 +1180,46 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
         <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1218,7 +1227,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
         <v>16</v>
@@ -1227,13 +1236,13 @@
         <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H11" t="s">
         <v>14</v>
@@ -1242,10 +1251,10 @@
         <v>15</v>
       </c>
       <c r="J11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L11" t="s">
         <v>15</v>
@@ -1274,10 +1283,10 @@
         <v>16</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G12" t="s">
         <v>16</v>
@@ -1312,22 +1321,22 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
         <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
@@ -1336,10 +1345,10 @@
         <v>15</v>
       </c>
       <c r="J13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L13" t="s">
         <v>17</v>
@@ -1359,7 +1368,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
@@ -1368,13 +1377,13 @@
         <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -1383,10 +1392,10 @@
         <v>15</v>
       </c>
       <c r="J14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L14" t="s">
         <v>17</v>
@@ -1418,7 +1427,7 @@
         <v>17</v>
       </c>
       <c r="F15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G15" t="s">
         <v>15</v>
@@ -1455,30 +1464,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1538,25 +1547,25 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F4">
+        <v>-4</v>
+      </c>
+      <c r="G4">
+        <v>9</v>
+      </c>
+      <c r="H4" t="s">
         <v>6</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-      <c r="H4" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1564,25 +1573,25 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>-10</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H5" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1593,22 +1602,22 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>6</v>
+      </c>
+      <c r="G6">
         <v>5</v>
       </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6">
+      <c r="H6" t="s">
         <v>3</v>
-      </c>
-      <c r="H6" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1619,21 +1628,125 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="H7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>3</v>
+      </c>
+      <c r="H8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9">
+        <v>8</v>
+      </c>
+      <c r="F9">
+        <v>11</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
+      </c>
+      <c r="H9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>4</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>6</v>
+      </c>
+      <c r="F10">
+        <v>8</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11" t="s">
         <v>13</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D11" t="s">
         <v>4</v>
       </c>
-      <c r="E7">
+      <c r="E11">
         <v>2</v>
       </c>
-      <c r="F7">
+      <c r="F11">
         <v>3</v>
       </c>
-      <c r="G7">
+      <c r="G11">
         <v>1</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H11" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1649,13 +1762,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1663,13 +1776,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>0.5714285714285714</v>
+        <v>1.357142857142857</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1677,13 +1790,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1694,10 +1807,10 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>1.142857142857143</v>
+        <v>1.571428571428571</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1705,13 +1818,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>1.214285714285714</v>
+        <v>1.642857142857143</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1719,10 +1832,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C6">
-        <v>1.285714285714286</v>
+        <v>1.642857142857143</v>
       </c>
       <c r="D6" t="s">
         <v>15</v>
@@ -1733,13 +1846,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>1.285714285714286</v>
+        <v>1.928571428571429</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1747,13 +1860,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>1.428571428571429</v>
+        <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1761,13 +1874,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>1.5</v>
+        <v>2.071428571428572</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1778,10 +1891,10 @@
         <v>5</v>
       </c>
       <c r="C10">
-        <v>1.5</v>
+        <v>2.142857142857143</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1789,13 +1902,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C11">
-        <v>1.642857142857143</v>
+        <v>2.142857142857143</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1803,10 +1916,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C12">
-        <v>1.714285714285714</v>
+        <v>2.142857142857143</v>
       </c>
       <c r="D12" t="s">
         <v>17</v>
@@ -1817,13 +1930,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13">
-        <v>1.928571428571429</v>
+        <v>2.357142857142857</v>
       </c>
       <c r="D13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1831,13 +1944,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C14">
-        <v>2.214285714285714</v>
+        <v>2.571428571428572</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1848,7 +1961,7 @@
         <v>13</v>
       </c>
       <c r="C15">
-        <v>2.571428571428572</v>
+        <v>2.928571428571428</v>
       </c>
       <c r="D15" t="s">
         <v>17</v>
@@ -1866,16 +1979,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1883,13 +1996,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C2">
-        <v>2.428571428571428</v>
+        <v>3.142857142857143</v>
       </c>
       <c r="D2">
-        <v>-0.5714285714285716</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
@@ -1900,16 +2013,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>2.214285714285714</v>
+        <v>2.642857142857143</v>
       </c>
       <c r="D3">
-        <v>0.2142857142857144</v>
+        <v>-0.3571428571428572</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1917,13 +2030,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>2.142857142857143</v>
+        <v>2.642857142857143</v>
       </c>
       <c r="D4">
-        <v>0.1428571428571428</v>
+        <v>0.6428571428571428</v>
       </c>
       <c r="E4" t="s">
         <v>15</v>
@@ -1937,10 +2050,10 @@
         <v>11</v>
       </c>
       <c r="C5">
-        <v>2.071428571428572</v>
+        <v>2.571428571428572</v>
       </c>
       <c r="D5">
-        <v>-0.9285714285714284</v>
+        <v>-0.4285714285714284</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
@@ -1951,13 +2064,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>2.571428571428572</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>0.5714285714285716</v>
       </c>
       <c r="E6" t="s">
         <v>15</v>
@@ -1971,13 +2084,13 @@
         <v>3</v>
       </c>
       <c r="C7">
-        <v>1.785714285714286</v>
+        <v>2.5</v>
       </c>
       <c r="D7">
-        <v>-1.214285714285714</v>
+        <v>-1.5</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1985,16 +2098,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C8">
-        <v>1.714285714285714</v>
+        <v>2.5</v>
       </c>
       <c r="D8">
-        <v>-0.2857142857142858</v>
+        <v>-0.5</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2002,16 +2115,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>1.642857142857143</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>0.6428571428571428</v>
+        <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2019,13 +2132,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>1.071428571428571</v>
+        <v>1.785714285714286</v>
       </c>
       <c r="D10">
-        <v>0.0714285714285714</v>
+        <v>0.7857142857142858</v>
       </c>
       <c r="E10" t="s">
         <v>16</v>
@@ -2036,16 +2149,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C11">
-        <v>1.071428571428571</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="D11">
-        <v>1.071428571428571</v>
+        <v>-0.7142857142857142</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2053,13 +2166,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="E12" t="s">
         <v>14</v>
@@ -2070,13 +2183,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C13">
-        <v>0.8571428571428571</v>
+        <v>1.214285714285714</v>
       </c>
       <c r="D13">
-        <v>-0.1428571428571429</v>
+        <v>0.2142857142857142</v>
       </c>
       <c r="E13" t="s">
         <v>16</v>
@@ -2087,13 +2200,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C14">
-        <v>0.6428571428571429</v>
+        <v>1.214285714285714</v>
       </c>
       <c r="D14">
-        <v>-0.3571428571428571</v>
+        <v>0.2142857142857142</v>
       </c>
       <c r="E14" t="s">
         <v>16</v>
@@ -2104,16 +2217,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C15">
-        <v>0.3571428571428572</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="D15">
-        <v>0.3571428571428572</v>
+        <v>-0.3571428571428571</v>
       </c>
       <c r="E15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -2128,87 +2241,87 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B2">
-        <v>43.1</v>
+        <v>28.6</v>
       </c>
       <c r="C2">
-        <v>19.8</v>
+        <v>21.3</v>
       </c>
       <c r="D2">
-        <v>13.7</v>
+        <v>16.6</v>
       </c>
       <c r="E2">
-        <v>10.8</v>
+        <v>14.1</v>
       </c>
       <c r="F2">
-        <v>5.4</v>
+        <v>8.6</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>6.3</v>
       </c>
       <c r="H2">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="I2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -2223,39 +2336,39 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>96.8</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B3">
-        <v>18.2</v>
+        <v>29.6</v>
       </c>
       <c r="C3">
-        <v>22.6</v>
+        <v>23.9</v>
       </c>
       <c r="D3">
-        <v>17.7</v>
+        <v>16.6</v>
       </c>
       <c r="E3">
-        <v>15.6</v>
+        <v>11.3</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>8.1</v>
       </c>
       <c r="G3">
-        <v>8.5</v>
+        <v>5.8</v>
       </c>
       <c r="H3">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="I3">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J3">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="K3">
         <v>0.1</v>
@@ -2273,45 +2386,45 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>92.59999999999999</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4">
-        <v>12.9</v>
+        <v>20.3</v>
       </c>
       <c r="C4">
-        <v>14.9</v>
+        <v>20.9</v>
       </c>
       <c r="D4">
-        <v>14.7</v>
+        <v>16.8</v>
       </c>
       <c r="E4">
-        <v>15.1</v>
+        <v>14.3</v>
       </c>
       <c r="F4">
-        <v>13.1</v>
+        <v>10.5</v>
       </c>
       <c r="G4">
-        <v>11.7</v>
+        <v>7.8</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="I4">
-        <v>7.6</v>
+        <v>2.7</v>
       </c>
       <c r="J4">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="K4">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -2323,42 +2436,42 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>82.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B5">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="C5">
-        <v>10.8</v>
+        <v>13.4</v>
       </c>
       <c r="D5">
-        <v>14.7</v>
+        <v>16.2</v>
       </c>
       <c r="E5">
-        <v>11.6</v>
+        <v>16.6</v>
       </c>
       <c r="F5">
-        <v>16.2</v>
+        <v>18.2</v>
       </c>
       <c r="G5">
-        <v>15.2</v>
+        <v>12.3</v>
       </c>
       <c r="H5">
-        <v>11.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>3.4</v>
       </c>
       <c r="J5">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="K5">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -2373,45 +2486,45 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>75.5</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6">
-        <v>7.5</v>
+        <v>4.4</v>
       </c>
       <c r="C6">
-        <v>13.1</v>
+        <v>6.6</v>
       </c>
       <c r="D6">
-        <v>11.1</v>
+        <v>11.4</v>
       </c>
       <c r="E6">
-        <v>12.1</v>
+        <v>14.1</v>
       </c>
       <c r="F6">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="G6">
-        <v>13.2</v>
+        <v>18.8</v>
       </c>
       <c r="H6">
-        <v>14.3</v>
+        <v>12.5</v>
       </c>
       <c r="I6">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>1.8</v>
+        <v>4.5</v>
       </c>
       <c r="K6">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -2423,95 +2536,95 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>73.8</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B7">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="D7">
-        <v>10.3</v>
+        <v>9</v>
       </c>
       <c r="E7">
-        <v>13.5</v>
+        <v>11.3</v>
       </c>
       <c r="F7">
-        <v>12.2</v>
+        <v>14</v>
       </c>
       <c r="G7">
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
       <c r="H7">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="I7">
-        <v>13.7</v>
+        <v>14.8</v>
       </c>
       <c r="J7">
-        <v>3.3</v>
+        <v>5.9</v>
       </c>
       <c r="K7">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="L7">
+        <v>0.3</v>
+      </c>
+      <c r="M7">
+        <v>0.1</v>
+      </c>
+      <c r="N7">
         <v>0.2</v>
       </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>64.5</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B8">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="C8">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="D8">
-        <v>10.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E8">
-        <v>12.1</v>
+        <v>9.4</v>
       </c>
       <c r="F8">
-        <v>13.6</v>
+        <v>14.1</v>
       </c>
       <c r="G8">
-        <v>15.7</v>
+        <v>17</v>
       </c>
       <c r="H8">
-        <v>15.5</v>
+        <v>18.4</v>
       </c>
       <c r="I8">
-        <v>17.5</v>
+        <v>15.2</v>
       </c>
       <c r="J8">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="K8">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="L8">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="M8">
         <v>0.1</v>
@@ -2523,112 +2636,112 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>61.3</v>
+        <v>59.2</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B9">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>6.8</v>
+        <v>3.7</v>
       </c>
       <c r="E9">
-        <v>9.1</v>
+        <v>7.4</v>
       </c>
       <c r="F9">
-        <v>12.3</v>
+        <v>7.6</v>
       </c>
       <c r="G9">
-        <v>14.9</v>
+        <v>12</v>
       </c>
       <c r="H9">
-        <v>20.6</v>
+        <v>17.6</v>
       </c>
       <c r="I9">
-        <v>20.5</v>
+        <v>23.5</v>
       </c>
       <c r="J9">
-        <v>5.5</v>
+        <v>15.6</v>
       </c>
       <c r="K9">
-        <v>1.8</v>
+        <v>8</v>
       </c>
       <c r="L9">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="M9">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>50.5</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D10">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E10">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="F10">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="G10">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="H10">
-        <v>1.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I10">
-        <v>5.5</v>
+        <v>17.5</v>
       </c>
       <c r="J10">
-        <v>22.5</v>
+        <v>31.1</v>
       </c>
       <c r="K10">
-        <v>23.1</v>
+        <v>18.6</v>
       </c>
       <c r="L10">
-        <v>18.6</v>
+        <v>8.9</v>
       </c>
       <c r="M10">
-        <v>14.6</v>
+        <v>5.3</v>
       </c>
       <c r="N10">
-        <v>9.5</v>
+        <v>1.8</v>
       </c>
       <c r="O10">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="P10">
-        <v>1.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2640,40 +2753,40 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F11">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G11">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="I11">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>29.1</v>
+        <v>13</v>
       </c>
       <c r="K11">
-        <v>24.5</v>
+        <v>22.9</v>
       </c>
       <c r="L11">
-        <v>16</v>
+        <v>22.3</v>
       </c>
       <c r="M11">
-        <v>11.7</v>
+        <v>16.1</v>
       </c>
       <c r="N11">
-        <v>7.6</v>
+        <v>11.3</v>
       </c>
       <c r="O11">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P11">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2690,45 +2803,45 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F12">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G12">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="H12">
+        <v>1.1</v>
+      </c>
+      <c r="I12">
+        <v>4.2</v>
+      </c>
+      <c r="J12">
+        <v>13.4</v>
+      </c>
+      <c r="K12">
+        <v>23.3</v>
+      </c>
+      <c r="L12">
+        <v>25.3</v>
+      </c>
+      <c r="M12">
+        <v>20</v>
+      </c>
+      <c r="N12">
+        <v>10.5</v>
+      </c>
+      <c r="O12">
+        <v>1.4</v>
+      </c>
+      <c r="P12">
         <v>0.8</v>
-      </c>
-      <c r="I12">
-        <v>3.4</v>
-      </c>
-      <c r="J12">
-        <v>11.1</v>
-      </c>
-      <c r="K12">
-        <v>17.5</v>
-      </c>
-      <c r="L12">
-        <v>23.4</v>
-      </c>
-      <c r="M12">
-        <v>23</v>
-      </c>
-      <c r="N12">
-        <v>14.2</v>
-      </c>
-      <c r="O12">
-        <v>6.4</v>
-      </c>
-      <c r="P12">
-        <v>0.2</v>
       </c>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2740,40 +2853,40 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H13">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="I13">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J13">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="K13">
-        <v>8.6</v>
+        <v>14.2</v>
       </c>
       <c r="L13">
-        <v>12.9</v>
+        <v>22.8</v>
       </c>
       <c r="M13">
-        <v>22.9</v>
+        <v>25</v>
       </c>
       <c r="N13">
-        <v>32.6</v>
+        <v>19.9</v>
       </c>
       <c r="O13">
-        <v>17.5</v>
+        <v>8.1</v>
       </c>
       <c r="P13">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2799,28 +2912,28 @@
         <v>0</v>
       </c>
       <c r="H14">
+        <v>0.3</v>
+      </c>
+      <c r="I14">
         <v>0.2</v>
       </c>
-      <c r="I14">
-        <v>2.6</v>
-      </c>
       <c r="J14">
-        <v>13.3</v>
+        <v>1.4</v>
       </c>
       <c r="K14">
-        <v>19.2</v>
+        <v>6.1</v>
       </c>
       <c r="L14">
-        <v>23.4</v>
+        <v>11.1</v>
       </c>
       <c r="M14">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="N14">
-        <v>15</v>
+        <v>30.3</v>
       </c>
       <c r="O14">
-        <v>7.1</v>
+        <v>31.3</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -2828,7 +2941,7 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2852,25 +2965,25 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J15">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K15">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="L15">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="M15">
-        <v>8.300000000000001</v>
+        <v>13.3</v>
       </c>
       <c r="N15">
-        <v>21.1</v>
+        <v>25.6</v>
       </c>
       <c r="O15">
-        <v>63.9</v>
+        <v>52.6</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -2883,258 +2996,303 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>43</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2">
+        <v>95.39999999999999</v>
+      </c>
+      <c r="C2">
+        <v>32.8</v>
+      </c>
+      <c r="D2">
+        <v>77</v>
+      </c>
+      <c r="E2">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="F2">
+        <v>95.09999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>6.3</v>
+      </c>
+      <c r="C3">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="D3">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="E3">
+        <v>92.80000000000001</v>
+      </c>
+      <c r="F3">
+        <v>94.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="D4">
+        <v>49.3</v>
+      </c>
+      <c r="E4">
+        <v>92</v>
+      </c>
+      <c r="F4">
+        <v>92.10000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>94</v>
+      </c>
+      <c r="C5">
+        <v>98.3</v>
+      </c>
+      <c r="D5">
+        <v>60.09999999999999</v>
+      </c>
+      <c r="E5">
+        <v>82.3</v>
+      </c>
+      <c r="F5">
+        <v>84.09999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>78.60000000000001</v>
+      </c>
+      <c r="C6">
+        <v>77.3</v>
+      </c>
+      <c r="D6">
+        <v>93.89999999999999</v>
+      </c>
+      <c r="E6">
+        <v>69.19999999999999</v>
+      </c>
+      <c r="F6">
+        <v>69.69999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B2">
-        <v>99.7</v>
-      </c>
-      <c r="C2">
-        <v>99.3</v>
-      </c>
-      <c r="D2">
-        <v>97.5</v>
-      </c>
-      <c r="E2">
-        <v>95.89999999999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3">
-        <v>80.7</v>
-      </c>
-      <c r="C3">
-        <v>79.80000000000001</v>
-      </c>
-      <c r="D3">
-        <v>91.60000000000001</v>
-      </c>
-      <c r="E3">
-        <v>92.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>6.800000000000001</v>
-      </c>
-      <c r="C4">
-        <v>90</v>
-      </c>
-      <c r="D4">
-        <v>82.39999999999999</v>
-      </c>
-      <c r="E4">
-        <v>78.2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
+      <c r="B7">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="C7">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="D7">
+        <v>98</v>
+      </c>
+      <c r="E7">
+        <v>57.4</v>
+      </c>
+      <c r="F7">
+        <v>63.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5">
-        <v>27.4</v>
-      </c>
-      <c r="C5">
-        <v>28.6</v>
-      </c>
-      <c r="D5">
-        <v>77.10000000000001</v>
-      </c>
-      <c r="E5">
-        <v>77.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>95.5</v>
-      </c>
-      <c r="C6">
-        <v>34</v>
-      </c>
-      <c r="D6">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="E6">
-        <v>76.3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="1" t="s">
+      <c r="B8">
+        <v>29.4</v>
+      </c>
+      <c r="C8">
+        <v>29.2</v>
+      </c>
+      <c r="D8">
+        <v>77.2</v>
+      </c>
+      <c r="E8">
+        <v>66.5</v>
+      </c>
+      <c r="F8">
+        <v>59.09999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B7">
+      <c r="B9">
         <v>100</v>
       </c>
-      <c r="C7">
+      <c r="C9">
         <v>96.8</v>
       </c>
-      <c r="D7">
-        <v>61.4</v>
-      </c>
-      <c r="E7">
-        <v>64.3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8">
-        <v>93.40000000000001</v>
-      </c>
-      <c r="C8">
-        <v>97.39999999999999</v>
-      </c>
-      <c r="D8">
-        <v>62</v>
-      </c>
-      <c r="E8">
-        <v>58.9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>67.80000000000001</v>
-      </c>
       <c r="D9">
-        <v>48.9</v>
+        <v>61.8</v>
       </c>
       <c r="E9">
-        <v>53.1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>29.6</v>
+      </c>
+      <c r="F9">
+        <v>31.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10">
+        <v>66</v>
+      </c>
+      <c r="C10">
+        <v>6.1</v>
+      </c>
+      <c r="D10">
+        <v>1.2</v>
+      </c>
+      <c r="E10">
+        <v>12.8</v>
+      </c>
+      <c r="F10">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11">
+        <v>1.3</v>
+      </c>
+      <c r="C11">
+        <v>0.4</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0.8</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <v>0.6</v>
+      </c>
+      <c r="C12">
+        <v>0.3</v>
+      </c>
+      <c r="D12">
+        <v>0.2</v>
+      </c>
+      <c r="E12">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="F12">
+        <v>0.7000000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B10">
-        <v>2</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>1.4</v>
-      </c>
-      <c r="E10">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11">
-        <v>68.60000000000001</v>
-      </c>
-      <c r="C11">
-        <v>4</v>
-      </c>
-      <c r="D11">
-        <v>1.6</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12">
-        <v>14.7</v>
-      </c>
-      <c r="C12">
+      <c r="B13">
+        <v>2.1</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>1.9</v>
+      </c>
+      <c r="E13">
+        <v>0.1</v>
+      </c>
+      <c r="F13">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14">
+        <v>15.5</v>
+      </c>
+      <c r="C14">
         <v>1.5</v>
       </c>
-      <c r="D12">
-        <v>0.6</v>
-      </c>
-      <c r="E12">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13">
-        <v>0.2</v>
-      </c>
-      <c r="C13">
-        <v>0.2</v>
-      </c>
-      <c r="D13">
-        <v>0.5</v>
-      </c>
-      <c r="E13">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="1" t="s">
+      <c r="D14">
+        <v>0.4</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B14">
-        <v>10.1</v>
-      </c>
-      <c r="C14">
-        <v>0.6</v>
-      </c>
-      <c r="D14">
+      <c r="B15">
+        <v>11.2</v>
+      </c>
+      <c r="C15">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="D15">
         <v>0.1</v>
       </c>
-      <c r="E14">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
       <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
         <v>0</v>
       </c>
     </row>
@@ -3150,28 +3308,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3182,25 +3340,25 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D2">
-        <v>81.90000000000001</v>
+        <v>76.83</v>
       </c>
       <c r="E2" t="s">
         <v>16</v>
       </c>
       <c r="F2">
-        <v>103.24</v>
+        <v>104.5</v>
       </c>
       <c r="G2">
-        <v>0.545</v>
+        <v>0.575</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3208,28 +3366,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3">
+        <v>88.48999999999999</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3">
+        <v>104.03</v>
+      </c>
+      <c r="G3">
+        <v>0.55</v>
+      </c>
+      <c r="H3">
+        <v>2.5</v>
+      </c>
+      <c r="I3">
         <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3">
-        <v>91.23</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3">
-        <v>102.91</v>
-      </c>
-      <c r="G3">
-        <v>0.576</v>
-      </c>
-      <c r="H3">
-        <v>2.3</v>
-      </c>
-      <c r="I3">
-        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3237,28 +3395,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D4">
-        <v>88.13</v>
+        <v>88.16</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F4">
-        <v>101.82</v>
+        <v>103.34</v>
       </c>
       <c r="G4">
-        <v>0.485</v>
+        <v>0.575</v>
       </c>
       <c r="H4">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3266,28 +3424,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D5">
-        <v>91.73</v>
+        <v>87.66</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F5">
-        <v>100.54</v>
+        <v>103.17</v>
       </c>
       <c r="G5">
-        <v>0.545</v>
+        <v>0.575</v>
       </c>
       <c r="H5">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="I5">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3295,28 +3453,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D6">
-        <v>76.37</v>
+        <v>101.02</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>99.8</v>
+        <v>101.16</v>
       </c>
       <c r="G6">
-        <v>0.485</v>
+        <v>0.5</v>
       </c>
       <c r="H6">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3327,25 +3485,25 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D7">
-        <v>115.29</v>
+        <v>104.31</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
       </c>
       <c r="F7">
-        <v>101</v>
+        <v>99.73999999999999</v>
       </c>
       <c r="G7">
-        <v>0.545</v>
+        <v>0.475</v>
       </c>
       <c r="H7">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I7">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3353,28 +3511,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D8">
-        <v>107.44</v>
+        <v>105.19</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F8">
-        <v>100.72</v>
+        <v>101.56</v>
       </c>
       <c r="G8">
-        <v>0.485</v>
+        <v>0.525</v>
       </c>
       <c r="H8">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="I8">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3382,28 +3540,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D9">
-        <v>106.83</v>
+        <v>88.66</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F9">
-        <v>100.7</v>
+        <v>99.23</v>
       </c>
       <c r="G9">
-        <v>0.515</v>
+        <v>0.45</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="I9">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3411,28 +3569,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D10">
-        <v>94.27</v>
+        <v>107.66</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F10">
-        <v>98.23</v>
+        <v>97.12</v>
       </c>
       <c r="G10">
-        <v>0.455</v>
+        <v>0.4</v>
       </c>
       <c r="H10">
-        <v>-0.5</v>
+        <v>-1.2</v>
       </c>
       <c r="I10">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3440,28 +3598,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D11">
-        <v>112.94</v>
+        <v>114.64</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F11">
-        <v>97.29000000000001</v>
+        <v>97.62</v>
       </c>
       <c r="G11">
-        <v>0.455</v>
+        <v>0.5</v>
       </c>
       <c r="H11">
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="I11">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3469,28 +3627,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D12">
-        <v>108.05</v>
+        <v>108.52</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F12">
-        <v>98.92</v>
+        <v>98.69</v>
       </c>
       <c r="G12">
-        <v>0.515</v>
+        <v>0.45</v>
       </c>
       <c r="H12">
-        <v>-1.5</v>
+        <v>-1.3</v>
       </c>
       <c r="I12">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3498,28 +3656,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D13">
-        <v>105.23</v>
+        <v>101.29</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F13">
-        <v>97.39</v>
+        <v>97.56999999999999</v>
       </c>
       <c r="G13">
-        <v>0.424</v>
+        <v>0.525</v>
       </c>
       <c r="H13">
-        <v>-1.6</v>
+        <v>-2.2</v>
       </c>
       <c r="I13">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -3527,28 +3685,28 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D14">
-        <v>108.96</v>
+        <v>107.31</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
       </c>
       <c r="F14">
-        <v>97.40000000000001</v>
+        <v>95.63</v>
       </c>
       <c r="G14">
-        <v>0.485</v>
+        <v>0.425</v>
       </c>
       <c r="H14">
-        <v>-1.6</v>
+        <v>-2.3</v>
       </c>
       <c r="I14">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -3559,25 +3717,25 @@
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D15">
-        <v>108.53</v>
+        <v>119.25</v>
       </c>
       <c r="E15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F15">
-        <v>96.95</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="G15">
-        <v>0.485</v>
+        <v>0.475</v>
       </c>
       <c r="H15">
-        <v>-2.2</v>
+        <v>-3.7</v>
       </c>
       <c r="I15">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3592,321 +3750,321 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>115.2933333333333</v>
+        <v>107.655</v>
       </c>
       <c r="E2">
-        <v>345.88</v>
+        <v>430.62</v>
       </c>
       <c r="F2">
-        <v>96.8</v>
+        <v>95.5</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C3">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="D3">
-        <v>112.94</v>
+        <v>114.645</v>
       </c>
       <c r="E3">
-        <v>338.82</v>
+        <v>458.58</v>
       </c>
       <c r="F3">
-        <v>92.60000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D4">
-        <v>105.2333333333333</v>
+        <v>119.25</v>
       </c>
       <c r="E4">
-        <v>315.7</v>
+        <v>477</v>
       </c>
       <c r="F4">
-        <v>82.39999999999999</v>
+        <v>90.60000000000001</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C5">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="D5">
-        <v>108.96</v>
+        <v>108.52</v>
       </c>
       <c r="E5">
-        <v>326.88</v>
+        <v>434.08</v>
       </c>
       <c r="F5">
-        <v>75.5</v>
+        <v>85.3</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D6">
-        <v>106.8333333333333</v>
+        <v>107.31</v>
       </c>
       <c r="E6">
-        <v>320.5</v>
+        <v>429.24</v>
       </c>
       <c r="F6">
-        <v>73.8</v>
+        <v>72.3</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C7">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="D7">
-        <v>108.0466666666667</v>
+        <v>104.315</v>
       </c>
       <c r="E7">
-        <v>324.14</v>
+        <v>417.26</v>
       </c>
       <c r="F7">
-        <v>64.5</v>
+        <v>60.5</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I7" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C8">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="D8">
-        <v>107.44</v>
+        <v>105.195</v>
       </c>
       <c r="E8">
-        <v>322.32</v>
+        <v>420.78</v>
       </c>
       <c r="F8">
-        <v>61.3</v>
+        <v>59.2</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I8" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C9">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="D9">
-        <v>108.5333333333333</v>
+        <v>101.29</v>
       </c>
       <c r="E9">
-        <v>325.6</v>
+        <v>405.16</v>
       </c>
       <c r="F9">
-        <v>50.5</v>
+        <v>31.9</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I9" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C10">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="D10">
-        <v>91.23333333333333</v>
+        <v>101.02</v>
       </c>
       <c r="E10">
-        <v>273.7</v>
+        <v>404.0799999999999</v>
       </c>
       <c r="F10">
-        <v>1.4</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="G10">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="H10" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I10" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D11">
-        <v>94.26666666666665</v>
+        <v>88.66499999999999</v>
       </c>
       <c r="E11">
-        <v>282.8</v>
+        <v>354.66</v>
       </c>
       <c r="F11">
-        <v>0.8999999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I11" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3914,57 +4072,57 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C12">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="D12">
-        <v>88.13333333333333</v>
+        <v>88.49499999999999</v>
       </c>
       <c r="E12">
-        <v>264.4</v>
+        <v>353.98</v>
       </c>
       <c r="F12">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G12">
-        <v>6.4</v>
+        <v>1.4</v>
       </c>
       <c r="H12" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I12" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C13">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="D13">
-        <v>81.89999999999999</v>
+        <v>87.655</v>
       </c>
       <c r="E13">
-        <v>245.7</v>
+        <v>350.62</v>
       </c>
       <c r="F13">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="G13">
-        <v>17.5</v>
+        <v>8.1</v>
       </c>
       <c r="H13" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I13" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -3972,57 +4130,57 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>91.73333333333333</v>
+        <v>88.16499999999999</v>
       </c>
       <c r="E14">
-        <v>275.2</v>
+        <v>352.66</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>7.1</v>
+        <v>31.3</v>
       </c>
       <c r="H14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I14" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D15">
-        <v>76.36666666666666</v>
+        <v>76.83</v>
       </c>
       <c r="E15">
-        <v>229.1</v>
+        <v>307.32</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>63.9</v>
+        <v>52.6</v>
       </c>
       <c r="H15" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I15" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -4037,19 +4195,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4060,16 +4218,16 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4080,7 +4238,7 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D3">
         <v>11</v>
@@ -4089,7 +4247,7 @@
         <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4100,16 +4258,16 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4120,16 +4278,16 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E5" t="s">
         <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4137,19 +4295,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4160,16 +4318,16 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4177,19 +4335,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="s">
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4197,19 +4355,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4217,19 +4375,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4237,19 +4395,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D11">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4257,19 +4415,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D12">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F12" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4277,19 +4435,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D13">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4297,19 +4455,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D14">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="E14" t="s">
         <v>16</v>
       </c>
       <c r="F14" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4317,19 +4475,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D15">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="E15" t="s">
         <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -4339,24 +4497,27 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>116</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -4369,11 +4530,14 @@
       <c r="D2">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="E2">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -4386,11 +4550,14 @@
       <c r="D3">
         <v>11</v>
       </c>
-      <c r="E3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="E3">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -4403,11 +4570,14 @@
       <c r="D4">
         <v>6</v>
       </c>
-      <c r="E4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="E4">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
@@ -4420,28 +4590,34 @@
       <c r="D5">
         <v>5</v>
       </c>
-      <c r="E5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>-9</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -4454,144 +4630,171 @@
       <c r="D7">
         <v>2</v>
       </c>
-      <c r="E7" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8">
         <v>5</v>
       </c>
-      <c r="B8">
-        <v>-9</v>
-      </c>
-      <c r="C8">
-        <v>-3</v>
-      </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>-8</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
-      <c r="E9" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="E9">
+        <v>-1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10">
         <v>3</v>
       </c>
-      <c r="B10">
-        <v>-8</v>
-      </c>
       <c r="C10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
-      <c r="E10" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="E10">
+        <v>-4</v>
+      </c>
+      <c r="F10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11">
+        <v>-3</v>
+      </c>
+      <c r="C11">
+        <v>-4</v>
+      </c>
+      <c r="D11">
+        <v>-9</v>
+      </c>
+      <c r="E11">
+        <v>-4</v>
+      </c>
+      <c r="F11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B11">
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="C11">
+      <c r="C12">
         <v>2</v>
       </c>
-      <c r="D11">
+      <c r="D12">
         <v>-2</v>
       </c>
-      <c r="E11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="1" t="s">
+      <c r="E12">
+        <v>-5</v>
+      </c>
+      <c r="F12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B12">
+      <c r="B13">
         <v>-1</v>
       </c>
-      <c r="C12">
+      <c r="C13">
         <v>-2</v>
       </c>
-      <c r="D12">
+      <c r="D13">
         <v>-7</v>
       </c>
-      <c r="E12" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13">
-        <v>-3</v>
-      </c>
-      <c r="C13">
+      <c r="E13">
+        <v>-10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14">
         <v>-4</v>
       </c>
-      <c r="D13">
-        <v>-9</v>
-      </c>
-      <c r="E13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="1" t="s">
+      <c r="C14">
+        <v>-15</v>
+      </c>
+      <c r="D14">
+        <v>-14</v>
+      </c>
+      <c r="E14">
+        <v>-14</v>
+      </c>
+      <c r="F14" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B14">
+      <c r="B15">
         <v>4</v>
       </c>
-      <c r="C14">
+      <c r="C15">
         <v>-5</v>
       </c>
-      <c r="D14">
+      <c r="D15">
         <v>-12</v>
       </c>
-      <c r="E14" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15">
-        <v>-4</v>
-      </c>
-      <c r="C15">
+      <c r="E15">
         <v>-15</v>
       </c>
-      <c r="D15">
-        <v>-14</v>
-      </c>
-      <c r="E15" t="s">
-        <v>107</v>
+      <c r="F15" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/BP- Loudoun 2025 2026.xlsx
+++ b/data/leagues/BP- Loudoun 2025 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="128">
   <si>
     <t>Bears, Jags, Foxes, Oh My!</t>
   </si>
@@ -67,19 +67,22 @@
     <t>Dave's Dynamos</t>
   </si>
   <si>
-    <t>0-4-0</t>
-  </si>
-  <si>
-    <t>2-2-0</t>
-  </si>
-  <si>
-    <t>1-3-0</t>
-  </si>
-  <si>
-    <t>3-1-0</t>
-  </si>
-  <si>
-    <t>4-0-0</t>
+    <t>0-5-0</t>
+  </si>
+  <si>
+    <t>2-3-0</t>
+  </si>
+  <si>
+    <t>3-2-0</t>
+  </si>
+  <si>
+    <t>1-4-0</t>
+  </si>
+  <si>
+    <t>4-1-0</t>
+  </si>
+  <si>
+    <t>5-0-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -160,6 +163,9 @@
     <t>Week_5</t>
   </si>
   <si>
+    <t>Week_6</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -184,42 +190,42 @@
     <t>Ishan Goel</t>
   </si>
   <si>
+    <t>Roy Armbruster</t>
+  </si>
+  <si>
+    <t>Justin Fox</t>
+  </si>
+  <si>
+    <t>Hannah Davis</t>
+  </si>
+  <si>
+    <t>Dale Goodwin</t>
+  </si>
+  <si>
+    <t>Yahya Ayaz</t>
+  </si>
+  <si>
     <t>Chungfu Yang</t>
   </si>
   <si>
-    <t>Justin Fox</t>
-  </si>
-  <si>
-    <t>Roy Armbruster</t>
-  </si>
-  <si>
-    <t>Hannah Davis</t>
+    <t>MARVIN AYALA</t>
+  </si>
+  <si>
+    <t>Jessica Stratton</t>
   </si>
   <si>
     <t>Dave Linton</t>
   </si>
   <si>
-    <t>MARVIN AYALA</t>
-  </si>
-  <si>
-    <t>Dale Goodwin</t>
-  </si>
-  <si>
     <t>Daniel Tracey</t>
   </si>
   <si>
-    <t>Yahya Ayaz</t>
+    <t>Jeffrey Laidacker</t>
   </si>
   <si>
     <t>Matthew Graesser</t>
   </si>
   <si>
-    <t>Jessica Stratton</t>
-  </si>
-  <si>
-    <t>Jeffrey Laidacker</t>
-  </si>
-  <si>
     <t>Robert Schottler</t>
   </si>
   <si>
@@ -247,72 +253,69 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>4-0</t>
-  </si>
-  <si>
-    <t>3-1</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>0-4</t>
-  </si>
-  <si>
-    <t>10.4-3.5-0.1</t>
-  </si>
-  <si>
-    <t>10.2-3.7-0.1</t>
-  </si>
-  <si>
-    <t>9.6-4.3-0.1</t>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>0-5</t>
+  </si>
+  <si>
+    <t>10.7-3.2-0.1</t>
+  </si>
+  <si>
+    <t>10.5-3.4-0.1</t>
+  </si>
+  <si>
+    <t>9.2-4.7-0.1</t>
   </si>
   <si>
     <t>9.3-4.5-0.1</t>
   </si>
   <si>
-    <t>8.6-5.3-0.1</t>
-  </si>
-  <si>
-    <t>8.5-5.3-0.1</t>
-  </si>
-  <si>
-    <t>8.4-5.5-0.2</t>
-  </si>
-  <si>
-    <t>7.4-6.5-0.1</t>
-  </si>
-  <si>
-    <t>5.9-8.0-0.1</t>
-  </si>
-  <si>
-    <t>4.8-9.1-0.1</t>
-  </si>
-  <si>
-    <t>4.7-9.2-0.1</t>
-  </si>
-  <si>
-    <t>4.0-9.9-0.1</t>
-  </si>
-  <si>
-    <t>2.8-11.1-0.1</t>
-  </si>
-  <si>
-    <t>2.7-11.2-0.1</t>
+    <t>9.1-4.8-0.1</t>
+  </si>
+  <si>
+    <t>8.2-5.7-0.1</t>
+  </si>
+  <si>
+    <t>7.6-6.2-0.1</t>
+  </si>
+  <si>
+    <t>6.9-7.0-0.1</t>
+  </si>
+  <si>
+    <t>5.8-8.1-0.1</t>
+  </si>
+  <si>
+    <t>4.4-9.5-0.1</t>
+  </si>
+  <si>
+    <t>3.2-10.7-0.1</t>
+  </si>
+  <si>
+    <t>3.0-10.9-0.1</t>
+  </si>
+  <si>
+    <t>2.4-11.5-0.1</t>
   </si>
   <si>
     <t>11-3</t>
   </si>
   <si>
+    <t>9-5</t>
+  </si>
+  <si>
     <t>10-4</t>
   </si>
   <si>
-    <t>9-5</t>
-  </si>
-  <si>
     <t>8-6</t>
   </si>
   <si>
@@ -322,15 +325,15 @@
     <t>6-8</t>
   </si>
   <si>
-    <t>5-9</t>
-  </si>
-  <si>
     <t>4-10</t>
   </si>
   <si>
     <t>3-11</t>
   </si>
   <si>
+    <t>2-12</t>
+  </si>
+  <si>
     <t>Owners</t>
   </si>
   <si>
@@ -343,27 +346,33 @@
     <t>↑2</t>
   </si>
   <si>
+    <t>↑3</t>
+  </si>
+  <si>
+    <t>↑6</t>
+  </si>
+  <si>
+    <t>↓4</t>
+  </si>
+  <si>
+    <t>↓5</t>
+  </si>
+  <si>
     <t>0</t>
   </si>
   <si>
-    <t>↑3</t>
-  </si>
-  <si>
-    <t>↑4</t>
-  </si>
-  <si>
-    <t>↓2</t>
-  </si>
-  <si>
-    <t>↓5</t>
-  </si>
-  <si>
-    <t>↑5</t>
+    <t>↑1</t>
   </si>
   <si>
     <t>↓3</t>
   </si>
   <si>
+    <t>↓1</t>
+  </si>
+  <si>
+    <t>↓7</t>
+  </si>
+  <si>
     <t>Week 1</t>
   </si>
   <si>
@@ -374,6 +383,9 @@
   </si>
   <si>
     <t>Week 4</t>
+  </si>
+  <si>
+    <t>Week 5</t>
   </si>
   <si>
     <t>Week</t>
@@ -807,43 +819,43 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -854,10 +866,10 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
         <v>15</v>
@@ -869,28 +881,28 @@
         <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I3" t="s">
         <v>15</v>
       </c>
       <c r="J3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" t="s">
         <v>17</v>
       </c>
-      <c r="L3" t="s">
-        <v>15</v>
-      </c>
-      <c r="M3" t="s">
-        <v>15</v>
-      </c>
-      <c r="N3" t="s">
-        <v>16</v>
-      </c>
       <c r="O3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -898,46 +910,46 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -948,10 +960,10 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
         <v>18</v>
@@ -960,19 +972,19 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I5" t="s">
         <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L5" t="s">
         <v>15</v>
@@ -981,10 +993,10 @@
         <v>15</v>
       </c>
       <c r="N5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -992,46 +1004,46 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G6" t="s">
         <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K6" t="s">
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -1042,13 +1054,13 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F7" t="s">
         <v>15</v>
@@ -1057,28 +1069,28 @@
         <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N7" t="s">
         <v>15</v>
       </c>
       <c r="O7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -1086,46 +1098,46 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -1136,28 +1148,28 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F9" t="s">
         <v>14</v>
       </c>
       <c r="G9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H9" t="s">
         <v>14</v>
       </c>
       <c r="I9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K9" t="s">
         <v>14</v>
@@ -1166,13 +1178,13 @@
         <v>15</v>
       </c>
       <c r="M9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -1180,46 +1192,46 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1227,22 +1239,22 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E11" t="s">
         <v>15</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H11" t="s">
         <v>14</v>
@@ -1260,13 +1272,13 @@
         <v>15</v>
       </c>
       <c r="M11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N11" t="s">
         <v>14</v>
       </c>
       <c r="O11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -1274,40 +1286,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" t="s">
         <v>17</v>
       </c>
-      <c r="F12" t="s">
-        <v>16</v>
-      </c>
       <c r="G12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N12" t="s">
         <v>15</v>
@@ -1321,46 +1333,46 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G13" t="s">
         <v>18</v>
       </c>
       <c r="H13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I13" t="s">
         <v>15</v>
       </c>
       <c r="J13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -1368,20 +1380,20 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" t="s">
         <v>17</v>
       </c>
-      <c r="C14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" t="s">
-        <v>17</v>
-      </c>
-      <c r="F14" t="s">
-        <v>16</v>
-      </c>
       <c r="G14" t="s">
         <v>18</v>
       </c>
@@ -1392,22 +1404,22 @@
         <v>15</v>
       </c>
       <c r="J14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N14" t="s">
         <v>15</v>
       </c>
       <c r="O14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:15">
@@ -1418,43 +1430,43 @@
         <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G15" t="s">
         <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I15" t="s">
         <v>15</v>
       </c>
       <c r="J15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1469,25 +1481,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1521,25 +1533,25 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E3">
-        <v>-3</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>-8</v>
       </c>
       <c r="G3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1547,25 +1559,25 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E4">
+        <v>-3</v>
+      </c>
+      <c r="F4">
+        <v>9</v>
+      </c>
+      <c r="G4">
+        <v>12</v>
+      </c>
+      <c r="H4" t="s">
         <v>5</v>
-      </c>
-      <c r="F4">
-        <v>-4</v>
-      </c>
-      <c r="G4">
-        <v>9</v>
-      </c>
-      <c r="H4" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1576,22 +1588,22 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="F5">
         <v>-4</v>
       </c>
       <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5" t="s">
         <v>6</v>
-      </c>
-      <c r="H5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1599,25 +1611,25 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="F6">
+        <v>-4</v>
+      </c>
+      <c r="G6">
         <v>6</v>
       </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
       <c r="H6" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1625,22 +1637,22 @@
         <v>5</v>
       </c>
       <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" t="s">
         <v>2</v>
       </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" t="s">
-        <v>3</v>
-      </c>
       <c r="E7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7" t="s">
         <v>3</v>
@@ -1651,25 +1663,25 @@
         <v>6</v>
       </c>
       <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
         <v>3</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8">
         <v>4</v>
       </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8">
-        <v>5</v>
-      </c>
       <c r="F8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8">
+        <v>4</v>
+      </c>
+      <c r="H8" t="s">
         <v>3</v>
-      </c>
-      <c r="H8" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1677,25 +1689,25 @@
         <v>7</v>
       </c>
       <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9" t="s">
         <v>4</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
+      <c r="F9">
         <v>2</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9">
-        <v>8</v>
-      </c>
-      <c r="F9">
-        <v>11</v>
       </c>
       <c r="G9">
         <v>3</v>
       </c>
       <c r="H9" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1706,22 +1718,22 @@
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G10">
+        <v>3</v>
+      </c>
+      <c r="H10" t="s">
         <v>2</v>
-      </c>
-      <c r="H10" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1729,25 +1741,25 @@
         <v>9</v>
       </c>
       <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>6</v>
+      </c>
+      <c r="F11">
+        <v>8</v>
+      </c>
+      <c r="G11">
         <v>2</v>
       </c>
-      <c r="C11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11">
-        <v>2</v>
-      </c>
-      <c r="F11">
-        <v>3</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
       <c r="H11" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1762,13 +1774,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1776,13 +1788,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>1.357142857142857</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1793,10 +1805,10 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>1.5</v>
+        <v>1.928571428571429</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1804,13 +1816,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C4">
-        <v>1.571428571428571</v>
+        <v>2.071428571428572</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1818,13 +1830,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>1.642857142857143</v>
+        <v>2.214285714285714</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1832,10 +1844,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>1.642857142857143</v>
+        <v>2.214285714285714</v>
       </c>
       <c r="D6" t="s">
         <v>15</v>
@@ -1846,10 +1858,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>1.928571428571429</v>
+        <v>2.285714285714286</v>
       </c>
       <c r="D7" t="s">
         <v>16</v>
@@ -1860,13 +1872,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>2.285714285714286</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1874,13 +1886,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>2.071428571428572</v>
+        <v>2.285714285714286</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1888,13 +1900,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>2.142857142857143</v>
+        <v>2.642857142857143</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1902,13 +1914,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C11">
-        <v>2.142857142857143</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1916,13 +1928,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C12">
-        <v>2.142857142857143</v>
+        <v>2.857142857142857</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1930,13 +1942,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C13">
-        <v>2.357142857142857</v>
+        <v>2.928571428571428</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1944,13 +1956,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C14">
-        <v>2.571428571428572</v>
+        <v>2.928571428571428</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1961,10 +1973,10 @@
         <v>13</v>
       </c>
       <c r="C15">
-        <v>2.928571428571428</v>
+        <v>3.785714285714286</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1979,16 +1991,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1999,13 +2011,13 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>3.142857142857143</v>
+        <v>4.142857142857143</v>
       </c>
       <c r="D2">
-        <v>0.1428571428571428</v>
+        <v>0.1428571428571432</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2016,13 +2028,13 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>2.642857142857143</v>
+        <v>3.571428571428572</v>
       </c>
       <c r="D3">
-        <v>-0.3571428571428572</v>
+        <v>-0.4285714285714284</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2030,16 +2042,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C4">
-        <v>2.642857142857143</v>
+        <v>3.285714285714286</v>
       </c>
       <c r="D4">
-        <v>0.6428571428571428</v>
+        <v>-0.7142857142857144</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2047,16 +2059,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5">
-        <v>2.571428571428572</v>
+        <v>3.142857142857143</v>
       </c>
       <c r="D5">
-        <v>-0.4285714285714284</v>
+        <v>-0.8571428571428572</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2064,13 +2076,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>2.571428571428572</v>
+        <v>2.928571428571428</v>
       </c>
       <c r="D6">
-        <v>0.5714285714285716</v>
+        <v>0.9285714285714284</v>
       </c>
       <c r="E6" t="s">
         <v>15</v>
@@ -2084,10 +2096,10 @@
         <v>3</v>
       </c>
       <c r="C7">
-        <v>2.5</v>
+        <v>2.857142857142857</v>
       </c>
       <c r="D7">
-        <v>-1.5</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -2098,16 +2110,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>2.5</v>
+        <v>2.642857142857143</v>
       </c>
       <c r="D8">
-        <v>-0.5</v>
+        <v>0.6428571428571428</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2115,13 +2127,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>2.642857142857143</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>0.6428571428571428</v>
       </c>
       <c r="E9" t="s">
         <v>15</v>
@@ -2132,13 +2144,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>1.785714285714286</v>
+        <v>2.5</v>
       </c>
       <c r="D10">
-        <v>0.7857142857142858</v>
+        <v>-0.5</v>
       </c>
       <c r="E10" t="s">
         <v>16</v>
@@ -2149,13 +2161,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C11">
-        <v>1.285714285714286</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>-0.7142857142857142</v>
+        <v>0</v>
       </c>
       <c r="E11" t="s">
         <v>15</v>
@@ -2169,10 +2181,10 @@
         <v>0</v>
       </c>
       <c r="C12">
-        <v>1.285714285714286</v>
+        <v>1.785714285714286</v>
       </c>
       <c r="D12">
-        <v>1.285714285714286</v>
+        <v>1.785714285714286</v>
       </c>
       <c r="E12" t="s">
         <v>14</v>
@@ -2183,16 +2195,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C13">
-        <v>1.214285714285714</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="D13">
-        <v>0.2142857142857142</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="E13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2209,7 +2221,7 @@
         <v>0.2142857142857142</v>
       </c>
       <c r="E14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2220,13 +2232,13 @@
         <v>7</v>
       </c>
       <c r="C15">
-        <v>0.6428571428571429</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D15">
-        <v>-0.3571428571428571</v>
+        <v>-0.1428571428571429</v>
       </c>
       <c r="E15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -2241,84 +2253,84 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B2">
-        <v>28.6</v>
+        <v>51.6</v>
       </c>
       <c r="C2">
-        <v>21.3</v>
+        <v>21.9</v>
       </c>
       <c r="D2">
-        <v>16.6</v>
+        <v>12.1</v>
       </c>
       <c r="E2">
-        <v>14.1</v>
+        <v>6.8</v>
       </c>
       <c r="F2">
-        <v>8.6</v>
+        <v>3.9</v>
       </c>
       <c r="G2">
-        <v>6.3</v>
+        <v>1.8</v>
       </c>
       <c r="H2">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J2">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="K2">
         <v>0.1</v>
@@ -2336,42 +2348,42 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>95.5</v>
+        <v>98.09999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>29.6</v>
+        <v>29.9</v>
       </c>
       <c r="C3">
-        <v>23.9</v>
+        <v>32.3</v>
       </c>
       <c r="D3">
-        <v>16.6</v>
+        <v>17.7</v>
       </c>
       <c r="E3">
-        <v>11.3</v>
+        <v>8.5</v>
       </c>
       <c r="F3">
-        <v>8.1</v>
+        <v>5.4</v>
       </c>
       <c r="G3">
-        <v>5.8</v>
+        <v>3.6</v>
       </c>
       <c r="H3">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="I3">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J3">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="K3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -2386,45 +2398,45 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>95.3</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B4">
-        <v>20.3</v>
+        <v>7</v>
       </c>
       <c r="C4">
-        <v>20.9</v>
+        <v>12.2</v>
       </c>
       <c r="D4">
-        <v>16.8</v>
+        <v>16.1</v>
       </c>
       <c r="E4">
-        <v>14.3</v>
+        <v>20.2</v>
       </c>
       <c r="F4">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>7.8</v>
+        <v>14</v>
       </c>
       <c r="H4">
-        <v>5.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I4">
-        <v>2.7</v>
+        <v>4.9</v>
       </c>
       <c r="J4">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="K4">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="L4">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -2436,42 +2448,42 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>90.59999999999999</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5">
-        <v>8.6</v>
+        <v>5.4</v>
       </c>
       <c r="C5">
-        <v>13.4</v>
+        <v>11.7</v>
       </c>
       <c r="D5">
-        <v>16.2</v>
+        <v>17.9</v>
       </c>
       <c r="E5">
-        <v>16.6</v>
+        <v>18.7</v>
       </c>
       <c r="F5">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="G5">
-        <v>12.3</v>
+        <v>9.1</v>
       </c>
       <c r="H5">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="I5">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="J5">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -2486,45 +2498,45 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>85.3</v>
+        <v>80.90000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="C6">
-        <v>6.6</v>
+        <v>12.4</v>
       </c>
       <c r="D6">
-        <v>11.4</v>
+        <v>14.6</v>
       </c>
       <c r="E6">
-        <v>14.1</v>
+        <v>17</v>
       </c>
       <c r="F6">
-        <v>17</v>
+        <v>16.4</v>
       </c>
       <c r="G6">
-        <v>18.8</v>
+        <v>15.1</v>
       </c>
       <c r="H6">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>5.9</v>
       </c>
       <c r="J6">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="K6">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="L6">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -2536,98 +2548,98 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>72.3</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="C7">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="D7">
-        <v>9</v>
+        <v>11.9</v>
       </c>
       <c r="E7">
-        <v>11.3</v>
+        <v>14.4</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>16.1</v>
       </c>
       <c r="G7">
-        <v>14.6</v>
+        <v>17.3</v>
       </c>
       <c r="H7">
-        <v>16.5</v>
+        <v>13.6</v>
       </c>
       <c r="I7">
-        <v>14.8</v>
+        <v>10.5</v>
       </c>
       <c r="J7">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="K7">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="L7">
         <v>0.3</v>
       </c>
       <c r="M7">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="N7">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>60.5</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B8">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="C8">
-        <v>6.2</v>
+        <v>1.8</v>
       </c>
       <c r="D8">
-        <v>9.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="E8">
-        <v>9.4</v>
+        <v>6.9</v>
       </c>
       <c r="F8">
+        <v>9.5</v>
+      </c>
+      <c r="G8">
         <v>14.1</v>
       </c>
-      <c r="G8">
-        <v>17</v>
-      </c>
       <c r="H8">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="I8">
-        <v>15.2</v>
+        <v>16.1</v>
       </c>
       <c r="J8">
-        <v>5.2</v>
+        <v>16.2</v>
       </c>
       <c r="K8">
-        <v>1.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L8">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="M8">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -2636,107 +2648,107 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>59.2</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B9">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D9">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="E9">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="F9">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
       <c r="G9">
-        <v>12</v>
+        <v>12.8</v>
       </c>
       <c r="H9">
-        <v>17.6</v>
+        <v>13.8</v>
       </c>
       <c r="I9">
-        <v>23.5</v>
+        <v>19.3</v>
       </c>
       <c r="J9">
-        <v>15.6</v>
+        <v>21.1</v>
       </c>
       <c r="K9">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="L9">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="M9">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="N9">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P9">
-        <v>31.9</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="C10">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="D10">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="E10">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="F10">
-        <v>1.5</v>
+        <v>6.4</v>
       </c>
       <c r="G10">
-        <v>3.7</v>
+        <v>9</v>
       </c>
       <c r="H10">
-        <v>9.199999999999999</v>
+        <v>14.4</v>
       </c>
       <c r="I10">
-        <v>17.5</v>
+        <v>22.2</v>
       </c>
       <c r="J10">
-        <v>31.1</v>
+        <v>22.2</v>
       </c>
       <c r="K10">
-        <v>18.6</v>
+        <v>14.6</v>
       </c>
       <c r="L10">
-        <v>8.9</v>
+        <v>4.2</v>
       </c>
       <c r="M10">
-        <v>5.3</v>
+        <v>1.1</v>
       </c>
       <c r="N10">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="O10">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="P10">
-        <v>7</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2747,46 +2759,46 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E11">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F11">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="H11">
-        <v>2.1</v>
+        <v>5.7</v>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="J11">
-        <v>13</v>
+        <v>19.3</v>
       </c>
       <c r="K11">
-        <v>22.9</v>
+        <v>33.6</v>
       </c>
       <c r="L11">
-        <v>22.3</v>
+        <v>14.6</v>
       </c>
       <c r="M11">
-        <v>16.1</v>
+        <v>6.8</v>
       </c>
       <c r="N11">
-        <v>11.3</v>
+        <v>2.7</v>
       </c>
       <c r="O11">
-        <v>6</v>
+        <v>0.4</v>
       </c>
       <c r="P11">
-        <v>1.3</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2803,40 +2815,40 @@
         <v>0</v>
       </c>
       <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
         <v>0.1</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>0.2</v>
       </c>
-      <c r="G12">
-        <v>0.5</v>
-      </c>
       <c r="H12">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="I12">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="J12">
-        <v>13.4</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>23.3</v>
+        <v>16.4</v>
       </c>
       <c r="L12">
-        <v>25.3</v>
+        <v>38</v>
       </c>
       <c r="M12">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N12">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="O12">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="P12">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2853,40 +2865,40 @@
         <v>0</v>
       </c>
       <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
         <v>0.1</v>
       </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0.2</v>
-      </c>
       <c r="H13">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="J13">
-        <v>6.6</v>
+        <v>1.4</v>
       </c>
       <c r="K13">
-        <v>14.2</v>
+        <v>3.7</v>
       </c>
       <c r="L13">
-        <v>22.8</v>
+        <v>15.7</v>
       </c>
       <c r="M13">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="N13">
-        <v>19.9</v>
+        <v>32.2</v>
       </c>
       <c r="O13">
-        <v>8.1</v>
+        <v>18.6</v>
       </c>
       <c r="P13">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2912,28 +2924,28 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="I14">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J14">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="K14">
-        <v>6.1</v>
+        <v>7.2</v>
       </c>
       <c r="L14">
-        <v>11.1</v>
+        <v>16.8</v>
       </c>
       <c r="M14">
-        <v>19.3</v>
+        <v>27</v>
       </c>
       <c r="N14">
-        <v>30.3</v>
+        <v>26.3</v>
       </c>
       <c r="O14">
-        <v>31.3</v>
+        <v>21</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -2968,22 +2980,22 @@
         <v>0.2</v>
       </c>
       <c r="J15">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="K15">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="L15">
-        <v>5.7</v>
+        <v>3.7</v>
       </c>
       <c r="M15">
-        <v>13.3</v>
+        <v>12.4</v>
       </c>
       <c r="N15">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="O15">
-        <v>52.6</v>
+        <v>57.3</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -2996,275 +3008,314 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>45</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B2">
-        <v>95.39999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="C2">
-        <v>32.8</v>
+        <v>31.6</v>
       </c>
       <c r="D2">
-        <v>77</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E2">
-        <v>95.59999999999999</v>
+        <v>96.89999999999999</v>
       </c>
       <c r="F2">
-        <v>95.09999999999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>99.8</v>
+      </c>
+      <c r="G2">
+        <v>97.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>93</v>
+      </c>
+      <c r="C3">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="D3">
+        <v>60.4</v>
+      </c>
+      <c r="E3">
+        <v>83.7</v>
+      </c>
+      <c r="F3">
+        <v>96.39999999999999</v>
+      </c>
+      <c r="G3">
+        <v>97.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
-        <v>6.3</v>
-      </c>
-      <c r="C3">
-        <v>88.90000000000001</v>
-      </c>
-      <c r="D3">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="E3">
-        <v>92.80000000000001</v>
-      </c>
-      <c r="F3">
-        <v>94.3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1" t="s">
+      <c r="B4">
+        <v>6.800000000000001</v>
+      </c>
+      <c r="C4">
+        <v>89.8</v>
+      </c>
+      <c r="D4">
+        <v>77.7</v>
+      </c>
+      <c r="E4">
+        <v>93.5</v>
+      </c>
+      <c r="F4">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="G4">
+        <v>80.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5">
+        <v>99.2</v>
+      </c>
+      <c r="C5">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="D5">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="E5">
+        <v>60.9</v>
+      </c>
+      <c r="F5">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="G5">
+        <v>79.10000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
+        <v>25.5</v>
+      </c>
+      <c r="C6">
+        <v>30.4</v>
+      </c>
+      <c r="D6">
+        <v>78.3</v>
+      </c>
+      <c r="E6">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="F6">
+        <v>81</v>
+      </c>
+      <c r="G6">
+        <v>78.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
         <v>67.90000000000001</v>
       </c>
-      <c r="D4">
-        <v>49.3</v>
-      </c>
-      <c r="E4">
-        <v>92</v>
-      </c>
-      <c r="F4">
-        <v>92.10000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>94</v>
-      </c>
-      <c r="C5">
-        <v>98.3</v>
-      </c>
-      <c r="D5">
-        <v>60.09999999999999</v>
-      </c>
-      <c r="E5">
-        <v>82.3</v>
-      </c>
-      <c r="F5">
-        <v>84.09999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1" t="s">
+      <c r="D7">
+        <v>48.9</v>
+      </c>
+      <c r="E7">
+        <v>92.60000000000001</v>
+      </c>
+      <c r="F7">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="G7">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>100</v>
+      </c>
+      <c r="C8">
+        <v>97</v>
+      </c>
+      <c r="D8">
+        <v>63.6</v>
+      </c>
+      <c r="E8">
+        <v>25</v>
+      </c>
+      <c r="F8">
+        <v>40.2</v>
+      </c>
+      <c r="G8">
+        <v>36.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <v>70.5</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>11.2</v>
+      </c>
+      <c r="F9">
+        <v>33.1</v>
+      </c>
+      <c r="G9">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6">
-        <v>78.60000000000001</v>
-      </c>
-      <c r="C6">
-        <v>77.3</v>
-      </c>
-      <c r="D6">
-        <v>93.89999999999999</v>
-      </c>
-      <c r="E6">
-        <v>69.19999999999999</v>
-      </c>
-      <c r="F6">
-        <v>69.69999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="C7">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="D7">
-        <v>98</v>
-      </c>
-      <c r="E7">
-        <v>57.4</v>
-      </c>
-      <c r="F7">
-        <v>63.1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8">
-        <v>29.4</v>
-      </c>
-      <c r="C8">
-        <v>29.2</v>
-      </c>
-      <c r="D8">
-        <v>77.2</v>
-      </c>
-      <c r="E8">
-        <v>66.5</v>
-      </c>
-      <c r="F8">
-        <v>59.09999999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9">
-        <v>100</v>
-      </c>
-      <c r="C9">
-        <v>96.8</v>
-      </c>
-      <c r="D9">
-        <v>61.8</v>
-      </c>
-      <c r="E9">
-        <v>29.6</v>
-      </c>
-      <c r="F9">
-        <v>31.1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="B10">
-        <v>66</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="C10">
-        <v>6.1</v>
+        <v>77.7</v>
       </c>
       <c r="D10">
-        <v>1.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="E10">
-        <v>12.8</v>
+        <v>67.5</v>
       </c>
       <c r="F10">
-        <v>9.199999999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>21.8</v>
+      </c>
+      <c r="G10">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B11">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="C11">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="F11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>6.7</v>
+      </c>
+      <c r="G11">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B12">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="C12">
+        <v>0.5</v>
+      </c>
+      <c r="D12">
+        <v>0.1</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>0.1</v>
+      </c>
+      <c r="G12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13">
+        <v>14.1</v>
+      </c>
+      <c r="C13">
+        <v>1.8</v>
+      </c>
+      <c r="D13">
         <v>0.3</v>
-      </c>
-      <c r="D12">
-        <v>0.2</v>
-      </c>
-      <c r="E12">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="F12">
-        <v>0.7000000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13">
-        <v>2.1</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>1.9</v>
       </c>
       <c r="E13">
         <v>0.1</v>
       </c>
       <c r="F13">
+        <v>0.1</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14">
+        <v>10.5</v>
+      </c>
+      <c r="C14">
         <v>0.4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14">
-        <v>15.5</v>
-      </c>
-      <c r="C14">
-        <v>1.5</v>
       </c>
       <c r="D14">
         <v>0.4</v>
@@ -3273,26 +3324,32 @@
         <v>0</v>
       </c>
       <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15">
+        <v>2.4</v>
+      </c>
+      <c r="C15">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15">
-        <v>11.2</v>
-      </c>
-      <c r="C15">
-        <v>0.8999999999999999</v>
-      </c>
       <c r="D15">
+        <v>1.9</v>
+      </c>
+      <c r="E15">
+        <v>0.2</v>
+      </c>
+      <c r="F15">
         <v>0.1</v>
       </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
+      <c r="G15">
         <v>0</v>
       </c>
     </row>
@@ -3308,28 +3365,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3340,25 +3397,25 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D2">
-        <v>76.83</v>
+        <v>78.58</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>104.5</v>
+        <v>107.44</v>
       </c>
       <c r="G2">
-        <v>0.575</v>
+        <v>0.6</v>
       </c>
       <c r="H2">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3366,28 +3423,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3">
+        <v>84.54000000000001</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3">
+        <v>104.46</v>
+      </c>
+      <c r="G3">
+        <v>0.578</v>
+      </c>
+      <c r="H3">
+        <v>2.3</v>
+      </c>
+      <c r="I3">
         <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3">
-        <v>88.48999999999999</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3">
-        <v>104.03</v>
-      </c>
-      <c r="G3">
-        <v>0.55</v>
-      </c>
-      <c r="H3">
-        <v>2.5</v>
-      </c>
-      <c r="I3">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3398,25 +3455,25 @@
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D4">
-        <v>88.16</v>
+        <v>92.38</v>
       </c>
       <c r="E4" t="s">
         <v>14</v>
       </c>
       <c r="F4">
-        <v>103.34</v>
+        <v>105.16</v>
       </c>
       <c r="G4">
-        <v>0.575</v>
+        <v>0.6</v>
       </c>
       <c r="H4">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3424,28 +3481,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D5">
-        <v>87.66</v>
+        <v>107.63</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5">
-        <v>103.17</v>
+        <v>103.14</v>
       </c>
       <c r="G5">
-        <v>0.575</v>
+        <v>0.533</v>
       </c>
       <c r="H5">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3453,28 +3510,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D6">
-        <v>101.02</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F6">
-        <v>101.16</v>
+        <v>101.91</v>
       </c>
       <c r="G6">
-        <v>0.5</v>
+        <v>0.444</v>
       </c>
       <c r="H6">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3482,28 +3539,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D7">
-        <v>104.31</v>
+        <v>123.19</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>99.73999999999999</v>
+        <v>101.07</v>
       </c>
       <c r="G7">
-        <v>0.475</v>
+        <v>0.511</v>
       </c>
       <c r="H7">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3511,28 +3568,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D8">
-        <v>105.19</v>
+        <v>87.8</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F8">
-        <v>101.56</v>
+        <v>103.41</v>
       </c>
       <c r="G8">
-        <v>0.525</v>
+        <v>0.533</v>
       </c>
       <c r="H8">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3540,28 +3597,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D9">
-        <v>88.66</v>
+        <v>108.08</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F9">
-        <v>99.23</v>
+        <v>101.93</v>
       </c>
       <c r="G9">
-        <v>0.45</v>
+        <v>0.467</v>
       </c>
       <c r="H9">
-        <v>-0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="I9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3569,28 +3626,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D10">
-        <v>107.66</v>
+        <v>101.91</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F10">
-        <v>97.12</v>
+        <v>100.56</v>
       </c>
       <c r="G10">
-        <v>0.4</v>
+        <v>0.556</v>
       </c>
       <c r="H10">
-        <v>-1.2</v>
+        <v>-0.3</v>
       </c>
       <c r="I10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3598,28 +3655,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D11">
-        <v>114.64</v>
+        <v>105.76</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F11">
-        <v>97.62</v>
+        <v>100.67</v>
       </c>
       <c r="G11">
-        <v>0.5</v>
+        <v>0.467</v>
       </c>
       <c r="H11">
-        <v>-1.2</v>
+        <v>-0.3</v>
       </c>
       <c r="I11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3627,28 +3684,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D12">
-        <v>108.52</v>
+        <v>104.62</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F12">
-        <v>98.69</v>
+        <v>98.33</v>
       </c>
       <c r="G12">
-        <v>0.45</v>
+        <v>0.378</v>
       </c>
       <c r="H12">
-        <v>-1.3</v>
+        <v>-1.7</v>
       </c>
       <c r="I12">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3656,28 +3713,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D13">
-        <v>101.29</v>
+        <v>101.45</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
       </c>
       <c r="F13">
-        <v>97.56999999999999</v>
+        <v>97.70999999999999</v>
       </c>
       <c r="G13">
-        <v>0.525</v>
+        <v>0.422</v>
       </c>
       <c r="H13">
-        <v>-2.2</v>
+        <v>-1.8</v>
       </c>
       <c r="I13">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -3685,28 +3742,28 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D14">
-        <v>107.31</v>
+        <v>115.84</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F14">
-        <v>95.63</v>
+        <v>98.87</v>
       </c>
       <c r="G14">
-        <v>0.425</v>
+        <v>0.467</v>
       </c>
       <c r="H14">
         <v>-2.3</v>
       </c>
       <c r="I14">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -3717,25 +3774,25 @@
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D15">
-        <v>119.25</v>
+        <v>113.69</v>
       </c>
       <c r="E15" t="s">
         <v>15</v>
       </c>
       <c r="F15">
-        <v>95.65000000000001</v>
+        <v>96.06999999999999</v>
       </c>
       <c r="G15">
-        <v>0.475</v>
+        <v>0.444</v>
       </c>
       <c r="H15">
-        <v>-3.7</v>
+        <v>-4.8</v>
       </c>
       <c r="I15">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3750,86 +3807,86 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D2">
-        <v>107.655</v>
+        <v>123.192</v>
       </c>
       <c r="E2">
-        <v>430.62</v>
+        <v>615.96</v>
       </c>
       <c r="F2">
-        <v>95.5</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C3">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="D3">
-        <v>114.645</v>
+        <v>115.836</v>
       </c>
       <c r="E3">
-        <v>458.58</v>
+        <v>579.1799999999999</v>
       </c>
       <c r="F3">
-        <v>95.3</v>
+        <v>97.39999999999999</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I3" t="s">
         <v>94</v>
@@ -3837,86 +3894,86 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>76</v>
       </c>
       <c r="C4">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="D4">
-        <v>119.25</v>
+        <v>108.084</v>
       </c>
       <c r="E4">
-        <v>477</v>
+        <v>540.42</v>
       </c>
       <c r="F4">
-        <v>90.60000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C5">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="D5">
-        <v>108.52</v>
+        <v>104.624</v>
       </c>
       <c r="E5">
-        <v>434.08</v>
+        <v>523.12</v>
       </c>
       <c r="F5">
-        <v>85.3</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
         <v>76</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="D6">
-        <v>107.31</v>
+        <v>105.764</v>
       </c>
       <c r="E6">
-        <v>429.24</v>
+        <v>528.8199999999999</v>
       </c>
       <c r="F6">
-        <v>72.3</v>
+        <v>79</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I6" t="s">
         <v>95</v>
@@ -3924,115 +3981,115 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C7">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="D7">
-        <v>104.315</v>
+        <v>113.688</v>
       </c>
       <c r="E7">
-        <v>417.26</v>
+        <v>568.4400000000001</v>
       </c>
       <c r="F7">
-        <v>60.5</v>
+        <v>67.60000000000001</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C8">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="D8">
-        <v>105.195</v>
+        <v>101.912</v>
       </c>
       <c r="E8">
-        <v>420.78</v>
+        <v>509.5599999999999</v>
       </c>
       <c r="F8">
-        <v>59.2</v>
+        <v>38.4</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C9">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D9">
-        <v>101.29</v>
+        <v>107.628</v>
       </c>
       <c r="E9">
-        <v>405.16</v>
+        <v>538.1399999999999</v>
       </c>
       <c r="F9">
-        <v>31.9</v>
+        <v>28.5</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>77</v>
       </c>
       <c r="C10">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="D10">
-        <v>101.02</v>
+        <v>101.448</v>
       </c>
       <c r="E10">
-        <v>404.0799999999999</v>
+        <v>507.24</v>
       </c>
       <c r="F10">
-        <v>7.000000000000001</v>
+        <v>20.8</v>
       </c>
       <c r="G10">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="H10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I10" t="s">
         <v>98</v>
@@ -4046,22 +4103,22 @@
         <v>77</v>
       </c>
       <c r="C11">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="D11">
-        <v>88.66499999999999</v>
+        <v>95.26399999999998</v>
       </c>
       <c r="E11">
-        <v>354.66</v>
+        <v>476.3199999999999</v>
       </c>
       <c r="F11">
-        <v>1.3</v>
+        <v>5.4</v>
       </c>
       <c r="G11">
-        <v>6</v>
+        <v>0.4</v>
       </c>
       <c r="H11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I11" t="s">
         <v>99</v>
@@ -4072,28 +4129,28 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C12">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D12">
-        <v>88.49499999999999</v>
+        <v>87.79599999999999</v>
       </c>
       <c r="E12">
-        <v>353.98</v>
+        <v>438.98</v>
       </c>
       <c r="F12">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="G12">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="H12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -4101,28 +4158,28 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C13">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D13">
-        <v>87.655</v>
+        <v>84.54400000000001</v>
       </c>
       <c r="E13">
-        <v>350.62</v>
+        <v>422.72</v>
       </c>
       <c r="F13">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="G13">
-        <v>8.1</v>
+        <v>18.6</v>
       </c>
       <c r="H13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -4130,25 +4187,25 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>88.16499999999999</v>
+        <v>92.376</v>
       </c>
       <c r="E14">
-        <v>352.66</v>
+        <v>461.88</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>31.3</v>
+        <v>21</v>
       </c>
       <c r="H14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I14" t="s">
         <v>101</v>
@@ -4159,28 +4216,28 @@
         <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C15">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D15">
-        <v>76.83</v>
+        <v>78.57599999999999</v>
       </c>
       <c r="E15">
-        <v>307.32</v>
+        <v>392.88</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>52.6</v>
+        <v>57.3</v>
       </c>
       <c r="H15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -4195,19 +4252,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4218,16 +4275,16 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4235,19 +4292,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D3">
         <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4255,19 +4312,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4275,10 +4332,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D5">
         <v>8</v>
@@ -4287,7 +4344,7 @@
         <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4295,19 +4352,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
         <v>65</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="s">
         <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4318,16 +4375,16 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4335,10 +4392,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D8">
         <v>3</v>
@@ -4347,7 +4404,7 @@
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4358,7 +4415,7 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D9">
         <v>-1</v>
@@ -4367,7 +4424,7 @@
         <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4378,16 +4435,16 @@
         <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D10">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="E10" t="s">
         <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4398,16 +4455,16 @@
         <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D11">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="E11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4418,16 +4475,16 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D12">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4438,10 +4495,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D13">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
@@ -4455,19 +4512,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14">
-        <v>-14</v>
+        <v>-16</v>
       </c>
       <c r="E14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F14" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4475,19 +4532,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D15">
-        <v>-15</v>
+        <v>-21</v>
       </c>
       <c r="E15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F15" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -4497,27 +4554,30 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>120</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -4533,91 +4593,106 @@
       <c r="E2">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="F2">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
+      <c r="E3">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>9</v>
+      </c>
+      <c r="G4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>-9</v>
+      </c>
+      <c r="C5">
+        <v>-3</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="G5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3">
+      <c r="B6">
         <v>-2</v>
       </c>
-      <c r="C3">
+      <c r="C6">
         <v>4</v>
       </c>
-      <c r="D3">
+      <c r="D6">
         <v>11</v>
       </c>
-      <c r="E3">
+      <c r="E6">
         <v>11</v>
       </c>
-      <c r="F3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>6</v>
-      </c>
-      <c r="C4">
+      <c r="F6">
         <v>7</v>
       </c>
-      <c r="D4">
-        <v>6</v>
-      </c>
-      <c r="E4">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5">
-        <v>6</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>-9</v>
-      </c>
-      <c r="C6">
-        <v>-3</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="G6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -4633,31 +4708,37 @@
       <c r="E7">
         <v>5</v>
       </c>
-      <c r="F7" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="F7">
+        <v>7</v>
+      </c>
+      <c r="G7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8">
+        <v>8</v>
+      </c>
+      <c r="F8">
         <v>3</v>
       </c>
-      <c r="F8" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="G8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
@@ -4673,11 +4754,14 @@
       <c r="E9">
         <v>-1</v>
       </c>
-      <c r="F9" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="F9">
+        <v>-1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -4693,11 +4777,14 @@
       <c r="E10">
         <v>-4</v>
       </c>
-      <c r="F10" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="F10">
+        <v>-1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
@@ -4713,11 +4800,14 @@
       <c r="E11">
         <v>-4</v>
       </c>
-      <c r="F11" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="F11">
+        <v>-3</v>
+      </c>
+      <c r="G11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
@@ -4733,11 +4823,14 @@
       <c r="E12">
         <v>-5</v>
       </c>
-      <c r="F12" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="F12">
+        <v>-8</v>
+      </c>
+      <c r="G12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
         <v>9</v>
       </c>
@@ -4753,48 +4846,57 @@
       <c r="E13">
         <v>-10</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13">
+        <v>-9</v>
+      </c>
+      <c r="G13" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14">
+        <v>4</v>
+      </c>
+      <c r="C14">
+        <v>-5</v>
+      </c>
+      <c r="D14">
+        <v>-12</v>
+      </c>
+      <c r="E14">
+        <v>-15</v>
+      </c>
+      <c r="F14">
+        <v>-16</v>
+      </c>
+      <c r="G14" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B14">
+      <c r="B15">
         <v>-4</v>
       </c>
-      <c r="C14">
+      <c r="C15">
         <v>-15</v>
       </c>
-      <c r="D14">
+      <c r="D15">
         <v>-14</v>
       </c>
-      <c r="E14">
+      <c r="E15">
         <v>-14</v>
       </c>
-      <c r="F14" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15">
-        <v>4</v>
-      </c>
-      <c r="C15">
-        <v>-5</v>
-      </c>
-      <c r="D15">
-        <v>-12</v>
-      </c>
-      <c r="E15">
-        <v>-15</v>
-      </c>
-      <c r="F15" t="s">
-        <v>112</v>
+      <c r="F15">
+        <v>-21</v>
+      </c>
+      <c r="G15" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/BP- Loudoun 2025 2026.xlsx
+++ b/data/leagues/BP- Loudoun 2025 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="133">
   <si>
     <t>Bears, Jags, Foxes, Oh My!</t>
   </si>
@@ -67,22 +67,25 @@
     <t>Dave's Dynamos</t>
   </si>
   <si>
-    <t>0-5-0</t>
-  </si>
-  <si>
-    <t>2-3-0</t>
-  </si>
-  <si>
-    <t>3-2-0</t>
-  </si>
-  <si>
-    <t>1-4-0</t>
-  </si>
-  <si>
-    <t>4-1-0</t>
-  </si>
-  <si>
-    <t>5-0-0</t>
+    <t>0-6-0</t>
+  </si>
+  <si>
+    <t>2-4-0</t>
+  </si>
+  <si>
+    <t>3-3-0</t>
+  </si>
+  <si>
+    <t>4-2-0</t>
+  </si>
+  <si>
+    <t>1-5-0</t>
+  </si>
+  <si>
+    <t>5-1-0</t>
+  </si>
+  <si>
+    <t>6-0-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -166,6 +169,9 @@
     <t>Week_6</t>
   </si>
   <si>
+    <t>Week_7</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -190,42 +196,42 @@
     <t>Ishan Goel</t>
   </si>
   <si>
+    <t>Justin Fox</t>
+  </si>
+  <si>
+    <t>Dale Goodwin</t>
+  </si>
+  <si>
+    <t>Daniel Tracey</t>
+  </si>
+  <si>
+    <t>Chungfu Yang</t>
+  </si>
+  <si>
     <t>Roy Armbruster</t>
   </si>
   <si>
-    <t>Justin Fox</t>
+    <t>Jessica Stratton</t>
   </si>
   <si>
     <t>Hannah Davis</t>
   </si>
   <si>
-    <t>Dale Goodwin</t>
+    <t>MARVIN AYALA</t>
+  </si>
+  <si>
+    <t>Dave Linton</t>
   </si>
   <si>
     <t>Yahya Ayaz</t>
   </si>
   <si>
-    <t>Chungfu Yang</t>
-  </si>
-  <si>
-    <t>MARVIN AYALA</t>
-  </si>
-  <si>
-    <t>Jessica Stratton</t>
-  </si>
-  <si>
-    <t>Dave Linton</t>
-  </si>
-  <si>
-    <t>Daniel Tracey</t>
+    <t>Matthew Graesser</t>
   </si>
   <si>
     <t>Jeffrey Laidacker</t>
   </si>
   <si>
-    <t>Matthew Graesser</t>
-  </si>
-  <si>
     <t>Robert Schottler</t>
   </si>
   <si>
@@ -253,69 +259,72 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>4-1</t>
-  </si>
-  <si>
-    <t>2-3</t>
-  </si>
-  <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>1-4</t>
-  </si>
-  <si>
-    <t>0-5</t>
-  </si>
-  <si>
-    <t>10.7-3.2-0.1</t>
-  </si>
-  <si>
-    <t>10.5-3.4-0.1</t>
-  </si>
-  <si>
-    <t>9.2-4.7-0.1</t>
-  </si>
-  <si>
-    <t>9.3-4.5-0.1</t>
-  </si>
-  <si>
-    <t>9.1-4.8-0.1</t>
-  </si>
-  <si>
-    <t>8.2-5.7-0.1</t>
-  </si>
-  <si>
-    <t>7.6-6.2-0.1</t>
-  </si>
-  <si>
-    <t>6.9-7.0-0.1</t>
-  </si>
-  <si>
-    <t>5.8-8.1-0.1</t>
-  </si>
-  <si>
-    <t>4.4-9.5-0.1</t>
-  </si>
-  <si>
-    <t>3.2-10.7-0.1</t>
-  </si>
-  <si>
-    <t>3.0-10.9-0.1</t>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>4-2</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>0-6</t>
+  </si>
+  <si>
+    <t>1-5</t>
+  </si>
+  <si>
+    <t>10.2-3.7-0.1</t>
+  </si>
+  <si>
+    <t>9.9-4.0-0.1</t>
+  </si>
+  <si>
+    <t>9.7-4.2-0.1</t>
+  </si>
+  <si>
+    <t>9.5-4.4-0.1</t>
+  </si>
+  <si>
+    <t>9.3-4.7-0.1</t>
+  </si>
+  <si>
+    <t>8.6-5.3-0.1</t>
+  </si>
+  <si>
+    <t>7.8-6.1-0.1</t>
+  </si>
+  <si>
+    <t>6.6-7.3-0.1</t>
+  </si>
+  <si>
+    <t>6.5-7.4-0.1</t>
+  </si>
+  <si>
+    <t>6.2-7.7-0.1</t>
+  </si>
+  <si>
+    <t>5.2-8.7-0.1</t>
   </si>
   <si>
     <t>2.4-11.5-0.1</t>
   </si>
   <si>
-    <t>11-3</t>
+    <t>2.1-11.8</t>
+  </si>
+  <si>
+    <t>3.5-10.4-0.1</t>
+  </si>
+  <si>
+    <t>10-4</t>
   </si>
   <si>
     <t>9-5</t>
   </si>
   <si>
-    <t>10-4</t>
-  </si>
-  <si>
     <t>8-6</t>
   </si>
   <si>
@@ -325,15 +334,15 @@
     <t>6-8</t>
   </si>
   <si>
-    <t>4-10</t>
+    <t>5-9</t>
+  </si>
+  <si>
+    <t>2-12</t>
   </si>
   <si>
     <t>3-11</t>
   </si>
   <si>
-    <t>2-12</t>
-  </si>
-  <si>
     <t>Owners</t>
   </si>
   <si>
@@ -346,31 +355,34 @@
     <t>↑2</t>
   </si>
   <si>
+    <t>↑8</t>
+  </si>
+  <si>
     <t>↑3</t>
   </si>
   <si>
-    <t>↑6</t>
-  </si>
-  <si>
     <t>↓4</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>↑1</t>
+  </si>
+  <si>
+    <t>↓6</t>
+  </si>
+  <si>
+    <t>↓3</t>
+  </si>
+  <si>
+    <t>↓2</t>
+  </si>
+  <si>
     <t>↓5</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>↑1</t>
-  </si>
-  <si>
-    <t>↓3</t>
-  </si>
-  <si>
-    <t>↓1</t>
-  </si>
-  <si>
-    <t>↓7</t>
+    <t>↑7</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -386,6 +398,9 @@
   </si>
   <si>
     <t>Week 5</t>
+  </si>
+  <si>
+    <t>Week 6</t>
   </si>
   <si>
     <t>Week</t>
@@ -825,37 +840,37 @@
         <v>15</v>
       </c>
       <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" t="s">
-        <v>17</v>
-      </c>
       <c r="L2" t="s">
         <v>16</v>
       </c>
       <c r="M2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -872,7 +887,7 @@
         <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
         <v>15</v>
@@ -896,13 +911,13 @@
         <v>16</v>
       </c>
       <c r="M3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -916,40 +931,40 @@
         <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I4" t="s">
         <v>16</v>
       </c>
       <c r="J4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N4" t="s">
         <v>16</v>
       </c>
       <c r="O4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -960,43 +975,43 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" t="s">
         <v>16</v>
       </c>
       <c r="H5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J5" t="s">
         <v>16</v>
       </c>
       <c r="K5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L5" t="s">
         <v>15</v>
       </c>
       <c r="M5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N5" t="s">
         <v>16</v>
       </c>
       <c r="O5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -1007,43 +1022,43 @@
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G6" t="s">
         <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L6" t="s">
         <v>16</v>
       </c>
       <c r="M6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N6" t="s">
         <v>16</v>
       </c>
       <c r="O6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -1051,46 +1066,46 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N7" t="s">
         <v>15</v>
       </c>
       <c r="O7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -1098,46 +1113,46 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" t="s">
         <v>15</v>
       </c>
-      <c r="E8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="H8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" t="s">
         <v>15</v>
-      </c>
-      <c r="G8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" t="s">
-        <v>15</v>
-      </c>
-      <c r="K8" t="s">
-        <v>17</v>
       </c>
       <c r="L8" t="s">
         <v>15</v>
       </c>
       <c r="M8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N8" t="s">
         <v>15</v>
       </c>
       <c r="O8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -1148,28 +1163,28 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s">
         <v>14</v>
       </c>
       <c r="G9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H9" t="s">
         <v>14</v>
       </c>
       <c r="I9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K9" t="s">
         <v>14</v>
@@ -1178,10 +1193,10 @@
         <v>15</v>
       </c>
       <c r="M9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O9" t="s">
         <v>16</v>
@@ -1192,46 +1207,46 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" t="s">
         <v>19</v>
       </c>
-      <c r="E10" t="s">
-        <v>18</v>
-      </c>
       <c r="F10" t="s">
         <v>16</v>
       </c>
       <c r="G10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L10" t="s">
         <v>19</v>
       </c>
       <c r="M10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1239,25 +1254,25 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H11" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I11" t="s">
         <v>15</v>
@@ -1266,19 +1281,19 @@
         <v>15</v>
       </c>
       <c r="K11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L11" t="s">
         <v>15</v>
       </c>
       <c r="M11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N11" t="s">
         <v>14</v>
       </c>
       <c r="O11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -1286,46 +1301,46 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N12" t="s">
         <v>15</v>
       </c>
       <c r="O12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -1333,46 +1348,46 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -1389,13 +1404,13 @@
         <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -1430,22 +1445,22 @@
         <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G15" t="s">
         <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I15" t="s">
         <v>15</v>
@@ -1454,19 +1469,19 @@
         <v>16</v>
       </c>
       <c r="K15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N15" t="s">
         <v>15</v>
       </c>
       <c r="O15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1476,30 +1491,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1507,25 +1522,25 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="F2">
-        <v>-14</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1533,25 +1548,25 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>-8</v>
+        <v>-14</v>
       </c>
       <c r="G3">
         <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1559,25 +1574,25 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E4">
-        <v>-3</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>9</v>
+        <v>-8</v>
       </c>
       <c r="G4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1585,25 +1600,25 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E5">
+        <v>-3</v>
+      </c>
+      <c r="F5">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5" t="s">
         <v>5</v>
-      </c>
-      <c r="F5">
-        <v>-4</v>
-      </c>
-      <c r="G5">
-        <v>9</v>
-      </c>
-      <c r="H5" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1611,22 +1626,22 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="F6">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H6" t="s">
         <v>9</v>
@@ -1637,25 +1652,25 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F7">
+        <v>-4</v>
+      </c>
+      <c r="G7">
+        <v>9</v>
+      </c>
+      <c r="H7" t="s">
         <v>6</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-      <c r="H7" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1663,25 +1678,25 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>-10</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H8" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1692,22 +1707,22 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>6</v>
+      </c>
+      <c r="G9">
         <v>5</v>
       </c>
-      <c r="F9">
-        <v>2</v>
-      </c>
-      <c r="G9">
+      <c r="H9" t="s">
         <v>3</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1715,25 +1730,25 @@
         <v>8</v>
       </c>
       <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
         <v>4</v>
       </c>
-      <c r="C10" t="s">
-        <v>2</v>
-      </c>
       <c r="D10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10">
         <v>12</v>
       </c>
-      <c r="E10">
-        <v>8</v>
-      </c>
       <c r="F10">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H10" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1741,25 +1756,77 @@
         <v>9</v>
       </c>
       <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11">
         <v>4</v>
       </c>
-      <c r="C11" t="s">
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>4</v>
+      </c>
+      <c r="H11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12">
         <v>5</v>
       </c>
-      <c r="D11" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>6</v>
-      </c>
-      <c r="F11">
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12">
+        <v>3</v>
+      </c>
+      <c r="H12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13">
         <v>8</v>
       </c>
-      <c r="G11">
+      <c r="F13">
+        <v>11</v>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+      <c r="H13" t="s">
         <v>2</v>
-      </c>
-      <c r="H11" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1774,13 +1841,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1791,7 +1858,7 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1.857142857142857</v>
+        <v>2.071428571428572</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -1802,10 +1869,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C3">
-        <v>1.928571428571429</v>
+        <v>2.142857142857143</v>
       </c>
       <c r="D3" t="s">
         <v>15</v>
@@ -1816,13 +1883,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>2.071428571428572</v>
+        <v>2.357142857142857</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1830,13 +1897,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>2.214285714285714</v>
+        <v>2.5</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1844,13 +1911,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>2.214285714285714</v>
+        <v>2.642857142857143</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1861,7 +1928,7 @@
         <v>1</v>
       </c>
       <c r="C7">
-        <v>2.285714285714286</v>
+        <v>2.928571428571428</v>
       </c>
       <c r="D7" t="s">
         <v>16</v>
@@ -1872,13 +1939,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>2.285714285714286</v>
+        <v>2.928571428571428</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1886,13 +1953,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C9">
-        <v>2.285714285714286</v>
+        <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1900,10 +1967,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C10">
-        <v>2.642857142857143</v>
+        <v>3.071428571428572</v>
       </c>
       <c r="D10" t="s">
         <v>18</v>
@@ -1914,13 +1981,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C11">
-        <v>2.714285714285714</v>
+        <v>3.214285714285714</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1931,10 +1998,10 @@
         <v>8</v>
       </c>
       <c r="C12">
-        <v>2.857142857142857</v>
+        <v>3.214285714285714</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1942,13 +2009,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C13">
-        <v>2.928571428571428</v>
+        <v>3.571428571428572</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1956,13 +2023,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C14">
-        <v>2.928571428571428</v>
+        <v>3.857142857142857</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1973,10 +2040,10 @@
         <v>13</v>
       </c>
       <c r="C15">
-        <v>3.785714285714286</v>
+        <v>4.5</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1991,16 +2058,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2011,13 +2078,13 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>4.142857142857143</v>
+        <v>4.642857142857143</v>
       </c>
       <c r="D2">
-        <v>0.1428571428571432</v>
+        <v>0.6428571428571432</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2025,16 +2092,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C3">
-        <v>3.571428571428572</v>
+        <v>4.285714285714286</v>
       </c>
       <c r="D3">
-        <v>-0.4285714285714284</v>
+        <v>-0.7142857142857144</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2042,16 +2109,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>3.285714285714286</v>
+        <v>3.857142857142857</v>
       </c>
       <c r="D4">
-        <v>-0.7142857142857144</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2059,16 +2126,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>3.142857142857143</v>
+        <v>3.785714285714286</v>
       </c>
       <c r="D5">
-        <v>-0.8571428571428572</v>
+        <v>-0.2142857142857144</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2076,16 +2143,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C6">
-        <v>2.928571428571428</v>
+        <v>3.642857142857143</v>
       </c>
       <c r="D6">
-        <v>0.9285714285714284</v>
+        <v>-1.357142857142857</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2096,13 +2163,13 @@
         <v>3</v>
       </c>
       <c r="C7">
-        <v>2.857142857142857</v>
+        <v>3.5</v>
       </c>
       <c r="D7">
-        <v>-1.142857142857143</v>
+        <v>-1.5</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2113,13 +2180,13 @@
         <v>4</v>
       </c>
       <c r="C8">
-        <v>2.642857142857143</v>
+        <v>3.357142857142857</v>
       </c>
       <c r="D8">
-        <v>0.6428571428571428</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2127,16 +2194,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>2.642857142857143</v>
+        <v>2.857142857142857</v>
       </c>
       <c r="D9">
-        <v>0.6428571428571428</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2144,16 +2211,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C10">
-        <v>2.5</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="D10">
-        <v>-0.5</v>
+        <v>0.7142857142857144</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2161,16 +2228,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>2.642857142857143</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>-0.3571428571428572</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2181,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="C12">
-        <v>1.785714285714286</v>
+        <v>2.071428571428572</v>
       </c>
       <c r="D12">
-        <v>1.785714285714286</v>
+        <v>2.071428571428572</v>
       </c>
       <c r="E12" t="s">
         <v>14</v>
@@ -2195,16 +2262,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13">
-        <v>1.428571428571429</v>
+        <v>1.928571428571429</v>
       </c>
       <c r="D13">
-        <v>-0.5714285714285714</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2212,16 +2279,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14">
-        <v>1.214285714285714</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="D14">
-        <v>0.2142857142857142</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2238,7 +2305,7 @@
         <v>-0.1428571428571429</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -2253,87 +2320,87 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2">
-        <v>51.6</v>
+        <v>28.3</v>
       </c>
       <c r="C2">
-        <v>21.9</v>
+        <v>22.5</v>
       </c>
       <c r="D2">
+        <v>17.5</v>
+      </c>
+      <c r="E2">
         <v>12.1</v>
       </c>
-      <c r="E2">
-        <v>6.8</v>
-      </c>
       <c r="F2">
-        <v>3.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G2">
-        <v>1.8</v>
+        <v>6.9</v>
       </c>
       <c r="H2">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J2">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="K2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -2348,42 +2415,42 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>98.09999999999999</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B3">
-        <v>29.9</v>
+        <v>30.7</v>
       </c>
       <c r="C3">
-        <v>32.3</v>
+        <v>22.3</v>
       </c>
       <c r="D3">
-        <v>17.7</v>
+        <v>16.6</v>
       </c>
       <c r="E3">
-        <v>8.5</v>
+        <v>11.6</v>
       </c>
       <c r="F3">
-        <v>5.4</v>
+        <v>9.1</v>
       </c>
       <c r="G3">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="H3">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="I3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -2398,45 +2465,45 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>97.40000000000001</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B4">
-        <v>7</v>
+        <v>13.3</v>
       </c>
       <c r="C4">
-        <v>12.2</v>
+        <v>14</v>
       </c>
       <c r="D4">
-        <v>16.1</v>
+        <v>16.9</v>
       </c>
       <c r="E4">
-        <v>20.2</v>
+        <v>16.3</v>
       </c>
       <c r="F4">
-        <v>14</v>
+        <v>15.6</v>
       </c>
       <c r="G4">
-        <v>14</v>
+        <v>11.8</v>
       </c>
       <c r="H4">
-        <v>9.300000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="I4">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="J4">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="K4">
         <v>0.3</v>
       </c>
       <c r="L4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -2448,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>83.5</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2456,37 +2523,37 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>5.4</v>
+        <v>10.4</v>
       </c>
       <c r="C5">
-        <v>11.7</v>
+        <v>14.7</v>
       </c>
       <c r="D5">
-        <v>17.9</v>
+        <v>14.7</v>
       </c>
       <c r="E5">
-        <v>18.7</v>
+        <v>16.2</v>
       </c>
       <c r="F5">
-        <v>18.1</v>
+        <v>15.7</v>
       </c>
       <c r="G5">
-        <v>9.1</v>
+        <v>12.9</v>
       </c>
       <c r="H5">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I5">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -2498,45 +2565,45 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>80.90000000000001</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B6">
-        <v>3.5</v>
+        <v>11.6</v>
       </c>
       <c r="C6">
-        <v>12.4</v>
+        <v>13.6</v>
       </c>
       <c r="D6">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E6">
-        <v>17</v>
+        <v>16.1</v>
       </c>
       <c r="F6">
-        <v>16.4</v>
+        <v>13.7</v>
       </c>
       <c r="G6">
-        <v>15.1</v>
+        <v>12.9</v>
       </c>
       <c r="H6">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I6">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="J6">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="K6">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="L6">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -2548,7 +2615,7 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>79</v>
+        <v>83.90000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2556,34 +2623,34 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>1.5</v>
+        <v>4.7</v>
       </c>
       <c r="C7">
-        <v>6.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D7">
-        <v>11.9</v>
+        <v>11.3</v>
       </c>
       <c r="E7">
-        <v>14.4</v>
+        <v>16</v>
       </c>
       <c r="F7">
-        <v>16.1</v>
+        <v>18.4</v>
       </c>
       <c r="G7">
-        <v>17.3</v>
+        <v>18.2</v>
       </c>
       <c r="H7">
-        <v>13.6</v>
+        <v>11.1</v>
       </c>
       <c r="I7">
-        <v>10.5</v>
+        <v>7.1</v>
       </c>
       <c r="J7">
-        <v>5.7</v>
+        <v>2.3</v>
       </c>
       <c r="K7">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="L7">
         <v>0.3</v>
@@ -2598,48 +2665,48 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>67.59999999999999</v>
+        <v>78.3</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B8">
         <v>0.8</v>
       </c>
       <c r="C8">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="D8">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="E8">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="F8">
-        <v>9.5</v>
+        <v>11.6</v>
       </c>
       <c r="G8">
-        <v>14.1</v>
+        <v>18.4</v>
       </c>
       <c r="H8">
-        <v>18.5</v>
+        <v>23.1</v>
       </c>
       <c r="I8">
-        <v>16.1</v>
+        <v>15.7</v>
       </c>
       <c r="J8">
-        <v>16.2</v>
+        <v>9.6</v>
       </c>
       <c r="K8">
-        <v>8.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="L8">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="M8">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -2648,157 +2715,157 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>38.4</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B9">
         <v>0.1</v>
       </c>
       <c r="C9">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D9">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="E9">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="F9">
-        <v>8.1</v>
+        <v>3</v>
       </c>
       <c r="G9">
-        <v>12.8</v>
+        <v>5.1</v>
       </c>
       <c r="H9">
-        <v>13.8</v>
+        <v>12</v>
       </c>
       <c r="I9">
-        <v>19.3</v>
+        <v>21.7</v>
       </c>
       <c r="J9">
-        <v>21.1</v>
+        <v>23.3</v>
       </c>
       <c r="K9">
-        <v>11.5</v>
+        <v>17.7</v>
       </c>
       <c r="L9">
-        <v>4.2</v>
+        <v>10.1</v>
       </c>
       <c r="M9">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="N9">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="O9">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>28.5</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B10">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C10">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="D10">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="E10">
+        <v>1.8</v>
+      </c>
+      <c r="F10">
         <v>2.6</v>
       </c>
-      <c r="F10">
-        <v>6.4</v>
-      </c>
       <c r="G10">
-        <v>9</v>
+        <v>4.9</v>
       </c>
       <c r="H10">
-        <v>14.4</v>
+        <v>10.6</v>
       </c>
       <c r="I10">
+        <v>17.3</v>
+      </c>
+      <c r="J10">
+        <v>25.7</v>
+      </c>
+      <c r="K10">
         <v>22.2</v>
       </c>
-      <c r="J10">
-        <v>22.2</v>
-      </c>
-      <c r="K10">
-        <v>14.6</v>
-      </c>
       <c r="L10">
-        <v>4.2</v>
+        <v>10.2</v>
       </c>
       <c r="M10">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="N10">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="O10">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P10">
-        <v>20.8</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E11">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="G11">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="H11">
-        <v>5.7</v>
+        <v>9.6</v>
       </c>
       <c r="I11">
-        <v>11.5</v>
+        <v>18.4</v>
       </c>
       <c r="J11">
-        <v>19.3</v>
+        <v>21.3</v>
       </c>
       <c r="K11">
-        <v>33.6</v>
+        <v>25.5</v>
       </c>
       <c r="L11">
-        <v>14.6</v>
+        <v>13.3</v>
       </c>
       <c r="M11">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="N11">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="O11">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="P11">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2812,48 +2879,48 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="G12">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="H12">
+        <v>1.6</v>
+      </c>
+      <c r="I12">
+        <v>4.4</v>
+      </c>
+      <c r="J12">
+        <v>12.2</v>
+      </c>
+      <c r="K12">
+        <v>20.7</v>
+      </c>
+      <c r="L12">
+        <v>40.4</v>
+      </c>
+      <c r="M12">
+        <v>15.8</v>
+      </c>
+      <c r="N12">
+        <v>3.6</v>
+      </c>
+      <c r="O12">
         <v>0.4</v>
       </c>
-      <c r="I12">
-        <v>2</v>
-      </c>
-      <c r="J12">
-        <v>5</v>
-      </c>
-      <c r="K12">
-        <v>16.4</v>
-      </c>
-      <c r="L12">
-        <v>38</v>
-      </c>
-      <c r="M12">
-        <v>23</v>
-      </c>
-      <c r="N12">
-        <v>12.5</v>
-      </c>
-      <c r="O12">
-        <v>2.4</v>
-      </c>
       <c r="P12">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2871,39 +2938,39 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
         <v>0.3</v>
       </c>
-      <c r="J13">
-        <v>1.4</v>
-      </c>
       <c r="K13">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="L13">
-        <v>15.7</v>
+        <v>6.4</v>
       </c>
       <c r="M13">
-        <v>28</v>
+        <v>23.4</v>
       </c>
       <c r="N13">
-        <v>32.2</v>
+        <v>40.7</v>
       </c>
       <c r="O13">
-        <v>18.6</v>
+        <v>27.7</v>
       </c>
       <c r="P13">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2924,28 +2991,28 @@
         <v>0</v>
       </c>
       <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
         <v>0.1</v>
       </c>
-      <c r="I14">
-        <v>0.6</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-      <c r="K14">
-        <v>7.2</v>
-      </c>
       <c r="L14">
-        <v>16.8</v>
+        <v>0.9</v>
       </c>
       <c r="M14">
-        <v>27</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="N14">
-        <v>26.3</v>
+        <v>26.6</v>
       </c>
       <c r="O14">
-        <v>21</v>
+        <v>63.1</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -2953,7 +3020,7 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2974,28 +3041,28 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I15">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="K15">
-        <v>0.7</v>
+        <v>6.1</v>
       </c>
       <c r="L15">
-        <v>3.7</v>
+        <v>16.6</v>
       </c>
       <c r="M15">
-        <v>12.4</v>
+        <v>40.5</v>
       </c>
       <c r="N15">
-        <v>25.7</v>
+        <v>26.3</v>
       </c>
       <c r="O15">
-        <v>57.3</v>
+        <v>8.5</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -3008,145 +3075,163 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>47</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2">
+        <v>26.2</v>
+      </c>
+      <c r="C2">
+        <v>30.9</v>
+      </c>
+      <c r="D2">
+        <v>77</v>
+      </c>
+      <c r="E2">
+        <v>67.30000000000001</v>
+      </c>
+      <c r="F2">
+        <v>82.19999999999999</v>
+      </c>
+      <c r="G2">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="H2">
+        <v>95.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2">
-        <v>95.09999999999999</v>
-      </c>
-      <c r="C2">
-        <v>31.6</v>
-      </c>
-      <c r="D2">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="E2">
-        <v>96.89999999999999</v>
-      </c>
-      <c r="F2">
-        <v>99.8</v>
-      </c>
-      <c r="G2">
-        <v>97.8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
+      <c r="B3">
+        <v>95.7</v>
+      </c>
+      <c r="C3">
+        <v>30.4</v>
+      </c>
+      <c r="D3">
+        <v>75.5</v>
+      </c>
+      <c r="E3">
+        <v>96.39999999999999</v>
+      </c>
+      <c r="F3">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="G3">
+        <v>93.8</v>
+      </c>
+      <c r="H3">
+        <v>95.39999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4">
+        <v>99.5</v>
+      </c>
+      <c r="C4">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="D4">
+        <v>98.2</v>
+      </c>
+      <c r="E4">
+        <v>55.50000000000001</v>
+      </c>
+      <c r="F4">
+        <v>76.7</v>
+      </c>
+      <c r="G4">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="H4">
+        <v>86.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>93</v>
-      </c>
-      <c r="C3">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="D3">
-        <v>60.4</v>
-      </c>
-      <c r="E3">
-        <v>83.7</v>
-      </c>
-      <c r="F3">
-        <v>96.39999999999999</v>
-      </c>
-      <c r="G3">
+      <c r="B5">
+        <v>94.69999999999999</v>
+      </c>
+      <c r="C5">
+        <v>97.7</v>
+      </c>
+      <c r="D5">
+        <v>63</v>
+      </c>
+      <c r="E5">
+        <v>83</v>
+      </c>
+      <c r="F5">
         <v>97.3</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
+      <c r="G5">
+        <v>84.7</v>
+      </c>
+      <c r="H5">
+        <v>85.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>6.800000000000001</v>
-      </c>
-      <c r="C4">
-        <v>89.8</v>
-      </c>
-      <c r="D4">
-        <v>77.7</v>
-      </c>
-      <c r="E4">
-        <v>93.5</v>
-      </c>
-      <c r="F4">
-        <v>79.90000000000001</v>
-      </c>
-      <c r="G4">
-        <v>80.7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5">
-        <v>99.2</v>
-      </c>
-      <c r="C5">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="D5">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="E5">
-        <v>60.9</v>
-      </c>
-      <c r="F5">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="G5">
-        <v>79.10000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="B6">
-        <v>25.5</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="C6">
-        <v>30.4</v>
+        <v>90.2</v>
       </c>
       <c r="D6">
-        <v>78.3</v>
+        <v>78.8</v>
       </c>
       <c r="E6">
-        <v>65.90000000000001</v>
+        <v>94.39999999999999</v>
       </c>
       <c r="F6">
-        <v>81</v>
+        <v>78.8</v>
       </c>
       <c r="G6">
-        <v>78.8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>87.2</v>
+      </c>
+      <c r="H6">
+        <v>85.39999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -3154,171 +3239,192 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>67.90000000000001</v>
+        <v>67.60000000000001</v>
       </c>
       <c r="D7">
-        <v>48.9</v>
+        <v>50.1</v>
       </c>
       <c r="E7">
-        <v>92.60000000000001</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="F7">
-        <v>64.40000000000001</v>
+        <v>66.60000000000001</v>
       </c>
       <c r="G7">
-        <v>70.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>80.5</v>
+      </c>
+      <c r="H7">
+        <v>74.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>68.60000000000001</v>
+      </c>
+      <c r="C8">
+        <v>6.600000000000001</v>
+      </c>
+      <c r="D8">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="E8">
+        <v>10.7</v>
+      </c>
+      <c r="F8">
+        <v>34</v>
+      </c>
+      <c r="G8">
+        <v>42.4</v>
+      </c>
+      <c r="H8">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B8">
+      <c r="B9">
         <v>100</v>
       </c>
-      <c r="C8">
-        <v>97</v>
-      </c>
-      <c r="D8">
-        <v>63.6</v>
-      </c>
-      <c r="E8">
-        <v>25</v>
-      </c>
-      <c r="F8">
-        <v>40.2</v>
-      </c>
-      <c r="G8">
-        <v>36.4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9">
-        <v>70.5</v>
-      </c>
       <c r="C9">
-        <v>5</v>
+        <v>97.2</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>62.3</v>
       </c>
       <c r="E9">
-        <v>11.2</v>
+        <v>29.2</v>
       </c>
       <c r="F9">
-        <v>33.1</v>
+        <v>38.2</v>
       </c>
       <c r="G9">
-        <v>30.6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>13.4</v>
+      </c>
+      <c r="H9">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10">
+        <v>0.6</v>
+      </c>
+      <c r="C10">
+        <v>0.1</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0.5</v>
+      </c>
+      <c r="F10">
+        <v>6.7</v>
+      </c>
+      <c r="G10">
+        <v>13.5</v>
+      </c>
+      <c r="H10">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B10">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="C10">
-        <v>77.7</v>
-      </c>
-      <c r="D10">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="E10">
-        <v>67.5</v>
-      </c>
-      <c r="F10">
-        <v>21.8</v>
-      </c>
-      <c r="G10">
-        <v>21.8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="B11">
-        <v>0.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="C11">
-        <v>0.1</v>
+        <v>77.3</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="E11">
-        <v>1.5</v>
+        <v>68.89999999999999</v>
       </c>
       <c r="F11">
-        <v>6.7</v>
+        <v>19.9</v>
       </c>
       <c r="G11">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>5.2</v>
+      </c>
+      <c r="H11">
+        <v>5.800000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B12">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="C12">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="D12">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="F12">
         <v>0.1</v>
       </c>
       <c r="G12">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>1.1</v>
+      </c>
+      <c r="H12">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B13">
-        <v>14.1</v>
+        <v>14.8</v>
       </c>
       <c r="C13">
         <v>1.8</v>
       </c>
       <c r="D13">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E13">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="H13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B14">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="C14">
-        <v>0.4</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="D14">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -3329,27 +3435,33 @@
       <c r="G14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="H14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B15">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="C15">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="E15">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="F15">
         <v>0.1</v>
       </c>
       <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
         <v>0</v>
       </c>
     </row>
@@ -3365,28 +3477,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3397,25 +3509,25 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D2">
-        <v>78.58</v>
+        <v>73.87</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>107.44</v>
+        <v>104.7</v>
       </c>
       <c r="G2">
-        <v>0.6</v>
+        <v>0.542</v>
       </c>
       <c r="H2">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3423,28 +3535,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D3">
-        <v>84.54000000000001</v>
+        <v>90.13</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>104.46</v>
+        <v>103.66</v>
       </c>
       <c r="G3">
-        <v>0.578</v>
+        <v>0.604</v>
       </c>
       <c r="H3">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3452,28 +3564,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D4">
-        <v>92.38</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F4">
-        <v>105.16</v>
+        <v>101.46</v>
       </c>
       <c r="G4">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H4">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="I4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3481,28 +3593,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D5">
-        <v>107.63</v>
+        <v>104.36</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F5">
-        <v>103.14</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G5">
-        <v>0.533</v>
+        <v>0.417</v>
       </c>
       <c r="H5">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3510,28 +3622,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D6">
-        <v>95.26000000000001</v>
+        <v>88.33</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>101.91</v>
+        <v>102.33</v>
       </c>
       <c r="G6">
-        <v>0.444</v>
+        <v>0.542</v>
       </c>
       <c r="H6">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3539,28 +3651,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D7">
-        <v>123.19</v>
+        <v>87.69</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
       </c>
       <c r="F7">
-        <v>101.07</v>
+        <v>101.96</v>
       </c>
       <c r="G7">
-        <v>0.511</v>
+        <v>0.625</v>
       </c>
       <c r="H7">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="I7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3568,28 +3680,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D8">
-        <v>87.8</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F8">
-        <v>103.41</v>
+        <v>100.15</v>
       </c>
       <c r="G8">
-        <v>0.533</v>
+        <v>0.583</v>
       </c>
       <c r="H8">
-        <v>0.6</v>
+        <v>-0.1</v>
       </c>
       <c r="I8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3597,28 +3709,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D9">
-        <v>108.08</v>
+        <v>106.92</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F9">
-        <v>101.93</v>
+        <v>99.12</v>
       </c>
       <c r="G9">
-        <v>0.467</v>
+        <v>0.5</v>
       </c>
       <c r="H9">
-        <v>-0.2</v>
+        <v>-0.8</v>
       </c>
       <c r="I9">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3626,28 +3738,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D10">
-        <v>101.91</v>
+        <v>110.14</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F10">
-        <v>100.56</v>
+        <v>99.16</v>
       </c>
       <c r="G10">
-        <v>0.556</v>
+        <v>0.438</v>
       </c>
       <c r="H10">
-        <v>-0.3</v>
+        <v>-1</v>
       </c>
       <c r="I10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3658,25 +3770,25 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D11">
-        <v>105.76</v>
+        <v>103.48</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F11">
-        <v>100.67</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="G11">
-        <v>0.467</v>
+        <v>0.417</v>
       </c>
       <c r="H11">
-        <v>-0.3</v>
+        <v>-1.2</v>
       </c>
       <c r="I11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3684,28 +3796,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D12">
-        <v>104.62</v>
+        <v>118.41</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F12">
-        <v>98.33</v>
+        <v>98.05</v>
       </c>
       <c r="G12">
-        <v>0.378</v>
+        <v>0.521</v>
       </c>
       <c r="H12">
-        <v>-1.7</v>
+        <v>-1.6</v>
       </c>
       <c r="I12">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3713,28 +3825,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13">
-        <v>101.45</v>
+        <v>109.53</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F13">
-        <v>97.70999999999999</v>
+        <v>96.48999999999999</v>
       </c>
       <c r="G13">
-        <v>0.422</v>
+        <v>0.417</v>
       </c>
       <c r="H13">
         <v>-1.8</v>
       </c>
       <c r="I13">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -3742,28 +3854,28 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D14">
-        <v>115.84</v>
+        <v>95.73999999999999</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F14">
-        <v>98.87</v>
+        <v>94.87</v>
       </c>
       <c r="G14">
-        <v>0.467</v>
+        <v>0.375</v>
       </c>
       <c r="H14">
-        <v>-2.3</v>
+        <v>-3</v>
       </c>
       <c r="I14">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -3774,25 +3886,25 @@
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D15">
-        <v>113.69</v>
+        <v>113.78</v>
       </c>
       <c r="E15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F15">
-        <v>96.06999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="G15">
-        <v>0.444</v>
+        <v>0.521</v>
       </c>
       <c r="H15">
-        <v>-4.8</v>
+        <v>-3.6</v>
       </c>
       <c r="I15">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3807,118 +3919,118 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C2">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D2">
-        <v>123.192</v>
+        <v>110.1433333333333</v>
       </c>
       <c r="E2">
-        <v>615.96</v>
+        <v>660.8599999999999</v>
       </c>
       <c r="F2">
-        <v>98.09999999999999</v>
+        <v>96</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C3">
-        <v>0.8</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D3">
-        <v>115.836</v>
+        <v>118.4066666666667</v>
       </c>
       <c r="E3">
-        <v>579.1799999999999</v>
+        <v>710.4400000000001</v>
       </c>
       <c r="F3">
-        <v>97.39999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C4">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D4">
-        <v>108.084</v>
+        <v>103.4766666666666</v>
       </c>
       <c r="E4">
-        <v>540.42</v>
+        <v>620.8599999999999</v>
       </c>
       <c r="F4">
-        <v>83.5</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3926,57 +4038,57 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C5">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D5">
-        <v>104.624</v>
+        <v>104.3566666666667</v>
       </c>
       <c r="E5">
-        <v>523.12</v>
+        <v>626.14</v>
       </c>
       <c r="F5">
-        <v>80.90000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C6">
-        <v>0.8</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D6">
-        <v>105.764</v>
+        <v>109.5266666666667</v>
       </c>
       <c r="E6">
-        <v>528.8199999999999</v>
+        <v>657.16</v>
       </c>
       <c r="F6">
-        <v>79</v>
+        <v>83.89999999999999</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3984,144 +4096,144 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C7">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
-        <v>113.688</v>
+        <v>113.7766666666667</v>
       </c>
       <c r="E7">
-        <v>568.4400000000001</v>
+        <v>682.6600000000001</v>
       </c>
       <c r="F7">
-        <v>67.60000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C8">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D8">
-        <v>101.912</v>
+        <v>106.9233333333333</v>
       </c>
       <c r="E8">
-        <v>509.5599999999999</v>
+        <v>641.5399999999998</v>
       </c>
       <c r="F8">
-        <v>38.4</v>
+        <v>45.8</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C9">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D9">
-        <v>107.628</v>
+        <v>97.15333333333332</v>
       </c>
       <c r="E9">
-        <v>538.1399999999999</v>
+        <v>582.92</v>
       </c>
       <c r="F9">
-        <v>28.5</v>
+        <v>11.6</v>
       </c>
       <c r="G9">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C10">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D10">
-        <v>101.448</v>
+        <v>96.42666666666666</v>
       </c>
       <c r="E10">
-        <v>507.24</v>
+        <v>578.5599999999999</v>
       </c>
       <c r="F10">
-        <v>20.8</v>
+        <v>10.2</v>
       </c>
       <c r="G10">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H10" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="I10" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C11">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D11">
-        <v>95.26399999999998</v>
+        <v>95.73666666666668</v>
       </c>
       <c r="E11">
-        <v>476.3199999999999</v>
+        <v>574.4200000000001</v>
       </c>
       <c r="F11">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="G11">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H11" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -4129,115 +4241,115 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C12">
+        <v>0.5</v>
+      </c>
+      <c r="D12">
+        <v>88.32666666666665</v>
+      </c>
+      <c r="E12">
+        <v>529.9599999999999</v>
+      </c>
+      <c r="F12">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="G12">
         <v>0.4</v>
       </c>
-      <c r="D12">
-        <v>87.79599999999999</v>
-      </c>
-      <c r="E12">
-        <v>438.98</v>
-      </c>
-      <c r="F12">
-        <v>0.3</v>
-      </c>
-      <c r="G12">
-        <v>2.4</v>
-      </c>
       <c r="H12" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="I12" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C13">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>84.54400000000001</v>
+        <v>90.12666666666667</v>
       </c>
       <c r="E13">
-        <v>422.72</v>
+        <v>540.76</v>
       </c>
       <c r="F13">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>18.6</v>
+        <v>27.7</v>
       </c>
       <c r="H13" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="I13" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D14">
-        <v>92.376</v>
+        <v>73.87333333333333</v>
       </c>
       <c r="E14">
-        <v>461.88</v>
+        <v>443.24</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>21</v>
+        <v>63.1</v>
       </c>
       <c r="H14" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I14" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C15">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D15">
-        <v>78.57599999999999</v>
+        <v>87.69</v>
       </c>
       <c r="E15">
-        <v>392.88</v>
+        <v>526.14</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>57.3</v>
+        <v>8.5</v>
       </c>
       <c r="H15" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I15" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -4252,19 +4364,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4275,16 +4387,16 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4292,19 +4404,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4315,16 +4427,16 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4332,19 +4444,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4352,19 +4464,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D6">
         <v>7</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4372,19 +4484,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D7">
         <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4392,19 +4504,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4412,19 +4524,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D9">
         <v>-1</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4432,19 +4544,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4452,19 +4564,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D11">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4475,16 +4587,16 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D12">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4498,13 +4610,13 @@
         <v>60</v>
       </c>
       <c r="D13">
-        <v>-9</v>
+        <v>-14</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F13" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4512,19 +4624,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D14">
-        <v>-16</v>
+        <v>-14</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F14" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4532,19 +4644,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15">
         <v>-21</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -4554,30 +4666,33 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>125</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -4596,34 +4711,40 @@
       <c r="F2">
         <v>15</v>
       </c>
-      <c r="G2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="G2">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>-9</v>
+      </c>
+      <c r="C3">
+        <v>-3</v>
+      </c>
+      <c r="D3">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="E3">
         <v>6</v>
       </c>
-      <c r="C3">
-        <v>7</v>
-      </c>
-      <c r="D3">
-        <v>6</v>
-      </c>
-      <c r="E3">
+      <c r="F3">
         <v>8</v>
       </c>
-      <c r="F3">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="G3">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -4642,172 +4763,196 @@
       <c r="F4">
         <v>9</v>
       </c>
-      <c r="G4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="G4">
+        <v>12</v>
+      </c>
+      <c r="H4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B5">
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="C5">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>7</v>
+      </c>
+      <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6">
         <v>6</v>
       </c>
-      <c r="F5">
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
         <v>8</v>
       </c>
-      <c r="G5" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1" t="s">
+      <c r="F6">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6">
+      <c r="B7">
         <v>-2</v>
       </c>
-      <c r="C6">
+      <c r="C7">
         <v>4</v>
       </c>
-      <c r="D6">
+      <c r="D7">
         <v>11</v>
       </c>
-      <c r="E6">
+      <c r="E7">
         <v>11</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7">
-        <v>-3</v>
-      </c>
-      <c r="C7">
-        <v>-2</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>5</v>
       </c>
       <c r="F7">
         <v>7</v>
       </c>
-      <c r="G7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="G7">
+        <v>7</v>
+      </c>
+      <c r="H7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8">
         <v>1</v>
       </c>
-      <c r="B8">
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>-4</v>
+      </c>
+      <c r="F8">
+        <v>-1</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C8">
+      <c r="B9">
+        <v>-3</v>
+      </c>
+      <c r="C9">
+        <v>-4</v>
+      </c>
+      <c r="D9">
+        <v>-9</v>
+      </c>
+      <c r="E9">
+        <v>-4</v>
+      </c>
+      <c r="F9">
+        <v>-3</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+      <c r="H9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10">
         <v>5</v>
       </c>
-      <c r="D8">
+      <c r="D10">
         <v>5</v>
       </c>
-      <c r="E8">
+      <c r="E10">
         <v>8</v>
       </c>
-      <c r="F8">
+      <c r="F10">
         <v>3</v>
       </c>
-      <c r="G8" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="1" t="s">
+      <c r="G10">
+        <v>-3</v>
+      </c>
+      <c r="H10" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B9">
+      <c r="B11">
         <v>-8</v>
       </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
         <v>1</v>
       </c>
-      <c r="E9">
+      <c r="E11">
         <v>-1</v>
       </c>
-      <c r="F9">
+      <c r="F11">
         <v>-1</v>
       </c>
-      <c r="G9" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10">
-        <v>3</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
+      <c r="G11">
         <v>-4</v>
       </c>
-      <c r="F10">
-        <v>-1</v>
-      </c>
-      <c r="G10" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11">
-        <v>-3</v>
-      </c>
-      <c r="C11">
-        <v>-4</v>
-      </c>
-      <c r="D11">
-        <v>-9</v>
-      </c>
-      <c r="E11">
-        <v>-4</v>
-      </c>
-      <c r="F11">
-        <v>-3</v>
-      </c>
-      <c r="G11" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="H11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
@@ -4826,11 +4971,14 @@
       <c r="F12">
         <v>-8</v>
       </c>
-      <c r="G12" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="G12">
+        <v>-10</v>
+      </c>
+      <c r="H12" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
         <v>9</v>
       </c>
@@ -4849,54 +4997,63 @@
       <c r="F13">
         <v>-9</v>
       </c>
-      <c r="G13" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="G13">
+        <v>-14</v>
+      </c>
+      <c r="H13" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14">
+        <v>-4</v>
+      </c>
+      <c r="C14">
+        <v>-15</v>
+      </c>
+      <c r="D14">
+        <v>-14</v>
+      </c>
+      <c r="E14">
+        <v>-14</v>
+      </c>
+      <c r="F14">
+        <v>-21</v>
+      </c>
+      <c r="G14">
+        <v>-14</v>
+      </c>
+      <c r="H14" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B14">
+      <c r="B15">
         <v>4</v>
       </c>
-      <c r="C14">
+      <c r="C15">
         <v>-5</v>
       </c>
-      <c r="D14">
+      <c r="D15">
         <v>-12</v>
       </c>
-      <c r="E14">
+      <c r="E15">
         <v>-15</v>
       </c>
-      <c r="F14">
+      <c r="F15">
         <v>-16</v>
       </c>
-      <c r="G14" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15">
-        <v>-4</v>
-      </c>
-      <c r="C15">
-        <v>-15</v>
-      </c>
-      <c r="D15">
-        <v>-14</v>
-      </c>
-      <c r="E15">
-        <v>-14</v>
-      </c>
-      <c r="F15">
+      <c r="G15">
         <v>-21</v>
       </c>
-      <c r="G15" t="s">
-        <v>115</v>
+      <c r="H15" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/BP- Loudoun 2025 2026.xlsx
+++ b/data/leagues/BP- Loudoun 2025 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="132">
   <si>
     <t>Bears, Jags, Foxes, Oh My!</t>
   </si>
@@ -67,25 +67,28 @@
     <t>Dave's Dynamos</t>
   </si>
   <si>
-    <t>0-6-0</t>
-  </si>
-  <si>
-    <t>2-4-0</t>
-  </si>
-  <si>
-    <t>3-3-0</t>
-  </si>
-  <si>
-    <t>4-2-0</t>
-  </si>
-  <si>
-    <t>1-5-0</t>
-  </si>
-  <si>
-    <t>5-1-0</t>
-  </si>
-  <si>
-    <t>6-0-0</t>
+    <t>1-6-0</t>
+  </si>
+  <si>
+    <t>3-4-0</t>
+  </si>
+  <si>
+    <t>4-3-0</t>
+  </si>
+  <si>
+    <t>2-5-0</t>
+  </si>
+  <si>
+    <t>0-7-0</t>
+  </si>
+  <si>
+    <t>5-2-0</t>
+  </si>
+  <si>
+    <t>6-1-0</t>
+  </si>
+  <si>
+    <t>7-0-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -172,6 +175,9 @@
     <t>Week_7</t>
   </si>
   <si>
+    <t>Week_8</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -196,45 +202,45 @@
     <t>Ishan Goel</t>
   </si>
   <si>
+    <t>Chungfu Yang</t>
+  </si>
+  <si>
+    <t>Daniel Tracey</t>
+  </si>
+  <si>
+    <t>Roy Armbruster</t>
+  </si>
+  <si>
     <t>Justin Fox</t>
   </si>
   <si>
+    <t>Jeffrey Laidacker</t>
+  </si>
+  <si>
     <t>Dale Goodwin</t>
   </si>
   <si>
-    <t>Daniel Tracey</t>
-  </si>
-  <si>
-    <t>Chungfu Yang</t>
-  </si>
-  <si>
-    <t>Roy Armbruster</t>
+    <t>Hannah Davis</t>
+  </si>
+  <si>
+    <t>MARVIN AYALA</t>
+  </si>
+  <si>
+    <t>Robert Schottler</t>
+  </si>
+  <si>
+    <t>Matthew Graesser</t>
   </si>
   <si>
     <t>Jessica Stratton</t>
   </si>
   <si>
-    <t>Hannah Davis</t>
-  </si>
-  <si>
-    <t>MARVIN AYALA</t>
+    <t>Yahya Ayaz</t>
   </si>
   <si>
     <t>Dave Linton</t>
   </si>
   <si>
-    <t>Yahya Ayaz</t>
-  </si>
-  <si>
-    <t>Matthew Graesser</t>
-  </si>
-  <si>
-    <t>Jeffrey Laidacker</t>
-  </si>
-  <si>
-    <t>Robert Schottler</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -259,64 +265,58 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>5-1</t>
-  </si>
-  <si>
-    <t>4-2</t>
-  </si>
-  <si>
-    <t>3-3</t>
-  </si>
-  <si>
-    <t>2-4</t>
-  </si>
-  <si>
-    <t>0-6</t>
-  </si>
-  <si>
-    <t>1-5</t>
-  </si>
-  <si>
-    <t>10.2-3.7-0.1</t>
-  </si>
-  <si>
-    <t>9.9-4.0-0.1</t>
-  </si>
-  <si>
-    <t>9.7-4.2-0.1</t>
-  </si>
-  <si>
-    <t>9.5-4.4-0.1</t>
-  </si>
-  <si>
-    <t>9.3-4.7-0.1</t>
-  </si>
-  <si>
-    <t>8.6-5.3-0.1</t>
-  </si>
-  <si>
-    <t>7.8-6.1-0.1</t>
-  </si>
-  <si>
-    <t>6.6-7.3-0.1</t>
-  </si>
-  <si>
-    <t>6.5-7.4-0.1</t>
-  </si>
-  <si>
-    <t>6.2-7.7-0.1</t>
-  </si>
-  <si>
-    <t>5.2-8.7-0.1</t>
-  </si>
-  <si>
-    <t>2.4-11.5-0.1</t>
-  </si>
-  <si>
-    <t>2.1-11.8</t>
-  </si>
-  <si>
-    <t>3.5-10.4-0.1</t>
+    <t>5-2</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>1-6</t>
+  </si>
+  <si>
+    <t>10.0-4.0-0.1</t>
+  </si>
+  <si>
+    <t>9.2-4.8-0.1</t>
+  </si>
+  <si>
+    <t>9.0-4.9-0.1</t>
+  </si>
+  <si>
+    <t>9.2-4.7-0.1</t>
+  </si>
+  <si>
+    <t>9.1-4.8-0.1</t>
+  </si>
+  <si>
+    <t>8.6-5.4-0.1</t>
+  </si>
+  <si>
+    <t>8.5-5.4-0.1</t>
+  </si>
+  <si>
+    <t>7.5-6.4-0.1</t>
+  </si>
+  <si>
+    <t>6.4-7.5-0.1</t>
+  </si>
+  <si>
+    <t>6.1-7.8-0.1</t>
+  </si>
+  <si>
+    <t>5.9-8.0-0.1</t>
+  </si>
+  <si>
+    <t>3.3-10.6-0.1</t>
+  </si>
+  <si>
+    <t>1.8-12.1</t>
+  </si>
+  <si>
+    <t>2.8-11.1-0.1</t>
   </si>
   <si>
     <t>10-4</t>
@@ -334,15 +334,12 @@
     <t>6-8</t>
   </si>
   <si>
-    <t>5-9</t>
-  </si>
-  <si>
-    <t>2-12</t>
-  </si>
-  <si>
     <t>3-11</t>
   </si>
   <si>
+    <t>1-13</t>
+  </si>
+  <si>
     <t>Owners</t>
   </si>
   <si>
@@ -352,37 +349,34 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↑4</t>
+  </si>
+  <si>
+    <t>↑8</t>
+  </si>
+  <si>
     <t>↑2</t>
   </si>
   <si>
-    <t>↑8</t>
-  </si>
-  <si>
-    <t>↑3</t>
-  </si>
-  <si>
-    <t>↓4</t>
-  </si>
-  <si>
     <t>0</t>
   </si>
   <si>
-    <t>↑1</t>
-  </si>
-  <si>
-    <t>↓6</t>
+    <t>↑6</t>
+  </si>
+  <si>
+    <t>↓7</t>
+  </si>
+  <si>
+    <t>↓1</t>
   </si>
   <si>
     <t>↓3</t>
   </si>
   <si>
-    <t>↓2</t>
-  </si>
-  <si>
     <t>↓5</t>
   </si>
   <si>
-    <t>↑7</t>
+    <t>↓9</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -401,6 +395,9 @@
   </si>
   <si>
     <t>Week 6</t>
+  </si>
+  <si>
+    <t>Week 7</t>
   </si>
   <si>
     <t>Week</t>
@@ -834,7 +831,7 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
         <v>15</v>
@@ -843,31 +840,31 @@
         <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K2" t="s">
         <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" t="s">
         <v>17</v>
-      </c>
-      <c r="N2" t="s">
-        <v>18</v>
       </c>
       <c r="O2" t="s">
         <v>19</v>
@@ -881,7 +878,7 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
         <v>16</v>
@@ -890,19 +887,19 @@
         <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I3" t="s">
         <v>15</v>
       </c>
       <c r="J3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K3" t="s">
         <v>16</v>
@@ -911,13 +908,13 @@
         <v>16</v>
       </c>
       <c r="M3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" t="s">
         <v>17</v>
       </c>
-      <c r="N3" t="s">
-        <v>18</v>
-      </c>
       <c r="O3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -928,43 +925,43 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
       <c r="G4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I4" t="s">
         <v>16</v>
       </c>
       <c r="J4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N4" t="s">
         <v>16</v>
       </c>
       <c r="O4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -972,40 +969,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G5" t="s">
         <v>16</v>
       </c>
       <c r="H5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" t="s">
         <v>17</v>
       </c>
-      <c r="I5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L5" t="s">
-        <v>15</v>
-      </c>
       <c r="M5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N5" t="s">
         <v>16</v>
@@ -1028,7 +1025,7 @@
         <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
@@ -1037,13 +1034,13 @@
         <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K6" t="s">
         <v>16</v>
@@ -1058,7 +1055,7 @@
         <v>16</v>
       </c>
       <c r="O6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -1069,13 +1066,13 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
@@ -1084,28 +1081,28 @@
         <v>16</v>
       </c>
       <c r="H7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N7" t="s">
         <v>15</v>
       </c>
       <c r="O7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -1116,13 +1113,13 @@
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
         <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
@@ -1134,7 +1131,7 @@
         <v>16</v>
       </c>
       <c r="I8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J8" t="s">
         <v>16</v>
@@ -1146,7 +1143,7 @@
         <v>15</v>
       </c>
       <c r="M8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N8" t="s">
         <v>15</v>
@@ -1160,46 +1157,46 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
         <v>14</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>18</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>14</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>18</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>14</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>18</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>14</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" t="s">
         <v>18</v>
       </c>
-      <c r="J9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M9" t="s">
         <v>14</v>
       </c>
-      <c r="L9" t="s">
-        <v>15</v>
-      </c>
-      <c r="M9" t="s">
-        <v>18</v>
-      </c>
       <c r="N9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="O9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -1207,43 +1204,43 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
         <v>19</v>
       </c>
       <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" t="s">
         <v>20</v>
       </c>
-      <c r="E10" t="s">
-        <v>19</v>
-      </c>
       <c r="F10" t="s">
         <v>16</v>
       </c>
       <c r="G10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H10" t="s">
         <v>19</v>
       </c>
       <c r="I10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M10" t="s">
         <v>20</v>
       </c>
       <c r="N10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O10" t="s">
         <v>20</v>
@@ -1254,31 +1251,31 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E11" t="s">
         <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H11" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I11" t="s">
         <v>15</v>
       </c>
       <c r="J11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K11" t="s">
         <v>16</v>
@@ -1287,13 +1284,13 @@
         <v>15</v>
       </c>
       <c r="M11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N11" t="s">
         <v>14</v>
       </c>
       <c r="O11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -1301,46 +1298,46 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" t="s">
         <v>17</v>
       </c>
-      <c r="F12" t="s">
-        <v>15</v>
-      </c>
       <c r="G12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="M12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N12" t="s">
         <v>15</v>
       </c>
       <c r="O12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -1348,10 +1345,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D13" t="s">
         <v>19</v>
@@ -1360,22 +1357,22 @@
         <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G13" t="s">
         <v>19</v>
       </c>
       <c r="H13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L13" t="s">
         <v>19</v>
@@ -1384,7 +1381,7 @@
         <v>19</v>
       </c>
       <c r="N13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O13" t="s">
         <v>19</v>
@@ -1395,46 +1392,46 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D14" t="s">
         <v>15</v>
       </c>
       <c r="E14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" t="s">
         <v>17</v>
       </c>
-      <c r="F14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G14" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" t="s">
-        <v>15</v>
-      </c>
       <c r="I14" t="s">
         <v>15</v>
       </c>
       <c r="J14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K14" t="s">
         <v>16</v>
       </c>
       <c r="L14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N14" t="s">
         <v>15</v>
       </c>
       <c r="O14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:15">
@@ -1442,37 +1439,37 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C15" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" t="s">
         <v>17</v>
       </c>
-      <c r="D15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="H15" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" t="s">
         <v>17</v>
       </c>
-      <c r="F15" t="s">
-        <v>17</v>
-      </c>
-      <c r="G15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H15" t="s">
-        <v>19</v>
-      </c>
-      <c r="I15" t="s">
-        <v>15</v>
-      </c>
       <c r="J15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K15" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M15" t="s">
         <v>19</v>
@@ -1491,30 +1488,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1548,25 +1545,25 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="F3">
-        <v>-14</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1574,25 +1571,25 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>-8</v>
+        <v>-14</v>
       </c>
       <c r="G4">
         <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1600,25 +1597,25 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E5">
-        <v>-3</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>-8</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1626,25 +1623,25 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6">
+        <v>-3</v>
+      </c>
+      <c r="F6">
         <v>9</v>
       </c>
-      <c r="D6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>-14</v>
-      </c>
-      <c r="F6">
-        <v>-3</v>
-      </c>
       <c r="G6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1652,25 +1649,25 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>-14</v>
+      </c>
+      <c r="F7">
+        <v>-3</v>
+      </c>
+      <c r="G7">
         <v>11</v>
       </c>
-      <c r="D7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7">
-        <v>5</v>
-      </c>
-      <c r="F7">
-        <v>-4</v>
-      </c>
-      <c r="G7">
+      <c r="H7" t="s">
         <v>9</v>
-      </c>
-      <c r="H7" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1681,22 +1678,22 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E8">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="F8">
         <v>-4</v>
       </c>
       <c r="G8">
+        <v>9</v>
+      </c>
+      <c r="H8" t="s">
         <v>6</v>
-      </c>
-      <c r="H8" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1704,25 +1701,25 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="F9">
+        <v>-4</v>
+      </c>
+      <c r="G9">
         <v>6</v>
       </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
       <c r="H9" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1730,25 +1727,25 @@
         <v>8</v>
       </c>
       <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
         <v>6</v>
-      </c>
-      <c r="C10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10">
-        <v>12</v>
-      </c>
-      <c r="F10">
-        <v>17</v>
       </c>
       <c r="G10">
         <v>5</v>
       </c>
       <c r="H10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1756,25 +1753,25 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11">
         <v>12</v>
       </c>
-      <c r="D11" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11">
+      <c r="F11">
+        <v>17</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+      <c r="H11" t="s">
         <v>4</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>4</v>
-      </c>
-      <c r="H11" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1782,51 +1779,25 @@
         <v>10</v>
       </c>
       <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
         <v>3</v>
       </c>
-      <c r="C12" t="s">
+      <c r="E12">
         <v>4</v>
       </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12">
-        <v>5</v>
-      </c>
       <c r="F12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12">
+        <v>4</v>
+      </c>
+      <c r="H12" t="s">
         <v>3</v>
-      </c>
-      <c r="H12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13">
-        <v>4</v>
-      </c>
-      <c r="C13" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13">
-        <v>8</v>
-      </c>
-      <c r="F13">
-        <v>11</v>
-      </c>
-      <c r="G13">
-        <v>3</v>
-      </c>
-      <c r="H13" t="s">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1841,13 +1812,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1858,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>2.071428571428572</v>
+        <v>2.642857142857143</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -1869,13 +1840,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>2.142857142857143</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1883,13 +1854,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>2.357142857142857</v>
+        <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1897,13 +1868,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>2.5</v>
+        <v>3.071428571428572</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1911,13 +1882,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>2.642857142857143</v>
+        <v>3.214285714285714</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1925,10 +1896,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>2.928571428571428</v>
+        <v>3.214285714285714</v>
       </c>
       <c r="D7" t="s">
         <v>16</v>
@@ -1939,13 +1910,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>2.928571428571428</v>
+        <v>3.357142857142857</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1953,10 +1924,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
@@ -1970,10 +1941,10 @@
         <v>10</v>
       </c>
       <c r="C10">
-        <v>3.071428571428572</v>
+        <v>3.571428571428572</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1981,13 +1952,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C11">
-        <v>3.214285714285714</v>
+        <v>3.714285714285714</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1995,13 +1966,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12">
-        <v>3.214285714285714</v>
+        <v>3.857142857142857</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2009,10 +1980,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C13">
-        <v>3.571428571428572</v>
+        <v>4</v>
       </c>
       <c r="D13" t="s">
         <v>19</v>
@@ -2026,7 +1997,7 @@
         <v>3</v>
       </c>
       <c r="C14">
-        <v>3.857142857142857</v>
+        <v>4.428571428571429</v>
       </c>
       <c r="D14" t="s">
         <v>19</v>
@@ -2040,7 +2011,7 @@
         <v>13</v>
       </c>
       <c r="C15">
-        <v>4.5</v>
+        <v>4.714285714285714</v>
       </c>
       <c r="D15" t="s">
         <v>19</v>
@@ -2058,16 +2029,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2078,13 +2049,13 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>4.642857142857143</v>
+        <v>5.285714285714286</v>
       </c>
       <c r="D2">
-        <v>0.6428571428571432</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2092,13 +2063,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>4.285714285714286</v>
+        <v>4.714285714285714</v>
       </c>
       <c r="D3">
-        <v>-0.7142857142857144</v>
+        <v>-0.2857142857142856</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
@@ -2112,10 +2083,10 @@
         <v>5</v>
       </c>
       <c r="C4">
-        <v>3.857142857142857</v>
+        <v>4.714285714285714</v>
       </c>
       <c r="D4">
-        <v>0.8571428571428572</v>
+        <v>0.7142857142857144</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -2126,16 +2097,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>3.785714285714286</v>
+        <v>4.428571428571429</v>
       </c>
       <c r="D5">
-        <v>-0.2142857142857144</v>
+        <v>-0.5714285714285712</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2143,16 +2114,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>3.642857142857143</v>
+        <v>4.357142857142857</v>
       </c>
       <c r="D6">
-        <v>-1.357142857142857</v>
+        <v>0.3571428571428568</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2163,10 +2134,10 @@
         <v>3</v>
       </c>
       <c r="C7">
-        <v>3.5</v>
+        <v>3.857142857142857</v>
       </c>
       <c r="D7">
-        <v>-1.5</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="E7" t="s">
         <v>19</v>
@@ -2177,16 +2148,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C8">
-        <v>3.357142857142857</v>
+        <v>3.857142857142857</v>
       </c>
       <c r="D8">
-        <v>0.3571428571428572</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2197,10 +2168,10 @@
         <v>6</v>
       </c>
       <c r="C9">
-        <v>2.857142857142857</v>
+        <v>3.642857142857143</v>
       </c>
       <c r="D9">
-        <v>-0.1428571428571428</v>
+        <v>-0.3571428571428572</v>
       </c>
       <c r="E9" t="s">
         <v>16</v>
@@ -2211,13 +2182,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>2.714285714285714</v>
+        <v>3.214285714285714</v>
       </c>
       <c r="D10">
-        <v>0.7142857142857144</v>
+        <v>0.2142857142857144</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
@@ -2228,16 +2199,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C11">
-        <v>2.642857142857143</v>
+        <v>3.071428571428572</v>
       </c>
       <c r="D11">
-        <v>-0.3571428571428572</v>
+        <v>0.07142857142857162</v>
       </c>
       <c r="E11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2248,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="C12">
-        <v>2.071428571428572</v>
+        <v>2.571428571428572</v>
       </c>
       <c r="D12">
-        <v>2.071428571428572</v>
+        <v>1.571428571428572</v>
       </c>
       <c r="E12" t="s">
         <v>14</v>
@@ -2262,16 +2233,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13">
-        <v>1.928571428571429</v>
+        <v>2.428571428571428</v>
       </c>
       <c r="D13">
-        <v>0.9285714285714286</v>
+        <v>-1.571428571428572</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2279,16 +2250,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14">
-        <v>1.857142857142857</v>
+        <v>2</v>
       </c>
       <c r="D14">
-        <v>-1.142857142857143</v>
+        <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2305,7 +2276,7 @@
         <v>-0.1428571428571429</v>
       </c>
       <c r="E15" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -2320,84 +2291,84 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B2">
-        <v>28.3</v>
+        <v>35.8</v>
       </c>
       <c r="C2">
-        <v>22.5</v>
+        <v>21.2</v>
       </c>
       <c r="D2">
-        <v>17.5</v>
+        <v>16.6</v>
       </c>
       <c r="E2">
-        <v>12.1</v>
+        <v>9.1</v>
       </c>
       <c r="F2">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>6.9</v>
+        <v>4.2</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="I2">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -2415,7 +2386,7 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>96</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2423,34 +2394,34 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>30.7</v>
+        <v>22.2</v>
       </c>
       <c r="C3">
-        <v>22.3</v>
+        <v>16.7</v>
       </c>
       <c r="D3">
-        <v>16.6</v>
+        <v>15.2</v>
       </c>
       <c r="E3">
-        <v>11.6</v>
+        <v>15.7</v>
       </c>
       <c r="F3">
-        <v>9.1</v>
+        <v>10.1</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H3">
-        <v>2.9</v>
+        <v>5.4</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J3">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="K3">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -2465,42 +2436,42 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>95.3</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B4">
-        <v>13.3</v>
+        <v>12.7</v>
       </c>
       <c r="C4">
-        <v>14</v>
+        <v>16.4</v>
       </c>
       <c r="D4">
-        <v>16.9</v>
+        <v>15.8</v>
       </c>
       <c r="E4">
-        <v>16.3</v>
+        <v>14.4</v>
       </c>
       <c r="F4">
-        <v>15.6</v>
+        <v>12.3</v>
       </c>
       <c r="G4">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I4">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="J4">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="K4">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -2515,39 +2486,39 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>87.90000000000001</v>
+        <v>83.59999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>10.4</v>
       </c>
       <c r="C5">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="D5">
-        <v>14.7</v>
+        <v>13.9</v>
       </c>
       <c r="E5">
         <v>16.2</v>
       </c>
       <c r="F5">
-        <v>15.7</v>
+        <v>13.5</v>
       </c>
       <c r="G5">
-        <v>12.9</v>
+        <v>13.6</v>
       </c>
       <c r="H5">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="I5">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="J5">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="K5">
         <v>0.7</v>
@@ -2565,45 +2536,45 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>84.59999999999999</v>
+        <v>82.2</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B6">
-        <v>11.6</v>
+        <v>7.2</v>
       </c>
       <c r="C6">
+        <v>11.7</v>
+      </c>
+      <c r="D6">
+        <v>13.8</v>
+      </c>
+      <c r="E6">
+        <v>13.2</v>
+      </c>
+      <c r="F6">
+        <v>16.9</v>
+      </c>
+      <c r="G6">
         <v>13.6</v>
       </c>
-      <c r="D6">
-        <v>16</v>
-      </c>
-      <c r="E6">
-        <v>16.1</v>
-      </c>
-      <c r="F6">
-        <v>13.7</v>
-      </c>
-      <c r="G6">
-        <v>12.9</v>
-      </c>
       <c r="H6">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="I6">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="J6">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="K6">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -2615,48 +2586,48 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>83.90000000000001</v>
+        <v>76.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7">
-        <v>4.7</v>
+        <v>7.9</v>
       </c>
       <c r="C7">
         <v>9.699999999999999</v>
       </c>
       <c r="D7">
-        <v>11.3</v>
+        <v>13</v>
       </c>
       <c r="E7">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="F7">
-        <v>18.4</v>
+        <v>15.1</v>
       </c>
       <c r="G7">
-        <v>18.2</v>
+        <v>13</v>
       </c>
       <c r="H7">
-        <v>11.1</v>
+        <v>12.1</v>
       </c>
       <c r="I7">
-        <v>7.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J7">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="K7">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="L7">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="M7">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -2665,48 +2636,48 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>78.3</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="C8">
-        <v>2.5</v>
+        <v>7.3</v>
       </c>
       <c r="D8">
-        <v>5.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E8">
-        <v>7.3</v>
+        <v>10.6</v>
       </c>
       <c r="F8">
-        <v>11.6</v>
+        <v>12.9</v>
       </c>
       <c r="G8">
-        <v>18.4</v>
+        <v>15.8</v>
       </c>
       <c r="H8">
-        <v>23.1</v>
+        <v>19.7</v>
       </c>
       <c r="I8">
-        <v>15.7</v>
+        <v>12.6</v>
       </c>
       <c r="J8">
-        <v>9.6</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="L8">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="M8">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -2715,7 +2686,7 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>45.8</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2726,46 +2697,46 @@
         <v>0.1</v>
       </c>
       <c r="C9">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="D9">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="E9">
-        <v>2.1</v>
+        <v>4.9</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>7.1</v>
       </c>
       <c r="G9">
-        <v>5.1</v>
+        <v>9.9</v>
       </c>
       <c r="H9">
-        <v>12</v>
+        <v>16.3</v>
       </c>
       <c r="I9">
-        <v>21.7</v>
+        <v>22.1</v>
       </c>
       <c r="J9">
-        <v>23.3</v>
+        <v>17.5</v>
       </c>
       <c r="K9">
-        <v>17.7</v>
+        <v>10.6</v>
       </c>
       <c r="L9">
-        <v>10.1</v>
+        <v>5.9</v>
       </c>
       <c r="M9">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="N9">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>11.6</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2773,49 +2744,49 @@
         <v>1</v>
       </c>
       <c r="B10">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C10">
         <v>0.3</v>
       </c>
       <c r="D10">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E10">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="F10">
         <v>2.6</v>
       </c>
       <c r="G10">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H10">
-        <v>10.6</v>
+        <v>7.2</v>
       </c>
       <c r="I10">
-        <v>17.3</v>
+        <v>15.6</v>
       </c>
       <c r="J10">
-        <v>25.7</v>
+        <v>26.5</v>
       </c>
       <c r="K10">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="L10">
-        <v>10.2</v>
+        <v>15.4</v>
       </c>
       <c r="M10">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="N10">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="O10">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>10.2</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2826,46 +2797,46 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D11">
+        <v>0.1</v>
+      </c>
+      <c r="E11">
         <v>0.2</v>
       </c>
-      <c r="E11">
-        <v>0.5</v>
-      </c>
       <c r="F11">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="G11">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="H11">
-        <v>9.6</v>
+        <v>5.1</v>
       </c>
       <c r="I11">
-        <v>18.4</v>
+        <v>11.2</v>
       </c>
       <c r="J11">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="K11">
-        <v>25.5</v>
+        <v>28.3</v>
       </c>
       <c r="L11">
-        <v>13.3</v>
+        <v>24.1</v>
       </c>
       <c r="M11">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="N11">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="O11">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2876,46 +2847,46 @@
         <v>0</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D12">
+        <v>0.1</v>
+      </c>
+      <c r="E12">
         <v>0.2</v>
       </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
       <c r="F12">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="G12">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="H12">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="I12">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="J12">
-        <v>12.2</v>
+        <v>14.2</v>
       </c>
       <c r="K12">
-        <v>20.7</v>
+        <v>27.2</v>
       </c>
       <c r="L12">
-        <v>40.4</v>
+        <v>39.1</v>
       </c>
       <c r="M12">
-        <v>15.8</v>
+        <v>7.7</v>
       </c>
       <c r="N12">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="O12">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2941,28 +2912,28 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J13">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="K13">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="L13">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="M13">
-        <v>23.4</v>
+        <v>52.9</v>
       </c>
       <c r="N13">
-        <v>40.7</v>
+        <v>26.5</v>
       </c>
       <c r="O13">
-        <v>27.7</v>
+        <v>6.9</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -3003,16 +2974,16 @@
         <v>0.1</v>
       </c>
       <c r="L14">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="M14">
-        <v>9.300000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="N14">
-        <v>26.6</v>
+        <v>15.2</v>
       </c>
       <c r="O14">
-        <v>63.1</v>
+        <v>80.2</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -3041,28 +3012,28 @@
         <v>0</v>
       </c>
       <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0.1</v>
+      </c>
+      <c r="J15">
         <v>0.2</v>
       </c>
-      <c r="I15">
-        <v>0.5</v>
-      </c>
-      <c r="J15">
-        <v>1.3</v>
-      </c>
       <c r="K15">
-        <v>6.1</v>
+        <v>1</v>
       </c>
       <c r="L15">
-        <v>16.6</v>
+        <v>3.8</v>
       </c>
       <c r="M15">
-        <v>40.5</v>
+        <v>25.5</v>
       </c>
       <c r="N15">
-        <v>26.3</v>
+        <v>56.5</v>
       </c>
       <c r="O15">
-        <v>8.5</v>
+        <v>12.9</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -3075,336 +3046,372 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>49</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B2">
-        <v>26.2</v>
+        <v>92.7</v>
       </c>
       <c r="C2">
-        <v>30.9</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="D2">
-        <v>77</v>
+        <v>60.5</v>
       </c>
       <c r="E2">
-        <v>67.30000000000001</v>
+        <v>82.19999999999999</v>
       </c>
       <c r="F2">
-        <v>82.19999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="G2">
-        <v>96.59999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="H2">
-        <v>95.8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>96</v>
+      </c>
+      <c r="I2">
+        <v>94.69999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B3">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="C3">
-        <v>30.4</v>
+        <v>31.2</v>
       </c>
       <c r="D3">
-        <v>75.5</v>
+        <v>76.8</v>
       </c>
       <c r="E3">
-        <v>96.39999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="F3">
         <v>99.40000000000001</v>
       </c>
       <c r="G3">
-        <v>93.8</v>
+        <v>93.89999999999999</v>
       </c>
       <c r="H3">
-        <v>95.39999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>91.8</v>
+      </c>
+      <c r="I3">
+        <v>86.40000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>68.5</v>
+      </c>
+      <c r="D4">
+        <v>49.6</v>
+      </c>
+      <c r="E4">
+        <v>91.5</v>
+      </c>
+      <c r="F4">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="G4">
+        <v>79.5</v>
+      </c>
+      <c r="H4">
+        <v>85</v>
+      </c>
+      <c r="I4">
+        <v>83.39999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>28.4</v>
+      </c>
+      <c r="C5">
+        <v>31.7</v>
+      </c>
+      <c r="D5">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="E5">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="F5">
+        <v>83.39999999999999</v>
+      </c>
+      <c r="G5">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="H5">
+        <v>78</v>
+      </c>
+      <c r="I5">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B4">
+      <c r="B6">
         <v>99.5</v>
       </c>
-      <c r="C4">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="D4">
-        <v>98.2</v>
-      </c>
-      <c r="E4">
-        <v>55.50000000000001</v>
-      </c>
-      <c r="F4">
-        <v>76.7</v>
-      </c>
-      <c r="G4">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="H4">
-        <v>86.2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>94.69999999999999</v>
-      </c>
-      <c r="C5">
-        <v>97.7</v>
-      </c>
-      <c r="D5">
-        <v>63</v>
-      </c>
-      <c r="E5">
-        <v>83</v>
-      </c>
-      <c r="F5">
-        <v>97.3</v>
-      </c>
-      <c r="G5">
-        <v>84.7</v>
-      </c>
-      <c r="H5">
-        <v>85.7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1" t="s">
+      <c r="C6">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="D6">
+        <v>98.3</v>
+      </c>
+      <c r="E6">
+        <v>60</v>
+      </c>
+      <c r="F6">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="G6">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="H6">
+        <v>67</v>
+      </c>
+      <c r="I6">
+        <v>78.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>69.19999999999999</v>
+      </c>
+      <c r="C7">
+        <v>4.3</v>
+      </c>
+      <c r="D7">
+        <v>0.8</v>
+      </c>
+      <c r="E7">
+        <v>12.5</v>
+      </c>
+      <c r="F7">
+        <v>34.1</v>
+      </c>
+      <c r="G7">
+        <v>39.7</v>
+      </c>
+      <c r="H7">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="I7">
+        <v>71.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B6">
+      <c r="B8">
+        <v>6.5</v>
+      </c>
+      <c r="C8">
+        <v>88.8</v>
+      </c>
+      <c r="D8">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="E8">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="F8">
+        <v>76</v>
+      </c>
+      <c r="G8">
+        <v>89.3</v>
+      </c>
+      <c r="H8">
+        <v>65.2</v>
+      </c>
+      <c r="I8">
+        <v>61.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9">
+        <v>0.8</v>
+      </c>
+      <c r="C9">
+        <v>0.2</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>1.3</v>
+      </c>
+      <c r="F9">
         <v>7.000000000000001</v>
       </c>
-      <c r="C6">
-        <v>90.2</v>
-      </c>
-      <c r="D6">
-        <v>78.8</v>
-      </c>
-      <c r="E6">
-        <v>94.39999999999999</v>
-      </c>
-      <c r="F6">
-        <v>78.8</v>
-      </c>
-      <c r="G6">
-        <v>87.2</v>
-      </c>
-      <c r="H6">
-        <v>85.39999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>67.60000000000001</v>
-      </c>
-      <c r="D7">
-        <v>50.1</v>
-      </c>
-      <c r="E7">
-        <v>93.40000000000001</v>
-      </c>
-      <c r="F7">
-        <v>66.60000000000001</v>
-      </c>
-      <c r="G7">
-        <v>80.5</v>
-      </c>
-      <c r="H7">
-        <v>74.2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8">
-        <v>68.60000000000001</v>
-      </c>
-      <c r="C8">
-        <v>6.600000000000001</v>
-      </c>
-      <c r="D8">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="E8">
-        <v>10.7</v>
-      </c>
-      <c r="F8">
-        <v>34</v>
-      </c>
-      <c r="G8">
-        <v>42.4</v>
-      </c>
-      <c r="H8">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="1" t="s">
+      <c r="G9">
+        <v>12.6</v>
+      </c>
+      <c r="H9">
+        <v>21.3</v>
+      </c>
+      <c r="I9">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B9">
+      <c r="B10">
         <v>100</v>
       </c>
-      <c r="C9">
-        <v>97.2</v>
-      </c>
-      <c r="D9">
-        <v>62.3</v>
-      </c>
-      <c r="E9">
-        <v>29.2</v>
-      </c>
-      <c r="F9">
-        <v>38.2</v>
-      </c>
-      <c r="G9">
-        <v>13.4</v>
-      </c>
-      <c r="H9">
-        <v>13.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10">
-        <v>0.6</v>
-      </c>
       <c r="C10">
-        <v>0.1</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>61.3</v>
       </c>
       <c r="E10">
-        <v>0.5</v>
+        <v>29.5</v>
       </c>
       <c r="F10">
-        <v>6.7</v>
+        <v>39.7</v>
       </c>
       <c r="G10">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="H10">
-        <v>9.6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>10.2</v>
+      </c>
+      <c r="I10">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B11">
-        <v>78.90000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="C11">
-        <v>77.3</v>
+        <v>76</v>
       </c>
       <c r="D11">
-        <v>91.90000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="E11">
-        <v>68.89999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="F11">
-        <v>19.9</v>
+        <v>19.3</v>
       </c>
       <c r="G11">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
       <c r="H11">
-        <v>5.800000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>6.800000000000001</v>
+      </c>
+      <c r="I11">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B12">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
         <v>0.2</v>
       </c>
-      <c r="D12">
-        <v>0.4</v>
-      </c>
       <c r="E12">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="F12">
+        <v>0.5</v>
+      </c>
+      <c r="G12">
+        <v>1.2</v>
+      </c>
+      <c r="H12">
+        <v>3.8</v>
+      </c>
+      <c r="I12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13">
+        <v>13.7</v>
+      </c>
+      <c r="C13">
+        <v>2.2</v>
+      </c>
+      <c r="D13">
         <v>0.1</v>
       </c>
-      <c r="G12">
-        <v>1.1</v>
-      </c>
-      <c r="H12">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13">
-        <v>14.8</v>
-      </c>
-      <c r="C13">
-        <v>1.8</v>
-      </c>
-      <c r="D13">
-        <v>0.2</v>
-      </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -3412,16 +3419,19 @@
       <c r="H13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="I13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B14">
-        <v>10</v>
+        <v>11.4</v>
       </c>
       <c r="C14">
-        <v>0.8999999999999999</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="D14">
         <v>0.1</v>
@@ -3438,30 +3448,36 @@
       <c r="H14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="I14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B15">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="E15">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="F15">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
         <v>0</v>
       </c>
     </row>
@@ -3477,28 +3493,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3509,25 +3525,25 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D2">
-        <v>73.87</v>
+        <v>68.48</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>104.7</v>
+        <v>105.26</v>
       </c>
       <c r="G2">
-        <v>0.542</v>
+        <v>0.551</v>
       </c>
       <c r="H2">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3535,28 +3551,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D3">
-        <v>90.13</v>
+        <v>90.06999999999999</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F3">
-        <v>103.66</v>
+        <v>104.86</v>
       </c>
       <c r="G3">
-        <v>0.604</v>
+        <v>0.612</v>
       </c>
       <c r="H3">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3564,28 +3580,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D4">
-        <v>97.15000000000001</v>
+        <v>102.45</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F4">
-        <v>101.46</v>
+        <v>102.05</v>
       </c>
       <c r="G4">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="H4">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3593,28 +3609,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D5">
-        <v>104.36</v>
+        <v>85.12</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F5">
-        <v>99.84999999999999</v>
+        <v>103.6</v>
       </c>
       <c r="G5">
-        <v>0.417</v>
+        <v>0.633</v>
       </c>
       <c r="H5">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3622,28 +3638,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D6">
-        <v>88.33</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>102.33</v>
+        <v>101.56</v>
       </c>
       <c r="G6">
-        <v>0.542</v>
+        <v>0.551</v>
       </c>
       <c r="H6">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3651,28 +3667,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D7">
-        <v>87.69</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F7">
-        <v>101.96</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="G7">
-        <v>0.625</v>
+        <v>0.429</v>
       </c>
       <c r="H7">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3680,28 +3696,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D8">
-        <v>96.43000000000001</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="E8" t="s">
         <v>16</v>
       </c>
       <c r="F8">
-        <v>100.15</v>
+        <v>99.27</v>
       </c>
       <c r="G8">
-        <v>0.583</v>
+        <v>0.49</v>
       </c>
       <c r="H8">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="I8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3712,25 +3728,25 @@
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D9">
-        <v>106.92</v>
+        <v>111.78</v>
       </c>
       <c r="E9" t="s">
         <v>16</v>
       </c>
       <c r="F9">
-        <v>99.12</v>
+        <v>99.56</v>
       </c>
       <c r="G9">
-        <v>0.5</v>
+        <v>0.531</v>
       </c>
       <c r="H9">
-        <v>-0.8</v>
+        <v>-1.6</v>
       </c>
       <c r="I9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3741,25 +3757,25 @@
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D10">
-        <v>110.14</v>
+        <v>104.75</v>
       </c>
       <c r="E10" t="s">
         <v>19</v>
       </c>
       <c r="F10">
-        <v>99.16</v>
+        <v>96.14</v>
       </c>
       <c r="G10">
-        <v>0.438</v>
+        <v>0.388</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>-2.6</v>
       </c>
       <c r="I10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3767,28 +3783,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D11">
-        <v>103.48</v>
+        <v>113.54</v>
       </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F11">
-        <v>97.34999999999999</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="G11">
-        <v>0.417</v>
+        <v>0.49</v>
       </c>
       <c r="H11">
-        <v>-1.2</v>
+        <v>-3</v>
       </c>
       <c r="I11">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3796,28 +3812,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D12">
-        <v>118.41</v>
+        <v>112.74</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F12">
-        <v>98.05</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G12">
-        <v>0.521</v>
+        <v>0.367</v>
       </c>
       <c r="H12">
-        <v>-1.6</v>
+        <v>-3.3</v>
       </c>
       <c r="I12">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3825,28 +3841,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D13">
-        <v>109.53</v>
+        <v>97.92</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F13">
-        <v>96.48999999999999</v>
+        <v>97.42</v>
       </c>
       <c r="G13">
-        <v>0.417</v>
+        <v>0.571</v>
       </c>
       <c r="H13">
-        <v>-1.8</v>
+        <v>-3.4</v>
       </c>
       <c r="I13">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -3854,28 +3870,28 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D14">
-        <v>95.73999999999999</v>
+        <v>116.92</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F14">
-        <v>94.87</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="G14">
-        <v>0.375</v>
+        <v>0.51</v>
       </c>
       <c r="H14">
-        <v>-3</v>
+        <v>-4.3</v>
       </c>
       <c r="I14">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -3883,28 +3899,28 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D15">
-        <v>113.78</v>
+        <v>100.47</v>
       </c>
       <c r="E15" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F15">
-        <v>96.8</v>
+        <v>93.39</v>
       </c>
       <c r="G15">
-        <v>0.521</v>
+        <v>0.388</v>
       </c>
       <c r="H15">
-        <v>-3.6</v>
+        <v>-4.9</v>
       </c>
       <c r="I15">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3919,51 +3935,51 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C2">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D2">
-        <v>110.1433333333333</v>
+        <v>112.7371428571429</v>
       </c>
       <c r="E2">
-        <v>660.8599999999999</v>
+        <v>789.16</v>
       </c>
       <c r="F2">
-        <v>96</v>
+        <v>94.89999999999999</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -3980,19 +3996,19 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C3">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D3">
-        <v>118.4066666666667</v>
+        <v>116.92</v>
       </c>
       <c r="E3">
-        <v>710.4400000000001</v>
+        <v>818.4400000000001</v>
       </c>
       <c r="F3">
-        <v>95.3</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -4001,27 +4017,27 @@
         <v>85</v>
       </c>
       <c r="I3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C4">
-        <v>0.8333333333333334</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D4">
-        <v>103.4766666666666</v>
+        <v>113.5371428571429</v>
       </c>
       <c r="E4">
-        <v>620.8599999999999</v>
+        <v>794.7600000000001</v>
       </c>
       <c r="F4">
-        <v>87.90000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -4030,27 +4046,27 @@
         <v>86</v>
       </c>
       <c r="I4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C5">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D5">
-        <v>104.3566666666667</v>
+        <v>104.7514285714285</v>
       </c>
       <c r="E5">
-        <v>626.14</v>
+        <v>733.2599999999999</v>
       </c>
       <c r="F5">
-        <v>84.59999999999999</v>
+        <v>82.19999999999999</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -4059,27 +4075,27 @@
         <v>87</v>
       </c>
       <c r="I5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C6">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D6">
-        <v>109.5266666666667</v>
+        <v>100.4742857142857</v>
       </c>
       <c r="E6">
-        <v>657.16</v>
+        <v>703.3199999999999</v>
       </c>
       <c r="F6">
-        <v>83.89999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -4088,27 +4104,27 @@
         <v>88</v>
       </c>
       <c r="I6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D7">
-        <v>113.7766666666667</v>
+        <v>111.78</v>
       </c>
       <c r="E7">
-        <v>682.6600000000001</v>
+        <v>782.4599999999998</v>
       </c>
       <c r="F7">
-        <v>78.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -4122,22 +4138,22 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
         <v>80</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D8">
-        <v>106.9233333333333</v>
+        <v>102.4457142857143</v>
       </c>
       <c r="E8">
-        <v>641.5399999999998</v>
+        <v>717.12</v>
       </c>
       <c r="F8">
-        <v>45.8</v>
+        <v>58.59999999999999</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -4154,19 +4170,19 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C9">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D9">
-        <v>97.15333333333332</v>
+        <v>98.99428571428571</v>
       </c>
       <c r="E9">
-        <v>582.92</v>
+        <v>692.9599999999999</v>
       </c>
       <c r="F9">
-        <v>11.6</v>
+        <v>26.4</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -4175,7 +4191,7 @@
         <v>91</v>
       </c>
       <c r="I9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -4183,28 +4199,28 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C10">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D10">
-        <v>96.42666666666666</v>
+        <v>97.91999999999999</v>
       </c>
       <c r="E10">
-        <v>578.5599999999999</v>
+        <v>685.4399999999999</v>
       </c>
       <c r="F10">
-        <v>10.2</v>
+        <v>9.9</v>
       </c>
       <c r="G10">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="s">
         <v>92</v>
       </c>
       <c r="I10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -4212,22 +4228,22 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C11">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D11">
-        <v>95.73666666666668</v>
+        <v>94.04285714285716</v>
       </c>
       <c r="E11">
-        <v>574.4200000000001</v>
+        <v>658.3000000000001</v>
       </c>
       <c r="F11">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="G11">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H11" t="s">
         <v>93</v>
@@ -4241,28 +4257,28 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C12">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D12">
-        <v>88.32666666666665</v>
+        <v>90.06857142857142</v>
       </c>
       <c r="E12">
-        <v>529.9599999999999</v>
+        <v>630.4799999999999</v>
       </c>
       <c r="F12">
-        <v>0.8999999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="G12">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H12" t="s">
         <v>94</v>
       </c>
       <c r="I12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -4270,28 +4286,28 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D13">
-        <v>90.12666666666667</v>
+        <v>90.50571428571428</v>
       </c>
       <c r="E13">
-        <v>540.76</v>
+        <v>633.54</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>27.7</v>
+        <v>6.9</v>
       </c>
       <c r="H13" t="s">
         <v>95</v>
       </c>
       <c r="I13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -4302,19 +4318,19 @@
         <v>83</v>
       </c>
       <c r="C14">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D14">
-        <v>73.87333333333333</v>
+        <v>68.48</v>
       </c>
       <c r="E14">
-        <v>443.24</v>
+        <v>479.36</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>63.1</v>
+        <v>80.2</v>
       </c>
       <c r="H14" t="s">
         <v>96</v>
@@ -4331,25 +4347,25 @@
         <v>83</v>
       </c>
       <c r="C15">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D15">
-        <v>87.69</v>
+        <v>85.11714285714285</v>
       </c>
       <c r="E15">
-        <v>526.14</v>
+        <v>595.8199999999999</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>8.5</v>
+        <v>12.9</v>
       </c>
       <c r="H15" t="s">
         <v>97</v>
       </c>
       <c r="I15" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -4364,19 +4380,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4387,16 +4403,16 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4404,19 +4420,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
         <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4424,19 +4440,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D4">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4447,7 +4463,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D5">
         <v>9</v>
@@ -4456,7 +4472,7 @@
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4467,16 +4483,16 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4484,19 +4500,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4504,19 +4520,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4524,19 +4540,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F9" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4544,19 +4560,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" t="s">
         <v>62</v>
       </c>
       <c r="D10">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4567,16 +4583,16 @@
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D11">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="E11" t="s">
         <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4587,7 +4603,7 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D12">
         <v>-10</v>
@@ -4596,7 +4612,7 @@
         <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4607,16 +4623,16 @@
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D13">
-        <v>-14</v>
+        <v>-17</v>
       </c>
       <c r="E13" t="s">
         <v>16</v>
       </c>
       <c r="F13" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4630,13 +4646,13 @@
         <v>61</v>
       </c>
       <c r="D14">
-        <v>-14</v>
+        <v>-19</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F14" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4647,16 +4663,16 @@
         <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D15">
-        <v>-21</v>
+        <v>-30</v>
       </c>
       <c r="E15" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -4666,33 +4682,36 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -4714,63 +4733,72 @@
       <c r="G2">
         <v>17</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>9</v>
+      </c>
+      <c r="G3">
+        <v>12</v>
+      </c>
+      <c r="H3">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:9">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3">
+      <c r="B4">
         <v>-9</v>
       </c>
-      <c r="C3">
+      <c r="C4">
         <v>-3</v>
       </c>
-      <c r="D3">
+      <c r="D4">
         <v>2</v>
       </c>
-      <c r="E3">
+      <c r="E4">
         <v>6</v>
       </c>
-      <c r="F3">
+      <c r="F4">
         <v>8</v>
       </c>
-      <c r="G3">
-        <v>16</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="G4">
+        <v>16</v>
+      </c>
+      <c r="H4">
+        <v>18</v>
+      </c>
+      <c r="I4" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>5</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>9</v>
-      </c>
-      <c r="G4">
-        <v>12</v>
-      </c>
-      <c r="H4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -4792,11 +4820,14 @@
       <c r="G5">
         <v>9</v>
       </c>
-      <c r="H5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="H5">
+        <v>9</v>
+      </c>
+      <c r="I5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
@@ -4818,115 +4849,130 @@
       <c r="G6">
         <v>7</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6">
+        <v>9</v>
+      </c>
+      <c r="I6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>-3</v>
+      </c>
+      <c r="C7">
+        <v>-4</v>
+      </c>
+      <c r="D7">
+        <v>-9</v>
+      </c>
+      <c r="E7">
+        <v>-4</v>
+      </c>
+      <c r="F7">
+        <v>-3</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="1" t="s">
+    <row r="8" spans="1:9">
+      <c r="A8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+      <c r="E8">
+        <v>8</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8">
+        <v>-3</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7">
+      <c r="B9">
         <v>-2</v>
       </c>
-      <c r="C7">
+      <c r="C9">
         <v>4</v>
       </c>
-      <c r="D7">
+      <c r="D9">
         <v>11</v>
       </c>
-      <c r="E7">
+      <c r="E9">
         <v>11</v>
       </c>
-      <c r="F7">
+      <c r="F9">
         <v>7</v>
       </c>
-      <c r="G7">
+      <c r="G9">
         <v>7</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8">
+    <row r="10" spans="1:9">
+      <c r="A10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10">
         <v>3</v>
       </c>
-      <c r="C8">
+      <c r="C10">
         <v>1</v>
       </c>
-      <c r="D8">
+      <c r="D10">
         <v>1</v>
       </c>
-      <c r="E8">
+      <c r="E10">
         <v>-4</v>
       </c>
-      <c r="F8">
+      <c r="F10">
         <v>-1</v>
       </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>-1</v>
+      </c>
+      <c r="I10" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9">
-        <v>-3</v>
-      </c>
-      <c r="C9">
-        <v>-4</v>
-      </c>
-      <c r="D9">
-        <v>-9</v>
-      </c>
-      <c r="E9">
-        <v>-4</v>
-      </c>
-      <c r="F9">
-        <v>-3</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
-      <c r="H9" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10">
-        <v>6</v>
-      </c>
-      <c r="C10">
-        <v>5</v>
-      </c>
-      <c r="D10">
-        <v>5</v>
-      </c>
-      <c r="E10">
-        <v>8</v>
-      </c>
-      <c r="F10">
-        <v>3</v>
-      </c>
-      <c r="G10">
-        <v>-3</v>
-      </c>
-      <c r="H10" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>3</v>
       </c>
@@ -4948,11 +4994,14 @@
       <c r="G11">
         <v>-4</v>
       </c>
-      <c r="H11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="H11">
+        <v>-7</v>
+      </c>
+      <c r="I11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
@@ -4974,11 +5023,14 @@
       <c r="G12">
         <v>-10</v>
       </c>
-      <c r="H12" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="H12">
+        <v>-10</v>
+      </c>
+      <c r="I12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
         <v>9</v>
       </c>
@@ -5000,11 +5052,14 @@
       <c r="G13">
         <v>-14</v>
       </c>
-      <c r="H13" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="H13">
+        <v>-17</v>
+      </c>
+      <c r="I13" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
         <v>10</v>
       </c>
@@ -5026,11 +5081,14 @@
       <c r="G14">
         <v>-14</v>
       </c>
-      <c r="H14" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="H14">
+        <v>-19</v>
+      </c>
+      <c r="I14" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
         <v>7</v>
       </c>
@@ -5052,8 +5110,11 @@
       <c r="G15">
         <v>-21</v>
       </c>
-      <c r="H15" t="s">
-        <v>118</v>
+      <c r="H15">
+        <v>-30</v>
+      </c>
+      <c r="I15" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/BP- Loudoun 2025 2026.xlsx
+++ b/data/leagues/BP- Loudoun 2025 2026.xlsx
@@ -277,40 +277,40 @@
     <t>1-6</t>
   </si>
   <si>
-    <t>10.0-4.0-0.1</t>
+    <t>9.9-4.0-0.1</t>
   </si>
   <si>
     <t>9.2-4.8-0.1</t>
   </si>
   <si>
-    <t>9.0-4.9-0.1</t>
+    <t>9.1-4.9-0.1</t>
   </si>
   <si>
     <t>9.2-4.7-0.1</t>
   </si>
   <si>
+    <t>8.6-5.4-0.1</t>
+  </si>
+  <si>
     <t>9.1-4.8-0.1</t>
   </si>
   <si>
-    <t>8.6-5.4-0.1</t>
-  </si>
-  <si>
     <t>8.5-5.4-0.1</t>
   </si>
   <si>
-    <t>7.5-6.4-0.1</t>
-  </si>
-  <si>
-    <t>6.4-7.5-0.1</t>
-  </si>
-  <si>
-    <t>6.1-7.8-0.1</t>
+    <t>7.4-6.5-0.1</t>
+  </si>
+  <si>
+    <t>6.5-7.4-0.1</t>
+  </si>
+  <si>
+    <t>6.0-7.9-0.1</t>
   </si>
   <si>
     <t>5.9-8.0-0.1</t>
   </si>
   <si>
-    <t>3.3-10.6-0.1</t>
+    <t>3.4-10.5-0.1</t>
   </si>
   <si>
     <t>1.8-12.1</t>
@@ -337,7 +337,7 @@
     <t>3-11</t>
   </si>
   <si>
-    <t>1-13</t>
+    <t>2-12</t>
   </si>
   <si>
     <t>Owners</t>
@@ -2344,35 +2344,35 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>35.8</v>
+        <v>34.6</v>
       </c>
       <c r="C2">
-        <v>21.2</v>
+        <v>21.6</v>
       </c>
       <c r="D2">
-        <v>16.6</v>
+        <v>16</v>
       </c>
       <c r="E2">
-        <v>9.1</v>
+        <v>11.9</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="G2">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H2">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J2">
+        <v>0.7</v>
+      </c>
+      <c r="K2">
         <v>0.2</v>
       </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
       <c r="L2">
         <v>0</v>
       </c>
@@ -2386,7 +2386,7 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>94.90000000000001</v>
+        <v>95.7</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2394,37 +2394,37 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="C3">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="D3">
-        <v>15.2</v>
+        <v>15.5</v>
       </c>
       <c r="E3">
-        <v>15.7</v>
+        <v>13.8</v>
       </c>
       <c r="F3">
-        <v>10.1</v>
+        <v>11.5</v>
       </c>
       <c r="G3">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="H3">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="I3">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J3">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="K3">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -2436,7 +2436,7 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>89.09999999999999</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2444,34 +2444,34 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>12.7</v>
+        <v>12.3</v>
       </c>
       <c r="C4">
-        <v>16.4</v>
+        <v>18.5</v>
       </c>
       <c r="D4">
-        <v>15.8</v>
+        <v>17.6</v>
       </c>
       <c r="E4">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="F4">
-        <v>12.3</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="J4">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="K4">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>83.59999999999999</v>
+        <v>84.7</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2494,31 +2494,31 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>10.4</v>
+        <v>11.9</v>
       </c>
       <c r="C5">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="D5">
-        <v>13.9</v>
+        <v>13.1</v>
       </c>
       <c r="E5">
-        <v>16.2</v>
+        <v>13.5</v>
       </c>
       <c r="F5">
-        <v>13.5</v>
+        <v>15.1</v>
       </c>
       <c r="G5">
-        <v>13.6</v>
+        <v>14.1</v>
       </c>
       <c r="H5">
-        <v>9.6</v>
+        <v>11.4</v>
       </c>
       <c r="I5">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="J5">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="K5">
         <v>0.7</v>
@@ -2536,48 +2536,48 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>82.2</v>
+        <v>80.90000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B6">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="C6">
-        <v>11.7</v>
+        <v>10.8</v>
       </c>
       <c r="D6">
-        <v>13.8</v>
+        <v>11.8</v>
       </c>
       <c r="E6">
-        <v>13.2</v>
+        <v>14.2</v>
       </c>
       <c r="F6">
-        <v>16.9</v>
+        <v>15.8</v>
       </c>
       <c r="G6">
-        <v>13.6</v>
+        <v>14.9</v>
       </c>
       <c r="H6">
-        <v>10.5</v>
+        <v>12.3</v>
       </c>
       <c r="I6">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J6">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="K6">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="L6">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -2586,45 +2586,45 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>76.40000000000001</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B7">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="C7">
-        <v>9.699999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="D7">
-        <v>13</v>
+        <v>13.8</v>
       </c>
       <c r="E7">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="F7">
-        <v>15.1</v>
+        <v>14.3</v>
       </c>
       <c r="G7">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="H7">
-        <v>12.1</v>
+        <v>12.6</v>
       </c>
       <c r="I7">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K7">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="L7">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -2636,7 +2636,7 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>72.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2644,40 +2644,40 @@
         <v>3</v>
       </c>
       <c r="B8">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="C8">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="D8">
         <v>8.300000000000001</v>
       </c>
       <c r="E8">
-        <v>10.6</v>
+        <v>11</v>
       </c>
       <c r="F8">
-        <v>12.9</v>
+        <v>13.5</v>
       </c>
       <c r="G8">
-        <v>15.8</v>
+        <v>14</v>
       </c>
       <c r="H8">
-        <v>19.7</v>
+        <v>18.4</v>
       </c>
       <c r="I8">
-        <v>12.6</v>
+        <v>14.6</v>
       </c>
       <c r="J8">
-        <v>6</v>
+        <v>7.1</v>
       </c>
       <c r="K8">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="L8">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -2686,7 +2686,7 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>58.6</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2694,49 +2694,49 @@
         <v>6</v>
       </c>
       <c r="B9">
+        <v>0.4</v>
+      </c>
+      <c r="C9">
+        <v>2.2</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>5.1</v>
+      </c>
+      <c r="F9">
+        <v>6.4</v>
+      </c>
+      <c r="G9">
+        <v>11</v>
+      </c>
+      <c r="H9">
+        <v>13.6</v>
+      </c>
+      <c r="I9">
+        <v>21.5</v>
+      </c>
+      <c r="J9">
+        <v>17.7</v>
+      </c>
+      <c r="K9">
+        <v>11.8</v>
+      </c>
+      <c r="L9">
+        <v>6.4</v>
+      </c>
+      <c r="M9">
+        <v>0.8</v>
+      </c>
+      <c r="N9">
         <v>0.1</v>
       </c>
-      <c r="C9">
-        <v>1.8</v>
-      </c>
-      <c r="D9">
-        <v>2.6</v>
-      </c>
-      <c r="E9">
-        <v>4.9</v>
-      </c>
-      <c r="F9">
-        <v>7.1</v>
-      </c>
-      <c r="G9">
-        <v>9.9</v>
-      </c>
-      <c r="H9">
-        <v>16.3</v>
-      </c>
-      <c r="I9">
-        <v>22.1</v>
-      </c>
-      <c r="J9">
-        <v>17.5</v>
-      </c>
-      <c r="K9">
-        <v>10.6</v>
-      </c>
-      <c r="L9">
-        <v>5.9</v>
-      </c>
-      <c r="M9">
-        <v>1.2</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>26.4</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2747,46 +2747,46 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D10">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E10">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="F10">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="G10">
         <v>4.8</v>
       </c>
       <c r="H10">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="I10">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="J10">
-        <v>26.5</v>
+        <v>25.3</v>
       </c>
       <c r="K10">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="L10">
-        <v>15.4</v>
+        <v>13.4</v>
       </c>
       <c r="M10">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="N10">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>9.9</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2794,49 +2794,49 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="F11">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="G11">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="H11">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="I11">
-        <v>11.2</v>
+        <v>10.3</v>
       </c>
       <c r="J11">
-        <v>21.1</v>
+        <v>20.4</v>
       </c>
       <c r="K11">
-        <v>28.3</v>
+        <v>27</v>
       </c>
       <c r="L11">
-        <v>24.1</v>
+        <v>26.2</v>
       </c>
       <c r="M11">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="N11">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2847,46 +2847,46 @@
         <v>0</v>
       </c>
       <c r="C12">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D12">
         <v>0.1</v>
       </c>
       <c r="E12">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="F12">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G12">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="H12">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="I12">
-        <v>5.8</v>
+        <v>6.7</v>
       </c>
       <c r="J12">
-        <v>14.2</v>
+        <v>15.4</v>
       </c>
       <c r="K12">
-        <v>27.2</v>
+        <v>27.9</v>
       </c>
       <c r="L12">
-        <v>39.1</v>
+        <v>38.1</v>
       </c>
       <c r="M12">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="N12">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2915,25 +2915,25 @@
         <v>0.1</v>
       </c>
       <c r="I13">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J13">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K13">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="L13">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="M13">
-        <v>52.9</v>
+        <v>56.4</v>
       </c>
       <c r="N13">
-        <v>26.5</v>
+        <v>24.4</v>
       </c>
       <c r="O13">
-        <v>6.9</v>
+        <v>5.4</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -2971,19 +2971,19 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L14">
         <v>0.1</v>
       </c>
       <c r="M14">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="N14">
-        <v>15.2</v>
+        <v>14.9</v>
       </c>
       <c r="O14">
-        <v>80.2</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -3015,25 +3015,25 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="K15">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="L15">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="M15">
-        <v>25.5</v>
+        <v>23</v>
       </c>
       <c r="N15">
-        <v>56.5</v>
+        <v>58</v>
       </c>
       <c r="O15">
-        <v>12.9</v>
+        <v>13.7</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -3080,28 +3080,28 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>92.7</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="C2">
-        <v>98.90000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="D2">
-        <v>60.5</v>
+        <v>61</v>
       </c>
       <c r="E2">
-        <v>82.19999999999999</v>
+        <v>81.89999999999999</v>
       </c>
       <c r="F2">
-        <v>96.5</v>
+        <v>96.39999999999999</v>
       </c>
       <c r="G2">
-        <v>85.8</v>
+        <v>84.3</v>
       </c>
       <c r="H2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I2">
-        <v>94.69999999999999</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3109,28 +3109,28 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>95.5</v>
+        <v>94.39999999999999</v>
       </c>
       <c r="C3">
-        <v>31.2</v>
+        <v>28.9</v>
       </c>
       <c r="D3">
-        <v>76.8</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="E3">
-        <v>96.5</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="F3">
-        <v>99.40000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="G3">
-        <v>93.89999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="H3">
-        <v>91.8</v>
+        <v>90.60000000000001</v>
       </c>
       <c r="I3">
-        <v>86.40000000000001</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3141,25 +3141,25 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>68.5</v>
+        <v>68.8</v>
       </c>
       <c r="D4">
-        <v>49.6</v>
+        <v>49.2</v>
       </c>
       <c r="E4">
-        <v>91.5</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="F4">
-        <v>67.90000000000001</v>
+        <v>64.60000000000001</v>
       </c>
       <c r="G4">
-        <v>79.5</v>
+        <v>78.2</v>
       </c>
       <c r="H4">
-        <v>85</v>
+        <v>84.3</v>
       </c>
       <c r="I4">
-        <v>83.39999999999999</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3167,86 +3167,86 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>28.4</v>
+        <v>27.2</v>
       </c>
       <c r="C5">
-        <v>31.7</v>
+        <v>29.8</v>
       </c>
       <c r="D5">
-        <v>80.40000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="E5">
-        <v>64.40000000000001</v>
+        <v>65</v>
       </c>
       <c r="F5">
-        <v>83.39999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="G5">
-        <v>95.59999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="H5">
-        <v>78</v>
+        <v>77.3</v>
       </c>
       <c r="I5">
-        <v>81</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B6">
-        <v>99.5</v>
+        <v>68.7</v>
       </c>
       <c r="C6">
-        <v>99.40000000000001</v>
+        <v>6.600000000000001</v>
       </c>
       <c r="D6">
-        <v>98.3</v>
+        <v>1.4</v>
       </c>
       <c r="E6">
-        <v>60</v>
+        <v>12.2</v>
       </c>
       <c r="F6">
-        <v>76.09999999999999</v>
+        <v>32.6</v>
       </c>
       <c r="G6">
-        <v>84.59999999999999</v>
+        <v>40.8</v>
       </c>
       <c r="H6">
-        <v>67</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I6">
-        <v>78.3</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B7">
-        <v>69.19999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="C7">
-        <v>4.3</v>
+        <v>99.5</v>
       </c>
       <c r="D7">
-        <v>0.8</v>
+        <v>97.5</v>
       </c>
       <c r="E7">
-        <v>12.5</v>
+        <v>61.2</v>
       </c>
       <c r="F7">
-        <v>34.1</v>
+        <v>77</v>
       </c>
       <c r="G7">
-        <v>39.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="H7">
-        <v>74.90000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I7">
-        <v>71.8</v>
+        <v>72.89999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3254,28 +3254,28 @@
         <v>3</v>
       </c>
       <c r="B8">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="C8">
-        <v>88.8</v>
+        <v>90</v>
       </c>
       <c r="D8">
-        <v>79.90000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="E8">
-        <v>92.40000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="F8">
-        <v>76</v>
+        <v>78.7</v>
       </c>
       <c r="G8">
-        <v>89.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H8">
-        <v>65.2</v>
+        <v>66.3</v>
       </c>
       <c r="I8">
-        <v>61.6</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3283,7 +3283,7 @@
         <v>6</v>
       </c>
       <c r="B9">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="C9">
         <v>0.2</v>
@@ -3292,19 +3292,19 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="F9">
-        <v>7.000000000000001</v>
+        <v>7.199999999999999</v>
       </c>
       <c r="G9">
-        <v>12.6</v>
+        <v>13.7</v>
       </c>
       <c r="H9">
-        <v>21.3</v>
+        <v>23.2</v>
       </c>
       <c r="I9">
-        <v>27.3</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3315,25 +3315,25 @@
         <v>100</v>
       </c>
       <c r="C10">
-        <v>98.09999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D10">
-        <v>61.3</v>
+        <v>63.2</v>
       </c>
       <c r="E10">
-        <v>29.5</v>
+        <v>26.2</v>
       </c>
       <c r="F10">
-        <v>39.7</v>
+        <v>42.1</v>
       </c>
       <c r="G10">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="H10">
-        <v>10.2</v>
+        <v>8.799999999999999</v>
       </c>
       <c r="I10">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3341,28 +3341,28 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>79.40000000000001</v>
+        <v>81</v>
       </c>
       <c r="C11">
-        <v>76</v>
+        <v>76.8</v>
       </c>
       <c r="D11">
-        <v>90.3</v>
+        <v>92.30000000000001</v>
       </c>
       <c r="E11">
-        <v>68.7</v>
+        <v>67.7</v>
       </c>
       <c r="F11">
-        <v>19.3</v>
+        <v>21.2</v>
       </c>
       <c r="G11">
-        <v>6.3</v>
+        <v>4.2</v>
       </c>
       <c r="H11">
-        <v>6.800000000000001</v>
+        <v>5.600000000000001</v>
       </c>
       <c r="I11">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3370,28 +3370,28 @@
         <v>9</v>
       </c>
       <c r="B12">
+        <v>0.2</v>
+      </c>
+      <c r="C12">
         <v>0.3</v>
       </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
       <c r="D12">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E12">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="F12">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G12">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="H12">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="I12">
-        <v>3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3399,25 +3399,25 @@
         <v>0</v>
       </c>
       <c r="B13">
-        <v>13.7</v>
+        <v>13.5</v>
       </c>
       <c r="C13">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="D13">
+        <v>0.2</v>
+      </c>
+      <c r="E13">
         <v>0.1</v>
       </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
       <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
         <v>0.1</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -3428,10 +3428,10 @@
         <v>7</v>
       </c>
       <c r="B14">
-        <v>11.4</v>
+        <v>10.2</v>
       </c>
       <c r="C14">
-        <v>0.7000000000000001</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="D14">
         <v>0.1</v>
@@ -3457,22 +3457,22 @@
         <v>10</v>
       </c>
       <c r="B15">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="E15">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -3979,7 +3979,7 @@
         <v>789.16</v>
       </c>
       <c r="F2">
-        <v>94.89999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -4008,7 +4008,7 @@
         <v>818.4400000000001</v>
       </c>
       <c r="F3">
-        <v>89.09999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -4017,7 +4017,7 @@
         <v>85</v>
       </c>
       <c r="I3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -4037,7 +4037,7 @@
         <v>794.7600000000001</v>
       </c>
       <c r="F4">
-        <v>83.59999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -4066,7 +4066,7 @@
         <v>733.2599999999999</v>
       </c>
       <c r="F5">
-        <v>82.19999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -4080,22 +4080,22 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C6">
-        <v>0.7142857142857143</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D6">
-        <v>100.4742857142857</v>
+        <v>111.78</v>
       </c>
       <c r="E6">
-        <v>703.3199999999999</v>
+        <v>782.4599999999998</v>
       </c>
       <c r="F6">
-        <v>76.40000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C7">
-        <v>0.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D7">
-        <v>111.78</v>
+        <v>100.4742857142857</v>
       </c>
       <c r="E7">
-        <v>782.4599999999998</v>
+        <v>703.3199999999999</v>
       </c>
       <c r="F7">
-        <v>72.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -4153,7 +4153,7 @@
         <v>717.12</v>
       </c>
       <c r="F8">
-        <v>58.59999999999999</v>
+        <v>57.09999999999999</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -4182,7 +4182,7 @@
         <v>692.9599999999999</v>
       </c>
       <c r="F9">
-        <v>26.4</v>
+        <v>28.1</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -4191,7 +4191,7 @@
         <v>91</v>
       </c>
       <c r="I9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -4211,7 +4211,7 @@
         <v>685.4399999999999</v>
       </c>
       <c r="F10">
-        <v>9.9</v>
+        <v>10.9</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -4240,7 +4240,7 @@
         <v>658.3000000000001</v>
       </c>
       <c r="F11">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -4269,7 +4269,7 @@
         <v>630.4799999999999</v>
       </c>
       <c r="F12">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -4301,7 +4301,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>6.9</v>
+        <v>5.4</v>
       </c>
       <c r="H13" t="s">
         <v>95</v>
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>80.2</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="H14" t="s">
         <v>96</v>
@@ -4359,7 +4359,7 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>12.9</v>
+        <v>13.7</v>
       </c>
       <c r="H15" t="s">
         <v>97</v>
@@ -4460,10 +4460,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D5">
         <v>9</v>
@@ -4472,7 +4472,7 @@
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4480,10 +4480,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D6">
         <v>9</v>
@@ -4492,7 +4492,7 @@
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4800,60 +4800,60 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="F5">
         <v>11</v>
       </c>
-      <c r="B5">
-        <v>-3</v>
-      </c>
-      <c r="C5">
-        <v>-2</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
+      <c r="G5">
         <v>7</v>
-      </c>
-      <c r="G5">
-        <v>9</v>
       </c>
       <c r="H5">
         <v>9</v>
       </c>
       <c r="I5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
+        <v>-3</v>
+      </c>
+      <c r="C6">
+        <v>-2</v>
+      </c>
+      <c r="D6">
         <v>2</v>
       </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6">
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
         <v>7</v>
       </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
       <c r="G6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H6">
         <v>9</v>
       </c>
       <c r="I6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:9">
